--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -881,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1379.3</v>
+        <v>1350.4</v>
       </c>
       <c r="D2">
-        <v>-0.38</v>
+        <v>-2.1</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -893,25 +893,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-5.73</v>
+        <v>-7.7</v>
       </c>
       <c r="H2">
-        <v>14.38</v>
+        <v>11.98</v>
       </c>
       <c r="I2">
-        <v>-3.08</v>
+        <v>-5.4</v>
       </c>
       <c r="J2">
-        <v>-1.95</v>
+        <v>-4.7</v>
       </c>
       <c r="K2">
-        <v>3.89</v>
+        <v>1.21</v>
       </c>
       <c r="L2">
-        <v>-1.74</v>
+        <v>-3.81</v>
       </c>
       <c r="M2">
-        <v>15.01</v>
+        <v>14.28</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -920,19 +920,19 @@
         <v>57</v>
       </c>
       <c r="P2">
-        <v>1395.96</v>
+        <v>1380.54</v>
       </c>
       <c r="Q2">
-        <v>1417.31</v>
+        <v>1414.07</v>
       </c>
       <c r="R2">
-        <v>1424.43</v>
+        <v>1422.9</v>
       </c>
       <c r="S2">
-        <v>1356.22</v>
+        <v>1356.1</v>
       </c>
       <c r="T2">
-        <v>1.7</v>
+        <v>-0.42</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -944,46 +944,46 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>37.19</v>
+        <v>30.88</v>
       </c>
       <c r="Z2">
-        <v>-7.37</v>
+        <v>-11.43</v>
       </c>
       <c r="AA2">
-        <v>-1.08</v>
+        <v>-3.15</v>
       </c>
       <c r="AB2">
-        <v>-6.28</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>21.4</v>
+        <v>22.7</v>
       </c>
       <c r="AF2">
-        <v>-21.38</v>
+        <v>14.88</v>
       </c>
       <c r="AG2">
-        <v>1455.66</v>
+        <v>1462.73</v>
       </c>
       <c r="AH2">
-        <v>1378.96</v>
+        <v>1365.4</v>
       </c>
       <c r="AI2">
-        <v>1442.5</v>
+        <v>1438.3</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>31.11</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,58 +994,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1459.8</v>
+        <v>1427.7</v>
       </c>
       <c r="D3">
-        <v>-0.35</v>
+        <v>-2.2</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
       </c>
       <c r="F3">
-        <v>1459.8</v>
+        <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-28.27</v>
+        <v>-29.85</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-3.32</v>
+        <v>-4.4</v>
       </c>
       <c r="J3">
-        <v>-10.33</v>
+        <v>-12.41</v>
       </c>
       <c r="K3">
-        <v>-15.82</v>
+        <v>-19.95</v>
       </c>
       <c r="L3">
-        <v>-19.88</v>
+        <v>-22.5</v>
       </c>
       <c r="M3">
-        <v>-1.55</v>
+        <v>-1.67</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P3">
-        <v>1475.32</v>
+        <v>1462.18</v>
       </c>
       <c r="Q3">
-        <v>1558.5</v>
+        <v>1548.57</v>
       </c>
       <c r="R3">
-        <v>1633.44</v>
+        <v>1626.28</v>
       </c>
       <c r="S3">
-        <v>1792.82</v>
+        <v>1789.94</v>
       </c>
       <c r="T3">
-        <v>-18.58</v>
+        <v>-20.24</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,16 +1060,16 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>18.95</v>
+        <v>15.95</v>
       </c>
       <c r="Z3">
-        <v>-49.09</v>
+        <v>-52.3</v>
       </c>
       <c r="AA3">
-        <v>-40.73</v>
+        <v>-43.04</v>
       </c>
       <c r="AB3">
-        <v>-8.359999999999999</v>
+        <v>-9.26</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1078,25 +1078,25 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>30.58</v>
+        <v>31.24</v>
       </c>
       <c r="AF3">
-        <v>-24.25</v>
+        <v>6.78</v>
       </c>
       <c r="AG3">
-        <v>1679.1</v>
+        <v>1678.04</v>
       </c>
       <c r="AH3">
-        <v>1437.89</v>
+        <v>1419.09</v>
       </c>
       <c r="AI3">
-        <v>1546.08</v>
+        <v>1536.78</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>59.71</v>
+        <v>63.34</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,58 +1107,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>471.5</v>
+        <v>457.6</v>
       </c>
       <c r="D4">
-        <v>0.11</v>
+        <v>-2.95</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
       </c>
       <c r="F4">
-        <v>460.4</v>
+        <v>457.6</v>
       </c>
       <c r="G4">
-        <v>-31.28</v>
+        <v>-33.3</v>
       </c>
       <c r="H4">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-4.66</v>
+        <v>-2.77</v>
       </c>
       <c r="J4">
-        <v>-7</v>
+        <v>-10.12</v>
       </c>
       <c r="K4">
-        <v>-3.01</v>
+        <v>-6.68</v>
       </c>
       <c r="L4">
-        <v>-20.9</v>
+        <v>-23.75</v>
       </c>
       <c r="M4">
-        <v>-7.29</v>
+        <v>-7.89</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>468.99</v>
+        <v>466.38</v>
       </c>
       <c r="Q4">
-        <v>496.13</v>
+        <v>493.56</v>
       </c>
       <c r="R4">
-        <v>501.48</v>
+        <v>500.93</v>
       </c>
       <c r="S4">
-        <v>561.41</v>
+        <v>560.6</v>
       </c>
       <c r="T4">
-        <v>-16.01</v>
+        <v>-18.37</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.53</v>
+        <v>31.25</v>
       </c>
       <c r="Z4">
-        <v>-9.470000000000001</v>
+        <v>-10.86</v>
       </c>
       <c r="AA4">
-        <v>-5.3</v>
+        <v>-6.42</v>
       </c>
       <c r="AB4">
-        <v>-4.17</v>
+        <v>-4.45</v>
       </c>
       <c r="AC4">
-        <v>16</v>
+        <v>17.69</v>
       </c>
       <c r="AD4">
-        <v>7.93</v>
+        <v>13.82</v>
       </c>
       <c r="AE4">
-        <v>13.78</v>
+        <v>13.84</v>
       </c>
       <c r="AF4">
-        <v>5.06</v>
+        <v>-27.99</v>
       </c>
       <c r="AG4">
-        <v>531.1900000000001</v>
+        <v>532</v>
       </c>
       <c r="AH4">
-        <v>461.08</v>
+        <v>455.12</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
@@ -1209,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>31.49</v>
+        <v>32.48</v>
       </c>
     </row>
   </sheetData>
@@ -1407,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.3</v>
+        <v>-1.95</v>
       </c>
       <c r="D7" s="5">
-        <v>-1.95</v>
+        <v>-4.7</v>
       </c>
       <c r="E7" s="6">
-        <v>1.35</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-10.4</v>
+        <v>-10.33</v>
       </c>
       <c r="D8" s="5">
-        <v>-10.33</v>
+        <v>-12.41</v>
       </c>
       <c r="E8" s="6">
-        <v>0.07000000000000001</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.99</v>
+        <v>-7</v>
       </c>
       <c r="D9" s="5">
-        <v>-7</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.01</v>
+        <v>-10.12</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-3.12</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-3.18</v>
+        <v>-3.08</v>
       </c>
       <c r="D10" s="5">
-        <v>-3.08</v>
+        <v>-5.4</v>
       </c>
       <c r="E10" s="6">
-        <v>0.1</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.73</v>
+        <v>-3.32</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.32</v>
+        <v>-4.4</v>
       </c>
       <c r="E11" s="6">
-        <v>0.41</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.86</v>
+        <v>-4.66</v>
       </c>
       <c r="D12" s="5">
-        <v>-4.66</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.2</v>
+        <v>-2.77</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.89</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1509,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-1.3</v>
+        <v>-1.74</v>
       </c>
       <c r="D13" s="5">
-        <v>-1.74</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.44</v>
+        <v>-3.81</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-2.07</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1526,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-19.51</v>
+        <v>-19.88</v>
       </c>
       <c r="D14" s="5">
-        <v>-19.88</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.37</v>
+        <v>-22.5</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1543,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-20.32</v>
+        <v>-20.9</v>
       </c>
       <c r="D15" s="5">
-        <v>-20.9</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.58</v>
+        <v>-23.75</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1560,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>3.26</v>
+        <v>3.89</v>
       </c>
       <c r="D16" s="5">
-        <v>3.89</v>
+        <v>1.21</v>
       </c>
       <c r="E16" s="6">
-        <v>0.63</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1577,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-13.61</v>
+        <v>-15.82</v>
       </c>
       <c r="D17" s="5">
-        <v>-15.82</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.21</v>
+        <v>-19.95</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-4.13</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1594,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>0.61</v>
+        <v>-3.01</v>
       </c>
       <c r="D18" s="5">
-        <v>-3.01</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-3.62</v>
+        <v>-6.68</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-3.67</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1611,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-5.37</v>
+        <v>-5.73</v>
       </c>
       <c r="D19" s="5">
-        <v>-5.73</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.36</v>
+        <v>-7.7</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.97</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1628,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-28.02</v>
+        <v>-28.27</v>
       </c>
       <c r="D20" s="5">
-        <v>-28.27</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.25</v>
+        <v>-29.85</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1645,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-31.35</v>
+        <v>-31.28</v>
       </c>
       <c r="D21" s="5">
-        <v>-31.28</v>
+        <v>-33.3</v>
       </c>
       <c r="E21" s="6">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1662,13 +1662,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1384.5</v>
+        <v>1379.3</v>
       </c>
       <c r="D22" s="5">
-        <v>1379.3</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-5.2</v>
+        <v>1350.4</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-28.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1679,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1465</v>
+        <v>1459.8</v>
       </c>
       <c r="D23" s="5">
-        <v>1459.8</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-5.2</v>
+        <v>1427.7</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-32.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1696,13 +1696,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>471</v>
+        <v>471.5</v>
       </c>
       <c r="D24" s="5">
-        <v>471.5</v>
+        <v>457.6</v>
       </c>
       <c r="E24" s="6">
-        <v>0.5</v>
+        <v>-13.9</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1713,13 +1713,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>38.5</v>
+        <v>37.19</v>
       </c>
       <c r="D25" s="5">
-        <v>37.19</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.31</v>
+        <v>30.88</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-6.31</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1730,13 +1730,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>19.51</v>
+        <v>18.95</v>
       </c>
       <c r="D26" s="5">
-        <v>18.95</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.5600000000000001</v>
+        <v>15.95</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-3</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1747,13 +1747,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>36.17</v>
+        <v>36.53</v>
       </c>
       <c r="D27" s="5">
-        <v>36.53</v>
+        <v>31.25</v>
       </c>
       <c r="E27" s="6">
-        <v>0.36</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1764,13 +1764,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>18.55</v>
+        <v>-21.38</v>
       </c>
       <c r="D28" s="5">
-        <v>-21.38</v>
+        <v>14.88</v>
       </c>
       <c r="E28" s="7">
-        <v>-39.93</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1781,13 +1781,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-65.12</v>
+        <v>-24.25</v>
       </c>
       <c r="D29" s="5">
-        <v>-24.25</v>
-      </c>
-      <c r="E29" s="6">
-        <v>40.87</v>
+        <v>6.78</v>
+      </c>
+      <c r="E29" s="7">
+        <v>31.03</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1798,13 +1798,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>74.48999999999999</v>
+        <v>5.06</v>
       </c>
       <c r="D30" s="5">
-        <v>5.06</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-69.43000000000001</v>
+        <v>-27.99</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-33.05</v>
       </c>
     </row>
   </sheetData>
@@ -1863,22 +1863,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="10">
-        <v>48.52</v>
+        <v>36.52</v>
       </c>
       <c r="C2" s="11">
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>30.9</v>
+        <v>26</v>
       </c>
       <c r="E2" s="10">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.4</v>
+        <v>-9.1</v>
       </c>
       <c r="G2" s="10">
-        <v>-5</v>
+        <v>-8.5</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1997,13 +1997,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1501</v>
+        <v>0.1428</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0155</v>
+        <v>-0.0167</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.07290000000000001</v>
+        <v>-0.0789</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -881,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1350.4</v>
+        <v>1358.8</v>
       </c>
       <c r="D2">
-        <v>-2.1</v>
+        <v>0.62</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -893,46 +893,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-7.7</v>
+        <v>-7.13</v>
       </c>
       <c r="H2">
-        <v>11.98</v>
+        <v>12.68</v>
       </c>
       <c r="I2">
-        <v>-5.4</v>
+        <v>-2.9</v>
       </c>
       <c r="J2">
-        <v>-4.7</v>
+        <v>-3.99</v>
       </c>
       <c r="K2">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="L2">
-        <v>-3.81</v>
+        <v>-3.05</v>
       </c>
       <c r="M2">
-        <v>14.28</v>
+        <v>14.01</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P2">
-        <v>1380.54</v>
+        <v>1372.42</v>
       </c>
       <c r="Q2">
-        <v>1414.07</v>
+        <v>1411.41</v>
       </c>
       <c r="R2">
-        <v>1422.9</v>
+        <v>1421.78</v>
       </c>
       <c r="S2">
-        <v>1356.1</v>
+        <v>1355.93</v>
       </c>
       <c r="T2">
-        <v>-0.42</v>
+        <v>0.21</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -944,46 +944,46 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>30.88</v>
+        <v>34.36</v>
       </c>
       <c r="Z2">
-        <v>-11.43</v>
+        <v>-13.81</v>
       </c>
       <c r="AA2">
-        <v>-3.15</v>
+        <v>-5.28</v>
       </c>
       <c r="AB2">
-        <v>-8.279999999999999</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE2">
-        <v>22.7</v>
+        <v>22.03</v>
       </c>
       <c r="AF2">
-        <v>14.88</v>
+        <v>7.3</v>
       </c>
       <c r="AG2">
-        <v>1462.73</v>
+        <v>1466</v>
       </c>
       <c r="AH2">
-        <v>1365.4</v>
+        <v>1356.81</v>
       </c>
       <c r="AI2">
-        <v>1438.3</v>
+        <v>1420.8</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>34.85</v>
+        <v>38.27</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1427.7</v>
+        <v>1440</v>
       </c>
       <c r="D3">
-        <v>-2.2</v>
+        <v>0.86</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1006,46 +1006,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-29.85</v>
+        <v>-29.24</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="I3">
-        <v>-4.4</v>
+        <v>-2.99</v>
       </c>
       <c r="J3">
-        <v>-12.41</v>
+        <v>-11.46</v>
       </c>
       <c r="K3">
-        <v>-19.95</v>
+        <v>-19.58</v>
       </c>
       <c r="L3">
-        <v>-22.5</v>
+        <v>-22.49</v>
       </c>
       <c r="M3">
-        <v>-1.67</v>
+        <v>-1.57</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P3">
-        <v>1462.18</v>
+        <v>1453.3</v>
       </c>
       <c r="Q3">
-        <v>1548.57</v>
+        <v>1539.38</v>
       </c>
       <c r="R3">
-        <v>1626.28</v>
+        <v>1619.2</v>
       </c>
       <c r="S3">
-        <v>1789.94</v>
+        <v>1787.28</v>
       </c>
       <c r="T3">
-        <v>-20.24</v>
+        <v>-19.43</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1060,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>15.95</v>
+        <v>21.11</v>
       </c>
       <c r="Z3">
-        <v>-52.3</v>
+        <v>-53.25</v>
       </c>
       <c r="AA3">
-        <v>-43.04</v>
+        <v>-45.08</v>
       </c>
       <c r="AB3">
-        <v>-9.26</v>
+        <v>-8.16</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>8.77</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE3">
-        <v>31.24</v>
+        <v>31.01</v>
       </c>
       <c r="AF3">
-        <v>6.78</v>
+        <v>-50.69</v>
       </c>
       <c r="AG3">
-        <v>1678.04</v>
+        <v>1672.41</v>
       </c>
       <c r="AH3">
-        <v>1419.09</v>
+        <v>1406.34</v>
       </c>
       <c r="AI3">
-        <v>1536.78</v>
+        <v>1535.77</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>63.34</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>457.6</v>
+        <v>470</v>
       </c>
       <c r="D4">
-        <v>-2.95</v>
+        <v>2.71</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1119,46 +1119,46 @@
         <v>457.6</v>
       </c>
       <c r="G4">
-        <v>-33.3</v>
+        <v>-31.49</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="I4">
-        <v>-2.77</v>
+        <v>0.15</v>
       </c>
       <c r="J4">
-        <v>-10.12</v>
+        <v>-7.69</v>
       </c>
       <c r="K4">
         <v>-6.68</v>
       </c>
       <c r="L4">
-        <v>-23.75</v>
+        <v>-21.19</v>
       </c>
       <c r="M4">
-        <v>-7.89</v>
+        <v>-7.51</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P4">
-        <v>466.38</v>
+        <v>466.52</v>
       </c>
       <c r="Q4">
-        <v>493.56</v>
+        <v>492.15</v>
       </c>
       <c r="R4">
-        <v>500.93</v>
+        <v>500.57</v>
       </c>
       <c r="S4">
-        <v>560.6</v>
+        <v>559.83</v>
       </c>
       <c r="T4">
-        <v>-18.37</v>
+        <v>-16.05</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.25</v>
+        <v>39.63</v>
       </c>
       <c r="Z4">
-        <v>-10.86</v>
+        <v>-10.84</v>
       </c>
       <c r="AA4">
-        <v>-6.42</v>
+        <v>-7.3</v>
       </c>
       <c r="AB4">
-        <v>-4.45</v>
+        <v>-3.54</v>
       </c>
       <c r="AC4">
-        <v>17.69</v>
+        <v>21.98</v>
       </c>
       <c r="AD4">
-        <v>13.82</v>
+        <v>18.56</v>
       </c>
       <c r="AE4">
-        <v>13.84</v>
+        <v>14.06</v>
       </c>
       <c r="AF4">
-        <v>-27.99</v>
+        <v>-41.62</v>
       </c>
       <c r="AG4">
-        <v>532</v>
+        <v>531.92</v>
       </c>
       <c r="AH4">
-        <v>455.12</v>
+        <v>452.38</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
@@ -1209,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>32.48</v>
+        <v>32.45</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1407,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-1.95</v>
+        <v>-4.7</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.7</v>
+        <v>-3.99</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.75</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-10.33</v>
+        <v>-12.41</v>
       </c>
       <c r="D8" s="5">
-        <v>-12.41</v>
+        <v>-11.46</v>
       </c>
       <c r="E8" s="6">
-        <v>-2.08</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-7</v>
+        <v>-10.12</v>
       </c>
       <c r="D9" s="5">
-        <v>-10.12</v>
+        <v>-7.69</v>
       </c>
       <c r="E9" s="6">
-        <v>-3.12</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-3.08</v>
+        <v>-5.4</v>
       </c>
       <c r="D10" s="5">
-        <v>-5.4</v>
+        <v>-2.9</v>
       </c>
       <c r="E10" s="6">
-        <v>-2.32</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.32</v>
+        <v>-4.4</v>
       </c>
       <c r="D11" s="5">
-        <v>-4.4</v>
+        <v>-2.99</v>
       </c>
       <c r="E11" s="6">
-        <v>-1.08</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.66</v>
+        <v>-2.77</v>
       </c>
       <c r="D12" s="5">
-        <v>-2.77</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.89</v>
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2.92</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1509,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-1.74</v>
+        <v>-3.81</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.81</v>
+        <v>-3.05</v>
       </c>
       <c r="E13" s="6">
-        <v>-2.07</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1526,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-19.88</v>
+        <v>-22.5</v>
       </c>
       <c r="D14" s="5">
-        <v>-22.5</v>
+        <v>-22.49</v>
       </c>
       <c r="E14" s="6">
-        <v>-2.62</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1543,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-20.9</v>
+        <v>-23.75</v>
       </c>
       <c r="D15" s="5">
-        <v>-23.75</v>
+        <v>-21.19</v>
       </c>
       <c r="E15" s="6">
-        <v>-2.85</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1560,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>3.89</v>
+        <v>1.21</v>
       </c>
       <c r="D16" s="5">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="E16" s="6">
-        <v>-2.68</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1577,234 +1577,217 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-15.82</v>
+        <v>-19.95</v>
       </c>
       <c r="D17" s="5">
-        <v>-19.95</v>
+        <v>-19.58</v>
       </c>
       <c r="E17" s="6">
-        <v>-4.13</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C18" s="5">
-        <v>-3.01</v>
+        <v>-7.7</v>
       </c>
       <c r="D18" s="5">
-        <v>-6.68</v>
+        <v>-7.13</v>
       </c>
       <c r="E18" s="6">
-        <v>-3.67</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-5.73</v>
+        <v>-29.85</v>
       </c>
       <c r="D19" s="5">
-        <v>-7.7</v>
+        <v>-29.24</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.97</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-28.27</v>
+        <v>-33.3</v>
       </c>
       <c r="D20" s="5">
-        <v>-29.85</v>
+        <v>-31.49</v>
       </c>
       <c r="E20" s="6">
-        <v>-1.58</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C21" s="5">
-        <v>-31.28</v>
+        <v>1350.4</v>
       </c>
       <c r="D21" s="5">
-        <v>-33.3</v>
+        <v>1358.8</v>
       </c>
       <c r="E21" s="6">
-        <v>-2.02</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1379.3</v>
+        <v>1427.7</v>
       </c>
       <c r="D22" s="5">
-        <v>1350.4</v>
+        <v>1440</v>
       </c>
       <c r="E22" s="6">
-        <v>-28.9</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1459.8</v>
+        <v>457.6</v>
       </c>
       <c r="D23" s="5">
-        <v>1427.7</v>
+        <v>470</v>
       </c>
       <c r="E23" s="6">
-        <v>-32.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C24" s="5">
-        <v>471.5</v>
+        <v>30.88</v>
       </c>
       <c r="D24" s="5">
-        <v>457.6</v>
+        <v>34.36</v>
       </c>
       <c r="E24" s="6">
-        <v>-13.9</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>37.19</v>
+        <v>15.95</v>
       </c>
       <c r="D25" s="5">
-        <v>30.88</v>
+        <v>21.11</v>
       </c>
       <c r="E25" s="6">
-        <v>-6.31</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>18.95</v>
+        <v>31.25</v>
       </c>
       <c r="D26" s="5">
-        <v>15.95</v>
+        <v>39.63</v>
       </c>
       <c r="E26" s="6">
-        <v>-3</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C27" s="5">
-        <v>36.53</v>
+        <v>14.88</v>
       </c>
       <c r="D27" s="5">
-        <v>31.25</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-5.28</v>
+        <v>7.3</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-7.58</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-21.38</v>
+        <v>6.78</v>
       </c>
       <c r="D28" s="5">
-        <v>14.88</v>
+        <v>-50.69</v>
       </c>
       <c r="E28" s="7">
-        <v>36.26</v>
+        <v>-57.47</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-24.25</v>
+        <v>-27.99</v>
       </c>
       <c r="D29" s="5">
-        <v>6.78</v>
+        <v>-41.62</v>
       </c>
       <c r="E29" s="7">
-        <v>31.03</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>5.06</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-27.99</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-33.05</v>
+        <v>-13.63</v>
       </c>
     </row>
   </sheetData>
@@ -1863,22 +1846,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="10">
-        <v>36.52</v>
+        <v>48.52</v>
       </c>
       <c r="C2" s="11">
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>26</v>
+        <v>31.7</v>
       </c>
       <c r="E2" s="10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2" s="10">
-        <v>-9.1</v>
+        <v>-7.7</v>
       </c>
       <c r="G2" s="10">
-        <v>-8.5</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1997,13 +1980,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1428</v>
+        <v>0.1401</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0167</v>
+        <v>-0.0157</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0789</v>
+        <v>-0.0751</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,46 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>21.1 → 37.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>21.1</t>
+  </si>
+  <si>
+    <t>37.0</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>39.6 → 50.4</t>
+  </si>
+  <si>
+    <t>39.6</t>
+  </si>
+  <si>
+    <t>50.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -359,17 +398,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -881,10 +921,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1358.8</v>
+        <v>1347.6</v>
       </c>
       <c r="D2">
-        <v>0.62</v>
+        <v>-0.82</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -893,46 +933,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-7.13</v>
+        <v>-7.89</v>
       </c>
       <c r="H2">
-        <v>12.68</v>
+        <v>11.75</v>
       </c>
       <c r="I2">
-        <v>-2.9</v>
+        <v>-2.99</v>
       </c>
       <c r="J2">
-        <v>-3.99</v>
+        <v>-4.56</v>
       </c>
       <c r="K2">
-        <v>1.65</v>
+        <v>0.39</v>
       </c>
       <c r="L2">
-        <v>-3.05</v>
+        <v>-4.94</v>
       </c>
       <c r="M2">
-        <v>14.01</v>
+        <v>14.05</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="P2">
-        <v>1372.42</v>
+        <v>1364.12</v>
       </c>
       <c r="Q2">
-        <v>1411.41</v>
+        <v>1408.69</v>
       </c>
       <c r="R2">
-        <v>1421.78</v>
+        <v>1421.12</v>
       </c>
       <c r="S2">
-        <v>1355.93</v>
+        <v>1355.73</v>
       </c>
       <c r="T2">
-        <v>0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -944,46 +984,46 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>34.36</v>
+        <v>32.05</v>
       </c>
       <c r="Z2">
-        <v>-13.81</v>
+        <v>-16.42</v>
       </c>
       <c r="AA2">
-        <v>-5.28</v>
+        <v>-7.51</v>
       </c>
       <c r="AB2">
-        <v>-8.529999999999999</v>
+        <v>-8.91</v>
       </c>
       <c r="AC2">
-        <v>4.02</v>
+        <v>5.37</v>
       </c>
       <c r="AD2">
-        <v>1.34</v>
+        <v>3.13</v>
       </c>
       <c r="AE2">
-        <v>22.03</v>
+        <v>21.56</v>
       </c>
       <c r="AF2">
-        <v>7.3</v>
+        <v>-14.99</v>
       </c>
       <c r="AG2">
-        <v>1466</v>
+        <v>1470.23</v>
       </c>
       <c r="AH2">
-        <v>1356.81</v>
+        <v>1347.14</v>
       </c>
       <c r="AI2">
-        <v>1420.8</v>
+        <v>1419.98</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>38.27</v>
+        <v>40.71</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1034,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1440</v>
+        <v>1486.7</v>
       </c>
       <c r="D3">
-        <v>0.86</v>
+        <v>3.24</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1006,46 +1046,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-29.24</v>
+        <v>-26.95</v>
       </c>
       <c r="H3">
+        <v>4.13</v>
+      </c>
+      <c r="I3">
         <v>0.86</v>
       </c>
-      <c r="I3">
-        <v>-2.99</v>
-      </c>
       <c r="J3">
-        <v>-11.46</v>
+        <v>-8.44</v>
       </c>
       <c r="K3">
-        <v>-19.58</v>
+        <v>-19.16</v>
       </c>
       <c r="L3">
-        <v>-22.49</v>
+        <v>-20.93</v>
       </c>
       <c r="M3">
-        <v>-1.57</v>
+        <v>-0.79</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P3">
-        <v>1453.3</v>
+        <v>1455.84</v>
       </c>
       <c r="Q3">
-        <v>1539.38</v>
+        <v>1532.92</v>
       </c>
       <c r="R3">
-        <v>1619.2</v>
+        <v>1612.85</v>
       </c>
       <c r="S3">
-        <v>1787.28</v>
+        <v>1784.9</v>
       </c>
       <c r="T3">
-        <v>-19.43</v>
+        <v>-16.71</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,34 +1100,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>21.11</v>
+        <v>36.95</v>
       </c>
       <c r="Z3">
-        <v>-53.25</v>
+        <v>-49.65</v>
       </c>
       <c r="AA3">
-        <v>-45.08</v>
+        <v>-46</v>
       </c>
       <c r="AB3">
-        <v>-8.16</v>
+        <v>-3.66</v>
       </c>
       <c r="AC3">
-        <v>8.77</v>
+        <v>42.11</v>
       </c>
       <c r="AD3">
-        <v>2.92</v>
+        <v>16.96</v>
       </c>
       <c r="AE3">
-        <v>31.01</v>
+        <v>33.26</v>
       </c>
       <c r="AF3">
-        <v>-50.69</v>
+        <v>-20.71</v>
       </c>
       <c r="AG3">
-        <v>1672.41</v>
+        <v>1662.85</v>
       </c>
       <c r="AH3">
-        <v>1406.34</v>
+        <v>1403</v>
       </c>
       <c r="AI3">
         <v>1535.77</v>
@@ -1096,7 +1136,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>66.48999999999999</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1147,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>470</v>
+        <v>490.5</v>
       </c>
       <c r="D4">
-        <v>2.71</v>
+        <v>4.36</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1119,46 +1159,46 @@
         <v>457.6</v>
       </c>
       <c r="G4">
-        <v>-31.49</v>
+        <v>-28.51</v>
       </c>
       <c r="H4">
-        <v>2.71</v>
+        <v>7.19</v>
       </c>
       <c r="I4">
-        <v>0.15</v>
+        <v>6.05</v>
       </c>
       <c r="J4">
-        <v>-7.69</v>
+        <v>-1.55</v>
       </c>
       <c r="K4">
-        <v>-6.68</v>
+        <v>-6.05</v>
       </c>
       <c r="L4">
-        <v>-21.19</v>
+        <v>-18.08</v>
       </c>
       <c r="M4">
-        <v>-7.51</v>
+        <v>-6.81</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="P4">
-        <v>466.52</v>
+        <v>472.12</v>
       </c>
       <c r="Q4">
-        <v>492.15</v>
+        <v>491.7</v>
       </c>
       <c r="R4">
-        <v>500.57</v>
+        <v>500.78</v>
       </c>
       <c r="S4">
-        <v>559.83</v>
+        <v>559.2</v>
       </c>
       <c r="T4">
-        <v>-16.05</v>
+        <v>-12.28</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1213,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.63</v>
+        <v>50.39</v>
       </c>
       <c r="Z4">
-        <v>-10.84</v>
+        <v>-9.06</v>
       </c>
       <c r="AA4">
-        <v>-7.3</v>
+        <v>-7.65</v>
       </c>
       <c r="AB4">
-        <v>-3.54</v>
+        <v>-1.41</v>
       </c>
       <c r="AC4">
-        <v>21.98</v>
+        <v>39.16</v>
       </c>
       <c r="AD4">
-        <v>18.56</v>
+        <v>26.27</v>
       </c>
       <c r="AE4">
-        <v>14.06</v>
+        <v>15.07</v>
       </c>
       <c r="AF4">
-        <v>-41.62</v>
+        <v>99.44</v>
       </c>
       <c r="AG4">
-        <v>531.92</v>
+        <v>531.3200000000001</v>
       </c>
       <c r="AH4">
-        <v>452.38</v>
+        <v>452.08</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
@@ -1209,7 +1249,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>32.45</v>
+        <v>31.07</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1370,430 +1410,502 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-4.7</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-3.99</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-4.56</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-12.41</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-11.46</v>
       </c>
-      <c r="E8" s="6">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-8.44</v>
+      </c>
+      <c r="E9" s="8">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-10.12</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-7.69</v>
       </c>
-      <c r="E9" s="6">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-1.55</v>
+      </c>
+      <c r="E10" s="8">
+        <v>6.14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-5.4</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-2.9</v>
       </c>
-      <c r="E10" s="6">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-2.99</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-4.4</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-2.99</v>
       </c>
-      <c r="E11" s="6">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>0.86</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-2.77</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>0.15</v>
       </c>
-      <c r="E12" s="6">
-        <v>2.92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>6.05</v>
+      </c>
+      <c r="E13" s="8">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-3.81</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-3.05</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-4.94</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-22.5</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-22.49</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-20.93</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-23.75</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-21.19</v>
       </c>
-      <c r="E15" s="6">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-18.08</v>
+      </c>
+      <c r="E16" s="8">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>1.21</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>1.65</v>
       </c>
-      <c r="E16" s="6">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-19.95</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>-19.58</v>
       </c>
-      <c r="E17" s="6">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-19.16</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-6.68</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-6.05</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="5">
-        <v>-7.7</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C20" s="6">
         <v>-7.13</v>
       </c>
-      <c r="E18" s="6">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-7.89</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-29.85</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C21" s="6">
         <v>-29.24</v>
       </c>
-      <c r="E19" s="6">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-26.95</v>
+      </c>
+      <c r="E21" s="8">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-33.3</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C22" s="6">
         <v>-31.49</v>
       </c>
-      <c r="E20" s="6">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-28.51</v>
+      </c>
+      <c r="E22" s="8">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="5">
-        <v>1350.4</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C23" s="6">
         <v>1358.8</v>
       </c>
-      <c r="E21" s="6">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D23" s="6">
+        <v>1347.6</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-11.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>1427.7</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C24" s="6">
         <v>1440</v>
       </c>
-      <c r="E22" s="6">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D24" s="6">
+        <v>1486.7</v>
+      </c>
+      <c r="E24" s="8">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>457.6</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C25" s="6">
         <v>470</v>
       </c>
-      <c r="E23" s="6">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D25" s="6">
+        <v>490.5</v>
+      </c>
+      <c r="E25" s="8">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="5">
-        <v>30.88</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C26" s="6">
         <v>34.36</v>
       </c>
-      <c r="E24" s="6">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D26" s="6">
+        <v>32.05</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>15.95</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C27" s="6">
         <v>21.11</v>
       </c>
-      <c r="E25" s="6">
-        <v>5.16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D27" s="6">
+        <v>36.95</v>
+      </c>
+      <c r="E27" s="8">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>31.25</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C28" s="6">
         <v>39.63</v>
       </c>
-      <c r="E26" s="6">
-        <v>8.380000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D28" s="6">
+        <v>50.39</v>
+      </c>
+      <c r="E28" s="8">
+        <v>10.76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="5">
-        <v>14.88</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C29" s="6">
         <v>7.3</v>
       </c>
-      <c r="E27" s="7">
-        <v>-7.58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D29" s="6">
+        <v>-14.99</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-22.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>6.78</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C30" s="6">
         <v>-50.69</v>
       </c>
-      <c r="E28" s="7">
-        <v>-57.47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-20.71</v>
+      </c>
+      <c r="E30" s="8">
+        <v>29.98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-27.99</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C31" s="6">
         <v>-41.62</v>
       </c>
-      <c r="E29" s="7">
-        <v>-13.63</v>
+      <c r="D31" s="6">
+        <v>99.44</v>
+      </c>
+      <c r="E31" s="8">
+        <v>141.06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1813,60 +1925,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
-        <v>48.52</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="11">
+        <v>36.52</v>
+      </c>
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>31.7</v>
-      </c>
-      <c r="E2" s="10">
-        <v>30</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-7.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="11">
+        <v>39.8</v>
+      </c>
+      <c r="E2" s="11">
+        <v>0</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-4.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1968,25 +2080,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1401</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0157</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0751</v>
+      <c r="A2" s="14">
+        <v>0.1405</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.06809999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,46 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>21.1 → 37.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>21.1</t>
-  </si>
-  <si>
-    <t>37.0</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>39.6 → 50.4</t>
-  </si>
-  <si>
-    <t>39.6</t>
-  </si>
-  <si>
-    <t>50.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -398,18 +359,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -921,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1347.6</v>
+        <v>1338.9</v>
       </c>
       <c r="D2">
-        <v>-0.82</v>
+        <v>-0.65</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -933,46 +893,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-7.89</v>
+        <v>-8.49</v>
       </c>
       <c r="H2">
-        <v>11.75</v>
+        <v>11.03</v>
       </c>
       <c r="I2">
-        <v>-2.99</v>
+        <v>-3.29</v>
       </c>
       <c r="J2">
-        <v>-4.56</v>
+        <v>-4.5</v>
       </c>
       <c r="K2">
-        <v>0.39</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L2">
-        <v>-4.94</v>
+        <v>-5.67</v>
       </c>
       <c r="M2">
-        <v>14.05</v>
+        <v>14.24</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="P2">
-        <v>1364.12</v>
+        <v>1355</v>
       </c>
       <c r="Q2">
-        <v>1408.69</v>
+        <v>1405.04</v>
       </c>
       <c r="R2">
-        <v>1421.12</v>
+        <v>1420.29</v>
       </c>
       <c r="S2">
-        <v>1355.73</v>
+        <v>1355.47</v>
       </c>
       <c r="T2">
-        <v>-0.6</v>
+        <v>-1.22</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -987,43 +947,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>32.05</v>
+        <v>30.33</v>
       </c>
       <c r="Z2">
-        <v>-16.42</v>
+        <v>-18.97</v>
       </c>
       <c r="AA2">
-        <v>-7.51</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AB2">
-        <v>-8.91</v>
+        <v>-9.16</v>
       </c>
       <c r="AC2">
         <v>5.37</v>
       </c>
       <c r="AD2">
-        <v>3.13</v>
+        <v>4.92</v>
       </c>
       <c r="AE2">
-        <v>21.56</v>
+        <v>21.51</v>
       </c>
       <c r="AF2">
-        <v>-14.99</v>
+        <v>-17.82</v>
       </c>
       <c r="AG2">
-        <v>1470.23</v>
+        <v>1473.99</v>
       </c>
       <c r="AH2">
-        <v>1347.14</v>
+        <v>1336.08</v>
       </c>
       <c r="AI2">
-        <v>1419.98</v>
+        <v>1413.89</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>40.71</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1486.7</v>
+        <v>1458.1</v>
       </c>
       <c r="D3">
-        <v>3.24</v>
+        <v>-1.92</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1046,46 +1006,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-26.95</v>
+        <v>-28.35</v>
       </c>
       <c r="H3">
-        <v>4.13</v>
+        <v>2.13</v>
       </c>
       <c r="I3">
-        <v>0.86</v>
+        <v>-0.47</v>
       </c>
       <c r="J3">
-        <v>-8.44</v>
+        <v>-9.75</v>
       </c>
       <c r="K3">
-        <v>-19.16</v>
+        <v>-22.03</v>
       </c>
       <c r="L3">
-        <v>-20.93</v>
+        <v>-22.72</v>
       </c>
       <c r="M3">
-        <v>-0.79</v>
+        <v>-1.47</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P3">
-        <v>1455.84</v>
+        <v>1454.46</v>
       </c>
       <c r="Q3">
-        <v>1532.92</v>
+        <v>1524.58</v>
       </c>
       <c r="R3">
-        <v>1612.85</v>
+        <v>1606.12</v>
       </c>
       <c r="S3">
-        <v>1784.9</v>
+        <v>1782.27</v>
       </c>
       <c r="T3">
-        <v>-16.71</v>
+        <v>-18.19</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1100,34 +1060,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>36.95</v>
+        <v>32.63</v>
       </c>
       <c r="Z3">
-        <v>-49.65</v>
+        <v>-48.55</v>
       </c>
       <c r="AA3">
-        <v>-46</v>
+        <v>-46.51</v>
       </c>
       <c r="AB3">
-        <v>-3.66</v>
+        <v>-2.05</v>
       </c>
       <c r="AC3">
-        <v>42.11</v>
+        <v>68.58</v>
       </c>
       <c r="AD3">
-        <v>16.96</v>
+        <v>39.82</v>
       </c>
       <c r="AE3">
-        <v>33.26</v>
+        <v>32.94</v>
       </c>
       <c r="AF3">
-        <v>-20.71</v>
+        <v>0.25</v>
       </c>
       <c r="AG3">
-        <v>1662.85</v>
+        <v>1651</v>
       </c>
       <c r="AH3">
-        <v>1403</v>
+        <v>1398.16</v>
       </c>
       <c r="AI3">
         <v>1535.77</v>
@@ -1136,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>60.09</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>490.5</v>
+        <v>492</v>
       </c>
       <c r="D4">
-        <v>4.36</v>
+        <v>0.31</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1159,46 +1119,46 @@
         <v>457.6</v>
       </c>
       <c r="G4">
-        <v>-28.51</v>
+        <v>-28.29</v>
       </c>
       <c r="H4">
-        <v>7.19</v>
+        <v>7.52</v>
       </c>
       <c r="I4">
-        <v>6.05</v>
+        <v>4.46</v>
       </c>
       <c r="J4">
-        <v>-1.55</v>
+        <v>-1.5</v>
       </c>
       <c r="K4">
-        <v>-6.05</v>
+        <v>-1.66</v>
       </c>
       <c r="L4">
-        <v>-18.08</v>
+        <v>-18.42</v>
       </c>
       <c r="M4">
-        <v>-6.81</v>
+        <v>-6.09</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P4">
-        <v>472.12</v>
+        <v>476.32</v>
       </c>
       <c r="Q4">
-        <v>491.7</v>
+        <v>491.2</v>
       </c>
       <c r="R4">
-        <v>500.78</v>
+        <v>500.8</v>
       </c>
       <c r="S4">
-        <v>559.2</v>
+        <v>558.5599999999999</v>
       </c>
       <c r="T4">
-        <v>-12.28</v>
+        <v>-11.92</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1213,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>50.39</v>
+        <v>51.08</v>
       </c>
       <c r="Z4">
-        <v>-9.06</v>
+        <v>-7.45</v>
       </c>
       <c r="AA4">
-        <v>-7.65</v>
+        <v>-7.61</v>
       </c>
       <c r="AB4">
-        <v>-1.41</v>
+        <v>0.16</v>
       </c>
       <c r="AC4">
-        <v>39.16</v>
+        <v>63.72</v>
       </c>
       <c r="AD4">
-        <v>26.27</v>
+        <v>41.62</v>
       </c>
       <c r="AE4">
-        <v>15.07</v>
+        <v>14.78</v>
       </c>
       <c r="AF4">
-        <v>99.44</v>
+        <v>69.13</v>
       </c>
       <c r="AG4">
-        <v>531.3200000000001</v>
+        <v>530.52</v>
       </c>
       <c r="AH4">
-        <v>452.08</v>
+        <v>451.87</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
@@ -1249,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>31.07</v>
+        <v>30.76</v>
       </c>
     </row>
   </sheetData>
@@ -1390,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1410,502 +1370,447 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-4.56</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-4.5</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.06</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-8.44</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-9.75</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-1.55</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-1.5</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-3.99</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-4.56</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-2.99</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-3.29</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-11.46</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-8.44</v>
-      </c>
-      <c r="E9" s="8">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.86</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-0.47</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-7.69</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-1.55</v>
-      </c>
-      <c r="E10" s="8">
-        <v>6.14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>6.05</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4.46</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-2.9</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-4.94</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-5.67</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="E12" s="8">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-20.93</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-22.72</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.15</v>
-      </c>
-      <c r="D13" s="6">
-        <v>6.05</v>
-      </c>
-      <c r="E13" s="8">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-18.08</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-18.42</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-3.05</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-4.94</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.39</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-22.49</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-20.93</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-19.16</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-22.03</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-21.19</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-18.08</v>
-      </c>
-      <c r="E16" s="8">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-6.05</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-1.66</v>
+      </c>
+      <c r="E18" s="6">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>1.65</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.39</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-7.89</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-8.49</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-19.58</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-19.16</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-26.95</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-28.35</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-6.68</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-6.05</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-28.51</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-28.29</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-7.13</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-7.89</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1347.6</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1338.9</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-8.699999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-29.24</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-26.95</v>
-      </c>
-      <c r="E21" s="8">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1486.7</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1458.1</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-28.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-31.49</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-28.51</v>
-      </c>
-      <c r="E22" s="8">
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>490.5</v>
+      </c>
+      <c r="D24" s="5">
+        <v>492</v>
+      </c>
+      <c r="E24" s="6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1358.8</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1347.6</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-11.2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>32.05</v>
+      </c>
+      <c r="D25" s="5">
+        <v>30.33</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1440</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1486.7</v>
-      </c>
-      <c r="E24" s="8">
-        <v>46.7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>36.95</v>
+      </c>
+      <c r="D26" s="5">
+        <v>32.63</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-4.32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>470</v>
-      </c>
-      <c r="D25" s="6">
-        <v>490.5</v>
-      </c>
-      <c r="E25" s="8">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>50.39</v>
+      </c>
+      <c r="D27" s="5">
+        <v>51.08</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>34.36</v>
-      </c>
-      <c r="D26" s="6">
-        <v>32.05</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-14.99</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-17.82</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>21.11</v>
-      </c>
-      <c r="D27" s="6">
-        <v>36.95</v>
-      </c>
-      <c r="E27" s="8">
-        <v>15.84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-20.71</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="E29" s="6">
+        <v>20.96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>39.63</v>
-      </c>
-      <c r="D28" s="6">
-        <v>50.39</v>
-      </c>
-      <c r="E28" s="8">
-        <v>10.76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>7.3</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-14.99</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-22.29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-50.69</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-20.71</v>
-      </c>
-      <c r="E30" s="8">
-        <v>29.98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-41.62</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C30" s="5">
         <v>99.44</v>
       </c>
-      <c r="E31" s="8">
-        <v>141.06</v>
+      <c r="D30" s="5">
+        <v>69.13</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-30.31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1925,60 +1830,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-4.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-5.2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2080,25 +1985,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1405</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.007900000000000001</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.06809999999999999</v>
+      <c r="A2" s="13">
+        <v>0.1424</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0147</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0609</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -881,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1338.9</v>
+        <v>1345</v>
       </c>
       <c r="D2">
-        <v>-0.65</v>
+        <v>0.46</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -893,46 +893,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-8.49</v>
+        <v>-8.07</v>
       </c>
       <c r="H2">
-        <v>11.03</v>
+        <v>11.53</v>
       </c>
       <c r="I2">
-        <v>-3.29</v>
+        <v>-2.49</v>
       </c>
       <c r="J2">
-        <v>-4.5</v>
+        <v>-4.74</v>
       </c>
       <c r="K2">
-        <v>-0.5600000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="L2">
-        <v>-5.67</v>
+        <v>-5.39</v>
       </c>
       <c r="M2">
-        <v>14.24</v>
+        <v>14.27</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P2">
-        <v>1355</v>
+        <v>1348.14</v>
       </c>
       <c r="Q2">
-        <v>1405.04</v>
+        <v>1401.29</v>
       </c>
       <c r="R2">
-        <v>1420.29</v>
+        <v>1419.16</v>
       </c>
       <c r="S2">
-        <v>1355.47</v>
+        <v>1355.33</v>
       </c>
       <c r="T2">
-        <v>-1.22</v>
+        <v>-0.76</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +947,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>30.33</v>
+        <v>33.04</v>
       </c>
       <c r="Z2">
-        <v>-18.97</v>
+        <v>-20.26</v>
       </c>
       <c r="AA2">
-        <v>-9.800000000000001</v>
+        <v>-11.89</v>
       </c>
       <c r="AB2">
-        <v>-9.16</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="AC2">
-        <v>5.37</v>
+        <v>5.12</v>
       </c>
       <c r="AD2">
-        <v>4.92</v>
+        <v>5.29</v>
       </c>
       <c r="AE2">
-        <v>21.51</v>
+        <v>20.91</v>
       </c>
       <c r="AF2">
-        <v>-17.82</v>
+        <v>-36.63</v>
       </c>
       <c r="AG2">
-        <v>1473.99</v>
+        <v>1474.82</v>
       </c>
       <c r="AH2">
-        <v>1336.08</v>
+        <v>1327.75</v>
       </c>
       <c r="AI2">
-        <v>1413.89</v>
+        <v>1408.94</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>43.6</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1458.1</v>
+        <v>1509.1</v>
       </c>
       <c r="D3">
-        <v>-1.92</v>
+        <v>3.5</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1006,46 +1006,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-28.35</v>
+        <v>-25.85</v>
       </c>
       <c r="H3">
-        <v>2.13</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
-        <v>-0.47</v>
+        <v>3.38</v>
       </c>
       <c r="J3">
-        <v>-9.75</v>
+        <v>-7.13</v>
       </c>
       <c r="K3">
-        <v>-22.03</v>
+        <v>-18.87</v>
       </c>
       <c r="L3">
-        <v>-22.72</v>
+        <v>-20.54</v>
       </c>
       <c r="M3">
-        <v>-1.47</v>
+        <v>-0.91</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="P3">
-        <v>1454.46</v>
+        <v>1464.32</v>
       </c>
       <c r="Q3">
-        <v>1524.58</v>
+        <v>1519.18</v>
       </c>
       <c r="R3">
-        <v>1606.12</v>
+        <v>1599.77</v>
       </c>
       <c r="S3">
-        <v>1782.27</v>
+        <v>1779.92</v>
       </c>
       <c r="T3">
-        <v>-18.19</v>
+        <v>-15.22</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,34 +1060,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>32.63</v>
+        <v>44.98</v>
       </c>
       <c r="Z3">
-        <v>-48.55</v>
+        <v>-43.07</v>
       </c>
       <c r="AA3">
-        <v>-46.51</v>
+        <v>-45.82</v>
       </c>
       <c r="AB3">
-        <v>-2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AC3">
-        <v>68.58</v>
+        <v>93.14</v>
       </c>
       <c r="AD3">
-        <v>39.82</v>
+        <v>67.94</v>
       </c>
       <c r="AE3">
-        <v>32.94</v>
+        <v>34.61</v>
       </c>
       <c r="AF3">
-        <v>0.25</v>
+        <v>50.03</v>
       </c>
       <c r="AG3">
-        <v>1651</v>
+        <v>1637.98</v>
       </c>
       <c r="AH3">
-        <v>1398.16</v>
+        <v>1400.39</v>
       </c>
       <c r="AI3">
         <v>1535.77</v>
@@ -1096,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>54.55</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D4">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1119,46 +1119,46 @@
         <v>457.6</v>
       </c>
       <c r="G4">
-        <v>-28.29</v>
+        <v>-28.14</v>
       </c>
       <c r="H4">
-        <v>7.52</v>
+        <v>7.74</v>
       </c>
       <c r="I4">
-        <v>4.46</v>
+        <v>4.56</v>
       </c>
       <c r="J4">
-        <v>-1.5</v>
+        <v>-1.79</v>
       </c>
       <c r="K4">
-        <v>-1.66</v>
+        <v>-2.63</v>
       </c>
       <c r="L4">
-        <v>-18.42</v>
+        <v>-18.05</v>
       </c>
       <c r="M4">
-        <v>-6.09</v>
+        <v>-6.42</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P4">
-        <v>476.32</v>
+        <v>480.62</v>
       </c>
       <c r="Q4">
-        <v>491.2</v>
+        <v>490.1</v>
       </c>
       <c r="R4">
-        <v>500.8</v>
+        <v>500.46</v>
       </c>
       <c r="S4">
-        <v>558.5599999999999</v>
+        <v>557.95</v>
       </c>
       <c r="T4">
-        <v>-11.92</v>
+        <v>-11.64</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>51.08</v>
+        <v>51.56</v>
       </c>
       <c r="Z4">
-        <v>-7.45</v>
+        <v>-6.02</v>
       </c>
       <c r="AA4">
-        <v>-7.61</v>
+        <v>-7.29</v>
       </c>
       <c r="AB4">
-        <v>0.16</v>
+        <v>1.27</v>
       </c>
       <c r="AC4">
-        <v>63.72</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="AD4">
-        <v>41.62</v>
+        <v>62.62</v>
       </c>
       <c r="AE4">
-        <v>14.78</v>
+        <v>14.36</v>
       </c>
       <c r="AF4">
-        <v>69.13</v>
+        <v>-28.76</v>
       </c>
       <c r="AG4">
-        <v>530.52</v>
+        <v>527.8200000000001</v>
       </c>
       <c r="AH4">
-        <v>451.87</v>
+        <v>452.38</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
@@ -1209,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>30.76</v>
+        <v>30.48</v>
       </c>
     </row>
   </sheetData>
@@ -1407,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.56</v>
+        <v>-4.5</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.5</v>
+        <v>-4.74</v>
       </c>
       <c r="E7" s="6">
-        <v>0.06</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-8.44</v>
+        <v>-9.75</v>
       </c>
       <c r="D8" s="5">
-        <v>-9.75</v>
+        <v>-7.13</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.31</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-1.55</v>
+        <v>-1.5</v>
       </c>
       <c r="D9" s="5">
-        <v>-1.5</v>
+        <v>-1.79</v>
       </c>
       <c r="E9" s="6">
-        <v>0.05</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-2.99</v>
+        <v>-3.29</v>
       </c>
       <c r="D10" s="5">
-        <v>-3.29</v>
+        <v>-2.49</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>0.86</v>
+        <v>-0.47</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.47</v>
+        <v>3.38</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.33</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>6.05</v>
+        <v>4.46</v>
       </c>
       <c r="D12" s="5">
-        <v>4.46</v>
+        <v>4.56</v>
       </c>
       <c r="E12" s="7">
-        <v>-1.59</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1509,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-4.94</v>
+        <v>-5.67</v>
       </c>
       <c r="D13" s="5">
-        <v>-5.67</v>
+        <v>-5.39</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.73</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1526,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-20.93</v>
+        <v>-22.72</v>
       </c>
       <c r="D14" s="5">
-        <v>-22.72</v>
+        <v>-20.54</v>
       </c>
       <c r="E14" s="7">
-        <v>-1.79</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1543,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-18.08</v>
+        <v>-18.42</v>
       </c>
       <c r="D15" s="5">
-        <v>-18.42</v>
+        <v>-18.05</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.34</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1560,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>0.39</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D16" s="5">
-        <v>-0.5600000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.95</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1577,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-19.16</v>
+        <v>-22.03</v>
       </c>
       <c r="D17" s="5">
-        <v>-22.03</v>
+        <v>-18.87</v>
       </c>
       <c r="E17" s="7">
-        <v>-2.87</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1594,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-6.05</v>
+        <v>-1.66</v>
       </c>
       <c r="D18" s="5">
-        <v>-1.66</v>
+        <v>-2.63</v>
       </c>
       <c r="E18" s="6">
-        <v>4.39</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1611,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-7.89</v>
+        <v>-8.49</v>
       </c>
       <c r="D19" s="5">
-        <v>-8.49</v>
+        <v>-8.07</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.6</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1628,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-26.95</v>
+        <v>-28.35</v>
       </c>
       <c r="D20" s="5">
-        <v>-28.35</v>
+        <v>-25.85</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1645,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-28.51</v>
+        <v>-28.29</v>
       </c>
       <c r="D21" s="5">
-        <v>-28.29</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.22</v>
+        <v>-28.14</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.15</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1662,13 +1662,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1347.6</v>
+        <v>1338.9</v>
       </c>
       <c r="D22" s="5">
-        <v>1338.9</v>
+        <v>1345</v>
       </c>
       <c r="E22" s="7">
-        <v>-8.699999999999999</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1679,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1486.7</v>
+        <v>1458.1</v>
       </c>
       <c r="D23" s="5">
-        <v>1458.1</v>
+        <v>1509.1</v>
       </c>
       <c r="E23" s="7">
-        <v>-28.6</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1696,13 +1696,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>490.5</v>
+        <v>492</v>
       </c>
       <c r="D24" s="5">
-        <v>492</v>
-      </c>
-      <c r="E24" s="6">
-        <v>1.5</v>
+        <v>493</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1713,13 +1713,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>32.05</v>
+        <v>30.33</v>
       </c>
       <c r="D25" s="5">
-        <v>30.33</v>
+        <v>33.04</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.72</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1730,13 +1730,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>36.95</v>
+        <v>32.63</v>
       </c>
       <c r="D26" s="5">
-        <v>32.63</v>
+        <v>44.98</v>
       </c>
       <c r="E26" s="7">
-        <v>-4.32</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1747,13 +1747,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>50.39</v>
+        <v>51.08</v>
       </c>
       <c r="D27" s="5">
-        <v>51.08</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.6899999999999999</v>
+        <v>51.56</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.48</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1764,13 +1764,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-14.99</v>
+        <v>-17.82</v>
       </c>
       <c r="D28" s="5">
-        <v>-17.82</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.83</v>
+        <v>-36.63</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-18.81</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1781,13 +1781,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-20.71</v>
+        <v>0.25</v>
       </c>
       <c r="D29" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="E29" s="6">
-        <v>20.96</v>
+        <v>50.03</v>
+      </c>
+      <c r="E29" s="7">
+        <v>49.78</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1798,13 +1798,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>99.44</v>
+        <v>69.13</v>
       </c>
       <c r="D30" s="5">
-        <v>69.13</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-30.31</v>
+        <v>-28.76</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-97.89</v>
       </c>
     </row>
   </sheetData>
@@ -1869,16 +1869,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>38</v>
+        <v>43.2</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-5.2</v>
+        <v>-4.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-8.1</v>
+        <v>-7.4</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1997,13 +1997,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1424</v>
+        <v>0.1427</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0147</v>
+        <v>-0.0091</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0609</v>
+        <v>-0.06419999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.6 → 48.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.6</t>
+  </si>
+  <si>
+    <t>48.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -359,14 +386,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -881,10 +909,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1345</v>
+        <v>1339.6</v>
       </c>
       <c r="D2">
-        <v>0.46</v>
+        <v>-0.4</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -893,25 +921,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-8.07</v>
+        <v>-8.44</v>
       </c>
       <c r="H2">
-        <v>11.53</v>
+        <v>11.09</v>
       </c>
       <c r="I2">
-        <v>-2.49</v>
+        <v>-0.8</v>
       </c>
       <c r="J2">
-        <v>-4.74</v>
+        <v>-5.66</v>
       </c>
       <c r="K2">
-        <v>-0.55</v>
+        <v>0.1</v>
       </c>
       <c r="L2">
-        <v>-5.39</v>
+        <v>-5.61</v>
       </c>
       <c r="M2">
-        <v>14.27</v>
+        <v>14.45</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -920,19 +948,19 @@
         <v>54</v>
       </c>
       <c r="P2">
-        <v>1348.14</v>
+        <v>1345.98</v>
       </c>
       <c r="Q2">
-        <v>1401.29</v>
+        <v>1397.52</v>
       </c>
       <c r="R2">
-        <v>1419.16</v>
+        <v>1417.76</v>
       </c>
       <c r="S2">
-        <v>1355.33</v>
+        <v>1355.07</v>
       </c>
       <c r="T2">
-        <v>-0.76</v>
+        <v>-1.14</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +975,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>33.04</v>
+        <v>31.86</v>
       </c>
       <c r="Z2">
-        <v>-20.26</v>
+        <v>-21.47</v>
       </c>
       <c r="AA2">
-        <v>-11.89</v>
+        <v>-13.81</v>
       </c>
       <c r="AB2">
-        <v>-8.359999999999999</v>
+        <v>-7.66</v>
       </c>
       <c r="AC2">
-        <v>5.12</v>
+        <v>6.17</v>
       </c>
       <c r="AD2">
-        <v>5.29</v>
+        <v>5.55</v>
       </c>
       <c r="AE2">
-        <v>20.91</v>
+        <v>20.38</v>
       </c>
       <c r="AF2">
-        <v>-36.63</v>
+        <v>-27.56</v>
       </c>
       <c r="AG2">
-        <v>1474.82</v>
+        <v>1475.67</v>
       </c>
       <c r="AH2">
-        <v>1327.75</v>
+        <v>1319.36</v>
       </c>
       <c r="AI2">
-        <v>1408.94</v>
+        <v>1401.63</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>46.11</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1022,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1509.1</v>
+        <v>1480</v>
       </c>
       <c r="D3">
-        <v>3.5</v>
+        <v>-1.93</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1006,46 +1034,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-25.85</v>
+        <v>-27.28</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>3.66</v>
       </c>
       <c r="I3">
-        <v>3.38</v>
+        <v>3.66</v>
       </c>
       <c r="J3">
-        <v>-7.13</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="K3">
-        <v>-18.87</v>
+        <v>-19.24</v>
       </c>
       <c r="L3">
-        <v>-20.54</v>
+        <v>-20.39</v>
       </c>
       <c r="M3">
-        <v>-0.91</v>
+        <v>-1.17</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P3">
-        <v>1464.32</v>
+        <v>1474.78</v>
       </c>
       <c r="Q3">
-        <v>1519.18</v>
+        <v>1512.18</v>
       </c>
       <c r="R3">
-        <v>1599.77</v>
+        <v>1593.63</v>
       </c>
       <c r="S3">
-        <v>1779.92</v>
+        <v>1777.49</v>
       </c>
       <c r="T3">
-        <v>-15.22</v>
+        <v>-16.74</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,34 +1088,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>44.98</v>
+        <v>40.43</v>
       </c>
       <c r="Z3">
-        <v>-43.07</v>
+        <v>-40.61</v>
       </c>
       <c r="AA3">
-        <v>-45.82</v>
+        <v>-44.78</v>
       </c>
       <c r="AB3">
-        <v>2.75</v>
+        <v>4.17</v>
       </c>
       <c r="AC3">
-        <v>93.14</v>
+        <v>87.91</v>
       </c>
       <c r="AD3">
-        <v>67.94</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="AE3">
-        <v>34.61</v>
+        <v>34.55</v>
       </c>
       <c r="AF3">
-        <v>50.03</v>
+        <v>-30.11</v>
       </c>
       <c r="AG3">
-        <v>1637.98</v>
+        <v>1622.13</v>
       </c>
       <c r="AH3">
-        <v>1400.39</v>
+        <v>1402.24</v>
       </c>
       <c r="AI3">
         <v>1535.77</v>
@@ -1096,7 +1124,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>48.62</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>493</v>
+        <v>486.65</v>
       </c>
       <c r="D4">
-        <v>0.2</v>
+        <v>-1.29</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1119,46 +1147,46 @@
         <v>457.6</v>
       </c>
       <c r="G4">
-        <v>-28.14</v>
+        <v>-29.07</v>
       </c>
       <c r="H4">
-        <v>7.74</v>
+        <v>6.35</v>
       </c>
       <c r="I4">
-        <v>4.56</v>
+        <v>6.35</v>
       </c>
       <c r="J4">
-        <v>-1.79</v>
+        <v>-5.5</v>
       </c>
       <c r="K4">
-        <v>-2.63</v>
+        <v>-2.4</v>
       </c>
       <c r="L4">
-        <v>-18.05</v>
+        <v>-18.62</v>
       </c>
       <c r="M4">
-        <v>-6.42</v>
+        <v>-6.54</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P4">
-        <v>480.62</v>
+        <v>486.43</v>
       </c>
       <c r="Q4">
-        <v>490.1</v>
+        <v>488.87</v>
       </c>
       <c r="R4">
-        <v>500.46</v>
+        <v>499.8</v>
       </c>
       <c r="S4">
-        <v>557.95</v>
+        <v>557.34</v>
       </c>
       <c r="T4">
-        <v>-11.64</v>
+        <v>-12.68</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1201,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>51.56</v>
+        <v>48.31</v>
       </c>
       <c r="Z4">
-        <v>-6.02</v>
+        <v>-5.34</v>
       </c>
       <c r="AA4">
-        <v>-7.29</v>
+        <v>-6.9</v>
       </c>
       <c r="AB4">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AC4">
-        <v>84.98999999999999</v>
+        <v>87.92</v>
       </c>
       <c r="AD4">
-        <v>62.62</v>
+        <v>78.88</v>
       </c>
       <c r="AE4">
-        <v>14.36</v>
+        <v>14.18</v>
       </c>
       <c r="AF4">
-        <v>-28.76</v>
+        <v>-63.48</v>
       </c>
       <c r="AG4">
-        <v>527.8200000000001</v>
+        <v>525.26</v>
       </c>
       <c r="AH4">
-        <v>452.38</v>
+        <v>452.47</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
@@ -1209,7 +1237,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>30.48</v>
+        <v>28.32</v>
       </c>
     </row>
   </sheetData>
@@ -1370,12 +1398,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1383,428 +1446,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-4.5</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-4.74</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.24</v>
+      <c r="D7" s="6">
+        <v>-5.66</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-9.75</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-7.13</v>
       </c>
+      <c r="D8" s="6">
+        <v>-8.470000000000001</v>
+      </c>
       <c r="E8" s="7">
-        <v>2.62</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-1.5</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-1.79</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.29</v>
+      <c r="D9" s="6">
+        <v>-5.5</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.71</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-3.29</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-2.49</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.8</v>
+      <c r="D10" s="6">
+        <v>-0.8</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.69</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-0.47</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>3.38</v>
       </c>
-      <c r="E11" s="7">
-        <v>3.85</v>
+      <c r="D11" s="6">
+        <v>3.66</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>4.46</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>4.56</v>
       </c>
-      <c r="E12" s="7">
+      <c r="D12" s="6">
+        <v>6.35</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-5.39</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-5.61</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-20.54</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-20.39</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-18.05</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-18.62</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-0.55</v>
+      </c>
+      <c r="D16" s="6">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="E16" s="8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-18.87</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-19.24</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.63</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-2.4</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-5.67</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-5.39</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-8.07</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-8.44</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-22.72</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-20.54</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-25.85</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-27.28</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-18.42</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-18.05</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-28.14</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-29.07</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.55</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1345</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1339.6</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-22.03</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-18.87</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1509.1</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1480</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-29.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-1.66</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-2.63</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>493</v>
+      </c>
+      <c r="D24" s="6">
+        <v>486.65</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-6.35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-8.49</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-8.07</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>33.04</v>
+      </c>
+      <c r="D25" s="6">
+        <v>31.86</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-28.35</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-25.85</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>44.98</v>
+      </c>
+      <c r="D26" s="6">
+        <v>40.43</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-28.29</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-28.14</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>51.56</v>
+      </c>
+      <c r="D27" s="6">
+        <v>48.31</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1338.9</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1345</v>
-      </c>
-      <c r="E22" s="7">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-36.63</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-27.56</v>
+      </c>
+      <c r="E28" s="8">
+        <v>9.07</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1458.1</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1509.1</v>
-      </c>
-      <c r="E23" s="7">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>50.03</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-30.11</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-80.14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>492</v>
-      </c>
-      <c r="D24" s="5">
-        <v>493</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5">
-        <v>30.33</v>
-      </c>
-      <c r="D25" s="5">
-        <v>33.04</v>
-      </c>
-      <c r="E25" s="7">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5">
-        <v>32.63</v>
-      </c>
-      <c r="D26" s="5">
-        <v>44.98</v>
-      </c>
-      <c r="E26" s="7">
-        <v>12.35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>51.08</v>
-      </c>
-      <c r="D27" s="5">
-        <v>51.56</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-17.82</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-36.63</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-18.81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="D29" s="5">
-        <v>50.03</v>
-      </c>
-      <c r="E29" s="7">
-        <v>49.78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>69.13</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-28.76</v>
       </c>
-      <c r="E30" s="6">
-        <v>-97.89</v>
+      <c r="D30" s="6">
+        <v>-63.48</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-34.72</v>
       </c>
     </row>
   </sheetData>
@@ -1830,60 +1893,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>43.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>40.2</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-4.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-7.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-6.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1985,25 +2048,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1427</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0091</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.06419999999999999</v>
+      <c r="A2" s="14">
+        <v>0.1445</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0117</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0654</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,34 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.6 → 48.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.6</t>
-  </si>
-  <si>
-    <t>48.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -270,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -909,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1339.6</v>
+        <v>1340</v>
       </c>
       <c r="D2">
-        <v>-0.4</v>
+        <v>0.03</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -921,46 +893,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-8.44</v>
+        <v>-8.41</v>
       </c>
       <c r="H2">
-        <v>11.09</v>
+        <v>11.12</v>
       </c>
       <c r="I2">
-        <v>-0.8</v>
+        <v>-1.38</v>
       </c>
       <c r="J2">
-        <v>-5.66</v>
+        <v>-5.3</v>
       </c>
       <c r="K2">
-        <v>0.1</v>
+        <v>-2.45</v>
       </c>
       <c r="L2">
-        <v>-5.61</v>
+        <v>-5.75</v>
       </c>
       <c r="M2">
-        <v>14.45</v>
+        <v>14.02</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P2">
-        <v>1345.98</v>
+        <v>1342.22</v>
       </c>
       <c r="Q2">
-        <v>1397.52</v>
+        <v>1393.38</v>
       </c>
       <c r="R2">
-        <v>1417.76</v>
+        <v>1416.41</v>
       </c>
       <c r="S2">
-        <v>1355.07</v>
+        <v>1354.84</v>
       </c>
       <c r="T2">
-        <v>-1.14</v>
+        <v>-1.1</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,43 +947,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>31.86</v>
+        <v>32.05</v>
       </c>
       <c r="Z2">
-        <v>-21.47</v>
+        <v>-22.14</v>
       </c>
       <c r="AA2">
-        <v>-13.81</v>
+        <v>-15.48</v>
       </c>
       <c r="AB2">
-        <v>-7.66</v>
+        <v>-6.67</v>
       </c>
       <c r="AC2">
-        <v>6.17</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AD2">
-        <v>5.55</v>
+        <v>6.72</v>
       </c>
       <c r="AE2">
-        <v>20.38</v>
+        <v>19.71</v>
       </c>
       <c r="AF2">
-        <v>-27.56</v>
+        <v>-46.93</v>
       </c>
       <c r="AG2">
-        <v>1475.67</v>
+        <v>1474.62</v>
       </c>
       <c r="AH2">
-        <v>1319.36</v>
+        <v>1312.14</v>
       </c>
       <c r="AI2">
-        <v>1401.63</v>
+        <v>1398.12</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>48.89</v>
+        <v>51.32</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1480</v>
+        <v>1500.6</v>
       </c>
       <c r="D3">
-        <v>-1.93</v>
+        <v>1.39</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1034,46 +1006,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-27.28</v>
+        <v>-26.27</v>
       </c>
       <c r="H3">
-        <v>3.66</v>
+        <v>5.11</v>
       </c>
       <c r="I3">
-        <v>3.66</v>
+        <v>4.21</v>
       </c>
       <c r="J3">
-        <v>-8.470000000000001</v>
+        <v>-7.37</v>
       </c>
       <c r="K3">
-        <v>-19.24</v>
+        <v>-17.6</v>
       </c>
       <c r="L3">
-        <v>-20.39</v>
+        <v>-19.86</v>
       </c>
       <c r="M3">
-        <v>-1.17</v>
+        <v>-0.26</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P3">
-        <v>1474.78</v>
+        <v>1486.9</v>
       </c>
       <c r="Q3">
-        <v>1512.18</v>
+        <v>1506.41</v>
       </c>
       <c r="R3">
-        <v>1593.63</v>
+        <v>1587.88</v>
       </c>
       <c r="S3">
-        <v>1777.49</v>
+        <v>1775.12</v>
       </c>
       <c r="T3">
-        <v>-16.74</v>
+        <v>-15.46</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1088,34 +1060,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>40.43</v>
+        <v>44.7</v>
       </c>
       <c r="Z3">
-        <v>-40.61</v>
+        <v>-36.57</v>
       </c>
       <c r="AA3">
-        <v>-44.78</v>
+        <v>-43.14</v>
       </c>
       <c r="AB3">
-        <v>4.17</v>
+        <v>6.57</v>
       </c>
       <c r="AC3">
-        <v>87.91</v>
+        <v>94.44</v>
       </c>
       <c r="AD3">
-        <v>83.20999999999999</v>
+        <v>91.83</v>
       </c>
       <c r="AE3">
-        <v>34.55</v>
+        <v>33.87</v>
       </c>
       <c r="AF3">
-        <v>-30.11</v>
+        <v>-27.45</v>
       </c>
       <c r="AG3">
-        <v>1622.13</v>
+        <v>1604.94</v>
       </c>
       <c r="AH3">
-        <v>1402.24</v>
+        <v>1407.89</v>
       </c>
       <c r="AI3">
         <v>1535.77</v>
@@ -1124,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>43.48</v>
+        <v>39.02</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>486.65</v>
+        <v>484.5</v>
       </c>
       <c r="D4">
-        <v>-1.29</v>
+        <v>-0.44</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1147,46 +1119,46 @@
         <v>457.6</v>
       </c>
       <c r="G4">
-        <v>-29.07</v>
+        <v>-29.38</v>
       </c>
       <c r="H4">
-        <v>6.35</v>
+        <v>5.88</v>
       </c>
       <c r="I4">
-        <v>6.35</v>
+        <v>3.09</v>
       </c>
       <c r="J4">
-        <v>-5.5</v>
+        <v>-5.23</v>
       </c>
       <c r="K4">
-        <v>-2.4</v>
+        <v>-2.39</v>
       </c>
       <c r="L4">
-        <v>-18.62</v>
+        <v>-19.64</v>
       </c>
       <c r="M4">
-        <v>-6.54</v>
+        <v>-6.57</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P4">
-        <v>486.43</v>
+        <v>489.33</v>
       </c>
       <c r="Q4">
-        <v>488.87</v>
+        <v>487.59</v>
       </c>
       <c r="R4">
-        <v>499.8</v>
+        <v>499.41</v>
       </c>
       <c r="S4">
-        <v>557.34</v>
+        <v>556.7</v>
       </c>
       <c r="T4">
-        <v>-12.68</v>
+        <v>-12.97</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1201,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>48.31</v>
+        <v>47.22</v>
       </c>
       <c r="Z4">
-        <v>-5.34</v>
+        <v>-4.91</v>
       </c>
       <c r="AA4">
-        <v>-6.9</v>
+        <v>-6.5</v>
       </c>
       <c r="AB4">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC4">
-        <v>87.92</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="AD4">
-        <v>78.88</v>
+        <v>87.08</v>
       </c>
       <c r="AE4">
-        <v>14.18</v>
+        <v>13.89</v>
       </c>
       <c r="AF4">
-        <v>-63.48</v>
+        <v>-45.01</v>
       </c>
       <c r="AG4">
-        <v>525.26</v>
+        <v>522.63</v>
       </c>
       <c r="AH4">
-        <v>452.47</v>
+        <v>452.55</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
@@ -1237,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>28.32</v>
+        <v>24.85</v>
       </c>
     </row>
   </sheetData>
@@ -1398,47 +1370,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1446,428 +1383,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-4.74</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-5.66</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.92</v>
+      <c r="D7" s="5">
+        <v>-5.3</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.36</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-7.13</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-8.470000000000001</v>
       </c>
-      <c r="E8" s="7">
-        <v>-1.34</v>
+      <c r="D8" s="5">
+        <v>-7.37</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-1.79</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-5.5</v>
       </c>
-      <c r="E9" s="7">
-        <v>-3.71</v>
+      <c r="D9" s="5">
+        <v>-5.23</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.27</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-2.49</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-0.8</v>
       </c>
-      <c r="E10" s="8">
-        <v>1.69</v>
+      <c r="D10" s="5">
+        <v>-1.38</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>3.38</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>3.66</v>
       </c>
-      <c r="E11" s="8">
-        <v>0.28</v>
+      <c r="D11" s="5">
+        <v>4.21</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>4.56</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>6.35</v>
       </c>
-      <c r="E12" s="8">
-        <v>1.79</v>
+      <c r="D12" s="5">
+        <v>3.09</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-3.26</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-5.39</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-5.61</v>
       </c>
+      <c r="D13" s="5">
+        <v>-5.75</v>
+      </c>
       <c r="E13" s="7">
-        <v>-0.22</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-20.54</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-20.39</v>
       </c>
-      <c r="E14" s="8">
-        <v>0.15</v>
+      <c r="D14" s="5">
+        <v>-19.86</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.53</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-18.05</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-18.62</v>
       </c>
+      <c r="D15" s="5">
+        <v>-19.64</v>
+      </c>
       <c r="E15" s="7">
-        <v>-0.57</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-0.55</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>0.1</v>
       </c>
-      <c r="E16" s="8">
-        <v>0.65</v>
+      <c r="D16" s="5">
+        <v>-2.45</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.55</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-18.87</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-19.24</v>
       </c>
-      <c r="E17" s="7">
-        <v>-0.37</v>
+      <c r="D17" s="5">
+        <v>-17.6</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.64</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-2.63</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-2.4</v>
       </c>
-      <c r="E18" s="8">
-        <v>0.23</v>
+      <c r="D18" s="5">
+        <v>-2.39</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.01</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-8.07</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-8.44</v>
       </c>
-      <c r="E19" s="7">
-        <v>-0.37</v>
+      <c r="D19" s="5">
+        <v>-8.41</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.03</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-25.85</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-27.28</v>
       </c>
-      <c r="E20" s="7">
-        <v>-1.43</v>
+      <c r="D20" s="5">
+        <v>-26.27</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.01</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-28.14</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-29.07</v>
       </c>
+      <c r="D21" s="5">
+        <v>-29.38</v>
+      </c>
       <c r="E21" s="7">
-        <v>-0.93</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>1345</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>1339.6</v>
       </c>
-      <c r="E22" s="7">
-        <v>-5.4</v>
+      <c r="D22" s="5">
+        <v>1340</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>1509.1</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>1480</v>
       </c>
-      <c r="E23" s="7">
-        <v>-29.1</v>
+      <c r="D23" s="5">
+        <v>1500.6</v>
+      </c>
+      <c r="E23" s="6">
+        <v>20.6</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>493</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>486.65</v>
       </c>
+      <c r="D24" s="5">
+        <v>484.5</v>
+      </c>
       <c r="E24" s="7">
-        <v>-6.35</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>33.04</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>31.86</v>
       </c>
-      <c r="E25" s="7">
-        <v>-1.18</v>
+      <c r="D25" s="5">
+        <v>32.05</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.19</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>44.98</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>40.43</v>
       </c>
-      <c r="E26" s="7">
-        <v>-4.55</v>
+      <c r="D26" s="5">
+        <v>44.7</v>
+      </c>
+      <c r="E26" s="6">
+        <v>4.27</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>51.56</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>48.31</v>
       </c>
+      <c r="D27" s="5">
+        <v>47.22</v>
+      </c>
       <c r="E27" s="7">
-        <v>-3.25</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>-36.63</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>-27.56</v>
       </c>
-      <c r="E28" s="8">
-        <v>9.07</v>
+      <c r="D28" s="5">
+        <v>-46.93</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-19.37</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>50.03</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>-30.11</v>
       </c>
-      <c r="E29" s="7">
-        <v>-80.14</v>
+      <c r="D29" s="5">
+        <v>-27.45</v>
+      </c>
+      <c r="E29" s="6">
+        <v>2.66</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-28.76</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-63.48</v>
       </c>
-      <c r="E30" s="7">
-        <v>-34.72</v>
+      <c r="D30" s="5">
+        <v>-45.01</v>
+      </c>
+      <c r="E30" s="6">
+        <v>18.47</v>
       </c>
     </row>
   </sheetData>
@@ -1893,60 +1830,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>40.2</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>41.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-7.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2048,25 +1985,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1445</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0117</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0654</v>
+      <c r="A2" s="13">
+        <v>0.1402</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0026</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.06570000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -154,10 +154,40 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>44.7 → 57.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>44.7</t>
+  </si>
+  <si>
+    <t>57.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -359,17 +389,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -881,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1340</v>
+        <v>1334.5</v>
       </c>
       <c r="D2">
-        <v>0.03</v>
+        <v>-0.41</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -893,25 +924,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-8.41</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="H2">
-        <v>11.12</v>
+        <v>10.66</v>
       </c>
       <c r="I2">
-        <v>-1.38</v>
+        <v>-0.97</v>
       </c>
       <c r="J2">
-        <v>-5.3</v>
+        <v>-6.2</v>
       </c>
       <c r="K2">
-        <v>-2.45</v>
+        <v>-3.82</v>
       </c>
       <c r="L2">
-        <v>-5.75</v>
+        <v>-4.83</v>
       </c>
       <c r="M2">
-        <v>14.02</v>
+        <v>13.73</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -920,19 +951,19 @@
         <v>51</v>
       </c>
       <c r="P2">
-        <v>1342.22</v>
+        <v>1339.6</v>
       </c>
       <c r="Q2">
-        <v>1393.38</v>
+        <v>1388.61</v>
       </c>
       <c r="R2">
-        <v>1416.41</v>
+        <v>1414.78</v>
       </c>
       <c r="S2">
-        <v>1354.84</v>
+        <v>1354.55</v>
       </c>
       <c r="T2">
-        <v>-1.1</v>
+        <v>-1.48</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +978,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>32.05</v>
+        <v>30.76</v>
       </c>
       <c r="Z2">
-        <v>-22.14</v>
+        <v>-22.86</v>
       </c>
       <c r="AA2">
-        <v>-15.48</v>
+        <v>-16.95</v>
       </c>
       <c r="AB2">
-        <v>-6.67</v>
+        <v>-5.91</v>
       </c>
       <c r="AC2">
-        <v>8.859999999999999</v>
+        <v>5.78</v>
       </c>
       <c r="AD2">
-        <v>6.72</v>
+        <v>6.94</v>
       </c>
       <c r="AE2">
-        <v>19.71</v>
+        <v>19.56</v>
       </c>
       <c r="AF2">
-        <v>-46.93</v>
+        <v>-3.19</v>
       </c>
       <c r="AG2">
-        <v>1474.62</v>
+        <v>1471.98</v>
       </c>
       <c r="AH2">
-        <v>1312.14</v>
+        <v>1305.23</v>
       </c>
       <c r="AI2">
-        <v>1398.12</v>
+        <v>1397.64</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>51.32</v>
+        <v>53.76</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1500.6</v>
+        <v>1577</v>
       </c>
       <c r="D3">
-        <v>1.39</v>
+        <v>5.09</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1006,46 +1037,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-26.27</v>
+        <v>-22.51</v>
       </c>
       <c r="H3">
-        <v>5.11</v>
+        <v>10.46</v>
       </c>
       <c r="I3">
-        <v>4.21</v>
+        <v>6.07</v>
       </c>
       <c r="J3">
-        <v>-7.37</v>
+        <v>-2.41</v>
       </c>
       <c r="K3">
-        <v>-17.6</v>
+        <v>-13.05</v>
       </c>
       <c r="L3">
-        <v>-19.86</v>
+        <v>-14.89</v>
       </c>
       <c r="M3">
-        <v>-0.26</v>
+        <v>0.6</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O3">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="P3">
-        <v>1486.9</v>
+        <v>1504.96</v>
       </c>
       <c r="Q3">
-        <v>1506.41</v>
+        <v>1505.42</v>
       </c>
       <c r="R3">
-        <v>1587.88</v>
+        <v>1583.13</v>
       </c>
       <c r="S3">
-        <v>1775.12</v>
+        <v>1773.17</v>
       </c>
       <c r="T3">
-        <v>-15.46</v>
+        <v>-11.06</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1091,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>44.7</v>
+        <v>57.01</v>
       </c>
       <c r="Z3">
-        <v>-36.57</v>
+        <v>-26.89</v>
       </c>
       <c r="AA3">
-        <v>-43.14</v>
+        <v>-39.89</v>
       </c>
       <c r="AB3">
-        <v>6.57</v>
+        <v>12.99</v>
       </c>
       <c r="AC3">
         <v>94.44</v>
       </c>
       <c r="AD3">
-        <v>91.83</v>
+        <v>92.27</v>
       </c>
       <c r="AE3">
-        <v>33.87</v>
+        <v>39.9</v>
       </c>
       <c r="AF3">
-        <v>-27.45</v>
+        <v>179.56</v>
       </c>
       <c r="AG3">
-        <v>1604.94</v>
+        <v>1600.44</v>
       </c>
       <c r="AH3">
-        <v>1407.89</v>
+        <v>1410.4</v>
       </c>
       <c r="AI3">
-        <v>1535.77</v>
+        <v>1422.11</v>
       </c>
       <c r="AJ3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AK3">
-        <v>39.02</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>484.5</v>
+        <v>464.5</v>
       </c>
       <c r="D4">
-        <v>-0.44</v>
+        <v>-4.13</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1119,46 +1150,46 @@
         <v>457.6</v>
       </c>
       <c r="G4">
-        <v>-29.38</v>
+        <v>-32.3</v>
       </c>
       <c r="H4">
-        <v>5.88</v>
+        <v>1.51</v>
       </c>
       <c r="I4">
-        <v>3.09</v>
+        <v>-5.3</v>
       </c>
       <c r="J4">
-        <v>-5.23</v>
+        <v>-8.92</v>
       </c>
       <c r="K4">
-        <v>-2.39</v>
+        <v>-5.41</v>
       </c>
       <c r="L4">
-        <v>-19.64</v>
+        <v>-22.64</v>
       </c>
       <c r="M4">
-        <v>-6.57</v>
+        <v>-7.02</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O4">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="P4">
-        <v>489.33</v>
+        <v>484.13</v>
       </c>
       <c r="Q4">
-        <v>487.59</v>
+        <v>485.06</v>
       </c>
       <c r="R4">
-        <v>499.41</v>
+        <v>498.19</v>
       </c>
       <c r="S4">
-        <v>556.7</v>
+        <v>555.9</v>
       </c>
       <c r="T4">
-        <v>-12.97</v>
+        <v>-16.44</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1204,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>47.22</v>
+        <v>38.54</v>
       </c>
       <c r="Z4">
-        <v>-4.91</v>
+        <v>-6.12</v>
       </c>
       <c r="AA4">
-        <v>-6.5</v>
+        <v>-6.43</v>
       </c>
       <c r="AB4">
-        <v>1.59</v>
+        <v>0.31</v>
       </c>
       <c r="AC4">
-        <v>88.31999999999999</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="AD4">
-        <v>87.08</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="AE4">
-        <v>13.89</v>
+        <v>15.69</v>
       </c>
       <c r="AF4">
-        <v>-45.01</v>
+        <v>469.2</v>
       </c>
       <c r="AG4">
-        <v>522.63</v>
+        <v>519.04</v>
       </c>
       <c r="AH4">
-        <v>452.55</v>
+        <v>451.09</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
@@ -1209,7 +1240,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>24.85</v>
+        <v>27.92</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1360,7 +1391,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1370,12 +1401,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1383,428 +1449,462 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-5.66</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-5.3</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.36</v>
+      <c r="D7" s="6">
+        <v>-6.2</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-8.470000000000001</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-7.37</v>
       </c>
-      <c r="E8" s="6">
-        <v>1.1</v>
+      <c r="D8" s="6">
+        <v>-2.41</v>
+      </c>
+      <c r="E8" s="8">
+        <v>4.96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
+        <v>-5.23</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-8.92</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-1.38</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-0.97</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>4.21</v>
+      </c>
+      <c r="D11" s="6">
+        <v>6.07</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3.09</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-5.3</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-8.390000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-5.75</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-4.83</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-19.86</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-14.89</v>
+      </c>
+      <c r="E14" s="8">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-19.64</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-22.64</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-2.45</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.82</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-17.6</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-13.05</v>
+      </c>
+      <c r="E17" s="8">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.39</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-5.41</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-3.02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-8.41</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-26.27</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-22.51</v>
+      </c>
+      <c r="E20" s="8">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-29.38</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-32.3</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1340</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1334.5</v>
+      </c>
+      <c r="E22" s="7">
         <v>-5.5</v>
       </c>
-      <c r="D9" s="5">
-        <v>-5.23</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1500.6</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1577</v>
+      </c>
+      <c r="E23" s="8">
+        <v>76.40000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>484.5</v>
+      </c>
+      <c r="D24" s="6">
+        <v>464.5</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="6">
+        <v>34</v>
+      </c>
+      <c r="D25" s="6">
+        <v>66</v>
+      </c>
+      <c r="E25" s="8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="6">
+        <v>66</v>
+      </c>
+      <c r="D26" s="6">
+        <v>34</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-0.8</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-1.38</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>32.05</v>
+      </c>
+      <c r="D27" s="6">
+        <v>30.76</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>3.66</v>
-      </c>
-      <c r="D11" s="5">
-        <v>4.21</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="6">
+        <v>44.7</v>
+      </c>
+      <c r="D28" s="6">
+        <v>57.01</v>
+      </c>
+      <c r="E28" s="8">
+        <v>12.31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>6.35</v>
-      </c>
-      <c r="D12" s="5">
-        <v>3.09</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="6">
+        <v>47.22</v>
+      </c>
+      <c r="D29" s="6">
+        <v>38.54</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-8.68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-5.61</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-5.75</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-46.93</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-3.19</v>
+      </c>
+      <c r="E30" s="8">
+        <v>43.74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-20.39</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-19.86</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-27.45</v>
+      </c>
+      <c r="D31" s="6">
+        <v>179.56</v>
+      </c>
+      <c r="E31" s="8">
+        <v>207.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-18.62</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-19.64</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-2.45</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-19.24</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-17.6</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-2.4</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-2.39</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-8.44</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-8.41</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-27.28</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-26.27</v>
-      </c>
-      <c r="E20" s="6">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-29.07</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-29.38</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1339.6</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1340</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1480</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1500.6</v>
-      </c>
-      <c r="E23" s="6">
-        <v>20.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>486.65</v>
-      </c>
-      <c r="D24" s="5">
-        <v>484.5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5">
-        <v>31.86</v>
-      </c>
-      <c r="D25" s="5">
-        <v>32.05</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5">
-        <v>40.43</v>
-      </c>
-      <c r="D26" s="5">
-        <v>44.7</v>
-      </c>
-      <c r="E26" s="6">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>48.31</v>
-      </c>
-      <c r="D27" s="5">
-        <v>47.22</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-27.56</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-46.93</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-19.37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-30.11</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-27.45</v>
-      </c>
-      <c r="E29" s="6">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-63.48</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C32" s="6">
         <v>-45.01</v>
       </c>
-      <c r="E30" s="6">
-        <v>18.47</v>
+      <c r="D32" s="6">
+        <v>469.2</v>
+      </c>
+      <c r="E32" s="8">
+        <v>514.21</v>
       </c>
     </row>
   </sheetData>
@@ -1830,60 +1930,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>41.3</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>42.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-7.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-5.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1985,25 +2085,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1402</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0026</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.06570000000000001</v>
+      <c r="A2" s="14">
+        <v>0.1373</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.006</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0702</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>44.7 → 57.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>44.7</t>
-  </si>
-  <si>
-    <t>57.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,18 +362,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -772,7 +744,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -912,10 +886,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1334.5</v>
+        <v>1326.8</v>
       </c>
       <c r="D2">
-        <v>-0.41</v>
+        <v>-0.58</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,46 +898,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-8.789999999999999</v>
+        <v>-9.32</v>
       </c>
       <c r="H2">
-        <v>10.66</v>
+        <v>10.03</v>
       </c>
       <c r="I2">
-        <v>-0.97</v>
+        <v>-0.9</v>
       </c>
       <c r="J2">
-        <v>-6.2</v>
+        <v>-7.22</v>
       </c>
       <c r="K2">
-        <v>-3.82</v>
+        <v>-4.38</v>
       </c>
       <c r="L2">
-        <v>-4.83</v>
+        <v>-5.33</v>
       </c>
       <c r="M2">
-        <v>13.73</v>
+        <v>13.4</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P2">
-        <v>1339.6</v>
+        <v>1337.18</v>
       </c>
       <c r="Q2">
-        <v>1388.61</v>
+        <v>1382.8</v>
       </c>
       <c r="R2">
-        <v>1414.78</v>
+        <v>1412.95</v>
       </c>
       <c r="S2">
-        <v>1354.55</v>
+        <v>1354.23</v>
       </c>
       <c r="T2">
-        <v>-1.48</v>
+        <v>-2.03</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,43 +952,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>30.76</v>
+        <v>29</v>
       </c>
       <c r="Z2">
-        <v>-22.86</v>
+        <v>-23.77</v>
       </c>
       <c r="AA2">
-        <v>-16.95</v>
+        <v>-18.32</v>
       </c>
       <c r="AB2">
-        <v>-5.91</v>
+        <v>-5.46</v>
       </c>
       <c r="AC2">
-        <v>5.78</v>
+        <v>3.39</v>
       </c>
       <c r="AD2">
-        <v>6.94</v>
+        <v>6.01</v>
       </c>
       <c r="AE2">
-        <v>19.56</v>
+        <v>20.22</v>
       </c>
       <c r="AF2">
-        <v>-3.19</v>
+        <v>20.85</v>
       </c>
       <c r="AG2">
-        <v>1471.98</v>
+        <v>1466.4</v>
       </c>
       <c r="AH2">
-        <v>1305.23</v>
+        <v>1299.19</v>
       </c>
       <c r="AI2">
-        <v>1397.64</v>
+        <v>1387.07</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>53.76</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +999,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1577</v>
+        <v>1553.7</v>
       </c>
       <c r="D3">
-        <v>5.09</v>
+        <v>-1.48</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1037,46 +1011,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-22.51</v>
+        <v>-23.66</v>
       </c>
       <c r="H3">
-        <v>10.46</v>
+        <v>8.83</v>
       </c>
       <c r="I3">
-        <v>6.07</v>
+        <v>6.56</v>
       </c>
       <c r="J3">
-        <v>-2.41</v>
+        <v>-2.71</v>
       </c>
       <c r="K3">
-        <v>-13.05</v>
+        <v>-12.13</v>
       </c>
       <c r="L3">
-        <v>-14.89</v>
+        <v>-17.05</v>
       </c>
       <c r="M3">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P3">
-        <v>1504.96</v>
+        <v>1524.08</v>
       </c>
       <c r="Q3">
-        <v>1505.42</v>
+        <v>1503.7</v>
       </c>
       <c r="R3">
-        <v>1583.13</v>
+        <v>1581.72</v>
       </c>
       <c r="S3">
-        <v>1773.17</v>
+        <v>1771.17</v>
       </c>
       <c r="T3">
-        <v>-11.06</v>
+        <v>-12.28</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1091,43 +1065,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>57.01</v>
+        <v>53.12</v>
       </c>
       <c r="Z3">
-        <v>-26.89</v>
+        <v>-20.87</v>
       </c>
       <c r="AA3">
-        <v>-39.89</v>
+        <v>-36.08</v>
       </c>
       <c r="AB3">
-        <v>12.99</v>
+        <v>15.22</v>
       </c>
       <c r="AC3">
-        <v>94.44</v>
+        <v>96.52</v>
       </c>
       <c r="AD3">
-        <v>92.27</v>
+        <v>95.13</v>
       </c>
       <c r="AE3">
-        <v>39.9</v>
+        <v>39.63</v>
       </c>
       <c r="AF3">
-        <v>179.56</v>
+        <v>-21.19</v>
       </c>
       <c r="AG3">
-        <v>1600.44</v>
+        <v>1593.52</v>
       </c>
       <c r="AH3">
-        <v>1410.4</v>
+        <v>1413.88</v>
       </c>
       <c r="AI3">
-        <v>1422.11</v>
+        <v>1449.16</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>41.32</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1112,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>464.5</v>
+        <v>463</v>
       </c>
       <c r="D4">
-        <v>-4.13</v>
+        <v>-0.32</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,46 +1124,46 @@
         <v>457.6</v>
       </c>
       <c r="G4">
-        <v>-32.3</v>
+        <v>-32.51</v>
       </c>
       <c r="H4">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="I4">
-        <v>-5.3</v>
+        <v>-5.89</v>
       </c>
       <c r="J4">
-        <v>-8.92</v>
+        <v>-10.11</v>
       </c>
       <c r="K4">
         <v>-5.41</v>
       </c>
       <c r="L4">
-        <v>-22.64</v>
+        <v>-23.77</v>
       </c>
       <c r="M4">
-        <v>-7.02</v>
+        <v>-6.81</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P4">
-        <v>484.13</v>
+        <v>478.33</v>
       </c>
       <c r="Q4">
-        <v>485.06</v>
+        <v>482.71</v>
       </c>
       <c r="R4">
-        <v>498.19</v>
+        <v>497.28</v>
       </c>
       <c r="S4">
-        <v>555.9</v>
+        <v>555.14</v>
       </c>
       <c r="T4">
-        <v>-16.44</v>
+        <v>-16.6</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,34 +1178,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.54</v>
+        <v>37.97</v>
       </c>
       <c r="Z4">
-        <v>-6.12</v>
+        <v>-7.12</v>
       </c>
       <c r="AA4">
-        <v>-6.43</v>
+        <v>-6.57</v>
       </c>
       <c r="AB4">
-        <v>0.31</v>
+        <v>-0.55</v>
       </c>
       <c r="AC4">
-        <v>68.29000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="AD4">
-        <v>81.51000000000001</v>
+        <v>69.67</v>
       </c>
       <c r="AE4">
-        <v>15.69</v>
+        <v>15.34</v>
       </c>
       <c r="AF4">
-        <v>469.2</v>
+        <v>-33.57</v>
       </c>
       <c r="AG4">
-        <v>519.04</v>
+        <v>515.92</v>
       </c>
       <c r="AH4">
-        <v>451.09</v>
+        <v>449.51</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
@@ -1240,7 +1214,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>27.92</v>
+        <v>30.58</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1401,47 +1375,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1449,462 +1388,411 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
+        <v>-6.2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-7.22</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-2.41</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-2.71</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-8.92</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-10.11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-0.97</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-0.9</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>6.07</v>
+      </c>
+      <c r="D11" s="5">
+        <v>6.56</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
         <v>-5.3</v>
       </c>
-      <c r="D7" s="6">
-        <v>-6.2</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D12" s="5">
+        <v>-5.89</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-4.83</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-5.33</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-7.37</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-2.41</v>
-      </c>
-      <c r="E8" s="8">
-        <v>4.96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-14.89</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-17.05</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-5.23</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-8.92</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-3.69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-22.64</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-23.77</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-1.38</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-0.97</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-3.82</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-4.38</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>4.21</v>
-      </c>
-      <c r="D11" s="6">
-        <v>6.07</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-13.05</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-12.13</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-9.32</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-22.51</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-23.66</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>3.09</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-5.3</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-8.390000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-32.3</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-32.51</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-5.75</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-4.83</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1334.5</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1326.8</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-7.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-19.86</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-14.89</v>
-      </c>
-      <c r="E14" s="8">
-        <v>4.97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1577</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1553.7</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-23.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-19.64</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-22.64</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>464.5</v>
+      </c>
+      <c r="D23" s="5">
+        <v>463</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-2.45</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.82</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="5">
+        <v>30.76</v>
+      </c>
+      <c r="D24" s="5">
+        <v>29</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-17.6</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-13.05</v>
-      </c>
-      <c r="E17" s="8">
-        <v>4.55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>57.01</v>
+      </c>
+      <c r="D25" s="5">
+        <v>53.12</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-3.89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-2.39</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-5.41</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-3.02</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>38.54</v>
+      </c>
+      <c r="D26" s="5">
+        <v>37.97</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-8.41</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-3.19</v>
+      </c>
+      <c r="D27" s="5">
+        <v>20.85</v>
+      </c>
+      <c r="E27" s="7">
+        <v>24.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-26.27</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-22.51</v>
-      </c>
-      <c r="E20" s="8">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>179.56</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-21.19</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-200.75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-29.38</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-32.3</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.92</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1340</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1334.5</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1500.6</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1577</v>
-      </c>
-      <c r="E23" s="8">
-        <v>76.40000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>484.5</v>
-      </c>
-      <c r="D24" s="6">
-        <v>464.5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="6">
-        <v>34</v>
-      </c>
-      <c r="D25" s="6">
-        <v>66</v>
-      </c>
-      <c r="E25" s="8">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="6">
-        <v>66</v>
-      </c>
-      <c r="D26" s="6">
-        <v>34</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>32.05</v>
-      </c>
-      <c r="D27" s="6">
-        <v>30.76</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>44.7</v>
-      </c>
-      <c r="D28" s="6">
-        <v>57.01</v>
-      </c>
-      <c r="E28" s="8">
-        <v>12.31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="6">
-        <v>47.22</v>
-      </c>
-      <c r="D29" s="6">
-        <v>38.54</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-8.68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-46.93</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-3.19</v>
-      </c>
-      <c r="E30" s="8">
-        <v>43.74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-27.45</v>
-      </c>
-      <c r="D31" s="6">
-        <v>179.56</v>
-      </c>
-      <c r="E31" s="8">
-        <v>207.01</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-45.01</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C29" s="5">
         <v>469.2</v>
       </c>
-      <c r="E32" s="8">
-        <v>514.21</v>
+      <c r="D29" s="5">
+        <v>-33.57</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-502.77</v>
       </c>
     </row>
   </sheetData>
@@ -1930,60 +1818,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>42.1</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>40</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-7.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-6.7</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.3</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2085,25 +1973,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1373</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.006</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0702</v>
+      <c r="A2" s="13">
+        <v>0.134</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.06809999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -744,9 +744,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -886,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1326.8</v>
+        <v>1302</v>
       </c>
       <c r="D2">
-        <v>-0.58</v>
+        <v>-1.87</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -898,25 +896,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-9.32</v>
+        <v>-11.01</v>
       </c>
       <c r="H2">
-        <v>10.03</v>
+        <v>7.97</v>
       </c>
       <c r="I2">
-        <v>-0.9</v>
+        <v>-3.2</v>
       </c>
       <c r="J2">
-        <v>-7.22</v>
+        <v>-9.77</v>
       </c>
       <c r="K2">
-        <v>-4.38</v>
+        <v>-5.32</v>
       </c>
       <c r="L2">
-        <v>-5.33</v>
+        <v>-6.62</v>
       </c>
       <c r="M2">
-        <v>13.4</v>
+        <v>13.36</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -925,19 +923,19 @@
         <v>49</v>
       </c>
       <c r="P2">
-        <v>1337.18</v>
+        <v>1328.58</v>
       </c>
       <c r="Q2">
-        <v>1382.8</v>
+        <v>1376.76</v>
       </c>
       <c r="R2">
-        <v>1412.95</v>
+        <v>1410.1</v>
       </c>
       <c r="S2">
-        <v>1354.23</v>
+        <v>1353.87</v>
       </c>
       <c r="T2">
-        <v>-2.03</v>
+        <v>-3.83</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -952,43 +950,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>29</v>
+        <v>24.19</v>
       </c>
       <c r="Z2">
-        <v>-23.77</v>
+        <v>-26.19</v>
       </c>
       <c r="AA2">
-        <v>-18.32</v>
+        <v>-19.89</v>
       </c>
       <c r="AB2">
-        <v>-5.46</v>
+        <v>-6.3</v>
       </c>
       <c r="AC2">
-        <v>3.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AD2">
-        <v>6.01</v>
+        <v>3.29</v>
       </c>
       <c r="AE2">
-        <v>20.22</v>
+        <v>20.69</v>
       </c>
       <c r="AF2">
-        <v>20.85</v>
+        <v>-31.88</v>
       </c>
       <c r="AG2">
-        <v>1466.4</v>
+        <v>1465.49</v>
       </c>
       <c r="AH2">
-        <v>1299.19</v>
+        <v>1288.02</v>
       </c>
       <c r="AI2">
-        <v>1387.07</v>
+        <v>1373.98</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>57.17</v>
+        <v>60.66</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -999,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1553.7</v>
+        <v>1540</v>
       </c>
       <c r="D3">
-        <v>-1.48</v>
+        <v>-0.88</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1011,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-23.66</v>
+        <v>-24.33</v>
       </c>
       <c r="H3">
-        <v>8.83</v>
+        <v>7.87</v>
       </c>
       <c r="I3">
-        <v>6.56</v>
+        <v>2.05</v>
       </c>
       <c r="J3">
-        <v>-2.71</v>
+        <v>-3.03</v>
       </c>
       <c r="K3">
-        <v>-12.13</v>
+        <v>-11.58</v>
       </c>
       <c r="L3">
-        <v>-17.05</v>
+        <v>-18.15</v>
       </c>
       <c r="M3">
-        <v>0.5600000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P3">
-        <v>1524.08</v>
+        <v>1530.26</v>
       </c>
       <c r="Q3">
-        <v>1503.7</v>
+        <v>1502.6</v>
       </c>
       <c r="R3">
-        <v>1581.72</v>
+        <v>1580.28</v>
       </c>
       <c r="S3">
-        <v>1771.17</v>
+        <v>1769.18</v>
       </c>
       <c r="T3">
-        <v>-12.28</v>
+        <v>-12.95</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1065,34 +1063,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>53.12</v>
+        <v>50.93</v>
       </c>
       <c r="Z3">
-        <v>-20.87</v>
+        <v>-17</v>
       </c>
       <c r="AA3">
-        <v>-36.08</v>
+        <v>-32.27</v>
       </c>
       <c r="AB3">
-        <v>15.22</v>
+        <v>15.27</v>
       </c>
       <c r="AC3">
-        <v>96.52</v>
+        <v>91.91</v>
       </c>
       <c r="AD3">
-        <v>95.13</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="AE3">
-        <v>39.63</v>
+        <v>39.16</v>
       </c>
       <c r="AF3">
-        <v>-21.19</v>
+        <v>-46.67</v>
       </c>
       <c r="AG3">
-        <v>1593.52</v>
+        <v>1589.92</v>
       </c>
       <c r="AH3">
-        <v>1413.88</v>
+        <v>1415.28</v>
       </c>
       <c r="AI3">
         <v>1449.16</v>
@@ -1101,7 +1099,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>43.4</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1112,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>463</v>
+        <v>458.7</v>
       </c>
       <c r="D4">
-        <v>-0.32</v>
+        <v>-0.93</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1124,46 +1122,46 @@
         <v>457.6</v>
       </c>
       <c r="G4">
-        <v>-32.51</v>
+        <v>-33.14</v>
       </c>
       <c r="H4">
-        <v>1.18</v>
+        <v>0.24</v>
       </c>
       <c r="I4">
-        <v>-5.89</v>
+        <v>-6.96</v>
       </c>
       <c r="J4">
-        <v>-10.11</v>
+        <v>-10.06</v>
       </c>
       <c r="K4">
-        <v>-5.41</v>
+        <v>-5.99</v>
       </c>
       <c r="L4">
-        <v>-23.77</v>
+        <v>-23.39</v>
       </c>
       <c r="M4">
-        <v>-6.81</v>
+        <v>-6.99</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P4">
-        <v>478.33</v>
+        <v>471.47</v>
       </c>
       <c r="Q4">
-        <v>482.71</v>
+        <v>480.35</v>
       </c>
       <c r="R4">
-        <v>497.28</v>
+        <v>496.51</v>
       </c>
       <c r="S4">
-        <v>555.14</v>
+        <v>554.33</v>
       </c>
       <c r="T4">
-        <v>-16.6</v>
+        <v>-17.25</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1178,34 +1176,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.97</v>
+        <v>36.33</v>
       </c>
       <c r="Z4">
-        <v>-7.12</v>
+        <v>-8.16</v>
       </c>
       <c r="AA4">
-        <v>-6.57</v>
+        <v>-6.88</v>
       </c>
       <c r="AB4">
-        <v>-0.55</v>
+        <v>-1.27</v>
       </c>
       <c r="AC4">
-        <v>52.4</v>
+        <v>35.65</v>
       </c>
       <c r="AD4">
-        <v>69.67</v>
+        <v>52.11</v>
       </c>
       <c r="AE4">
-        <v>15.34</v>
+        <v>15.22</v>
       </c>
       <c r="AF4">
-        <v>-33.57</v>
+        <v>-19.61</v>
       </c>
       <c r="AG4">
-        <v>515.92</v>
+        <v>513.3099999999999</v>
       </c>
       <c r="AH4">
-        <v>449.51</v>
+        <v>447.39</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
@@ -1214,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>30.58</v>
+        <v>33.72</v>
       </c>
     </row>
   </sheetData>
@@ -1355,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1412,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.2</v>
+        <v>-7.22</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.22</v>
+        <v>-9.77</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.02</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1429,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.41</v>
+        <v>-2.71</v>
       </c>
       <c r="D8" s="5">
-        <v>-2.71</v>
+        <v>-3.03</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1446,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-8.92</v>
+        <v>-10.11</v>
       </c>
       <c r="D9" s="5">
-        <v>-10.11</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1.19</v>
+        <v>-10.06</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.05</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1463,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-0.97</v>
+        <v>-0.9</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.9</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.07000000000000001</v>
+        <v>-3.2</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.3</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1480,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>6.07</v>
+        <v>6.56</v>
       </c>
       <c r="D11" s="5">
-        <v>6.56</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.49</v>
+        <v>2.05</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-4.51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1497,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.3</v>
+        <v>-5.89</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.89</v>
+        <v>-6.96</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.59</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1514,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-4.83</v>
+        <v>-5.33</v>
       </c>
       <c r="D13" s="5">
-        <v>-5.33</v>
+        <v>-6.62</v>
       </c>
       <c r="E13" s="6">
-        <v>-0.5</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1531,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-14.89</v>
+        <v>-17.05</v>
       </c>
       <c r="D14" s="5">
-        <v>-17.05</v>
+        <v>-18.15</v>
       </c>
       <c r="E14" s="6">
-        <v>-2.16</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1548,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-22.64</v>
+        <v>-23.77</v>
       </c>
       <c r="D15" s="5">
-        <v>-23.77</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-1.13</v>
+        <v>-23.39</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.38</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1565,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-3.82</v>
+        <v>-4.38</v>
       </c>
       <c r="D16" s="5">
-        <v>-4.38</v>
+        <v>-5.32</v>
       </c>
       <c r="E16" s="6">
-        <v>-0.5600000000000001</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1582,217 +1580,234 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-13.05</v>
+        <v>-12.13</v>
       </c>
       <c r="D17" s="5">
-        <v>-12.13</v>
+        <v>-11.58</v>
       </c>
       <c r="E17" s="7">
-        <v>0.92</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-8.789999999999999</v>
+        <v>-5.41</v>
       </c>
       <c r="D18" s="5">
-        <v>-9.32</v>
+        <v>-5.99</v>
       </c>
       <c r="E18" s="6">
-        <v>-0.53</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-22.51</v>
+        <v>-9.32</v>
       </c>
       <c r="D19" s="5">
-        <v>-23.66</v>
+        <v>-11.01</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.15</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-32.3</v>
+        <v>-23.66</v>
       </c>
       <c r="D20" s="5">
-        <v>-32.51</v>
+        <v>-24.33</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.21</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>1334.5</v>
+        <v>-32.51</v>
       </c>
       <c r="D21" s="5">
-        <v>1326.8</v>
+        <v>-33.14</v>
       </c>
       <c r="E21" s="6">
-        <v>-7.7</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1577</v>
+        <v>1326.8</v>
       </c>
       <c r="D22" s="5">
-        <v>1553.7</v>
+        <v>1302</v>
       </c>
       <c r="E22" s="6">
-        <v>-23.3</v>
+        <v>-24.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>464.5</v>
+        <v>1553.7</v>
       </c>
       <c r="D23" s="5">
-        <v>463</v>
+        <v>1540</v>
       </c>
       <c r="E23" s="6">
-        <v>-1.5</v>
+        <v>-13.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>30.76</v>
+        <v>463</v>
       </c>
       <c r="D24" s="5">
-        <v>29</v>
+        <v>458.7</v>
       </c>
       <c r="E24" s="6">
-        <v>-1.76</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>57.01</v>
+        <v>29</v>
       </c>
       <c r="D25" s="5">
-        <v>53.12</v>
+        <v>24.19</v>
       </c>
       <c r="E25" s="6">
-        <v>-3.89</v>
+        <v>-4.81</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>38.54</v>
+        <v>53.12</v>
       </c>
       <c r="D26" s="5">
-        <v>37.97</v>
+        <v>50.93</v>
       </c>
       <c r="E26" s="6">
-        <v>-0.57</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>-3.19</v>
+        <v>37.97</v>
       </c>
       <c r="D27" s="5">
-        <v>20.85</v>
-      </c>
-      <c r="E27" s="7">
-        <v>24.04</v>
+        <v>36.33</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>179.56</v>
+        <v>20.85</v>
       </c>
       <c r="D28" s="5">
-        <v>-21.19</v>
+        <v>-31.88</v>
       </c>
       <c r="E28" s="6">
-        <v>-200.75</v>
+        <v>-52.73</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>469.2</v>
+        <v>-21.19</v>
       </c>
       <c r="D29" s="5">
+        <v>-46.67</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-25.48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="5">
         <v>-33.57</v>
       </c>
-      <c r="E29" s="6">
-        <v>-502.77</v>
+      <c r="D30" s="5">
+        <v>-19.61</v>
+      </c>
+      <c r="E30" s="7">
+        <v>13.96</v>
       </c>
     </row>
   </sheetData>
@@ -1857,16 +1872,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>40</v>
+        <v>37.2</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.7</v>
+        <v>-7.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.3</v>
+        <v>-7.6</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1985,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.134</v>
+        <v>0.1336</v>
       </c>
       <c r="B2" s="13">
-        <v>0.005600000000000001</v>
+        <v>0.0044</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.06809999999999999</v>
+        <v>-0.0699</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.9 → 47.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.9</t>
+  </si>
+  <si>
+    <t>47.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -362,17 +389,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -884,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1302</v>
+        <v>1292.2</v>
       </c>
       <c r="D2">
-        <v>-1.87</v>
+        <v>-0.75</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,25 +924,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-11.01</v>
+        <v>-11.68</v>
       </c>
       <c r="H2">
-        <v>7.97</v>
+        <v>7.16</v>
       </c>
       <c r="I2">
-        <v>-3.2</v>
+        <v>-3.54</v>
       </c>
       <c r="J2">
-        <v>-9.77</v>
+        <v>-9.18</v>
       </c>
       <c r="K2">
-        <v>-5.32</v>
+        <v>-6.35</v>
       </c>
       <c r="L2">
-        <v>-6.62</v>
+        <v>-6.55</v>
       </c>
       <c r="M2">
-        <v>13.36</v>
+        <v>13.43</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -923,19 +951,19 @@
         <v>49</v>
       </c>
       <c r="P2">
-        <v>1328.58</v>
+        <v>1319.1</v>
       </c>
       <c r="Q2">
-        <v>1376.76</v>
+        <v>1368.67</v>
       </c>
       <c r="R2">
-        <v>1410.1</v>
+        <v>1406.74</v>
       </c>
       <c r="S2">
-        <v>1353.87</v>
+        <v>1353.51</v>
       </c>
       <c r="T2">
-        <v>-3.83</v>
+        <v>-4.53</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,43 +978,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>24.19</v>
+        <v>22.6</v>
       </c>
       <c r="Z2">
-        <v>-26.19</v>
+        <v>-28.58</v>
       </c>
       <c r="AA2">
-        <v>-19.89</v>
+        <v>-21.63</v>
       </c>
       <c r="AB2">
-        <v>-6.3</v>
+        <v>-6.95</v>
       </c>
       <c r="AC2">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>3.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE2">
-        <v>20.69</v>
+        <v>20.2</v>
       </c>
       <c r="AF2">
-        <v>-31.88</v>
+        <v>63.72</v>
       </c>
       <c r="AG2">
-        <v>1465.49</v>
+        <v>1457.25</v>
       </c>
       <c r="AH2">
-        <v>1288.02</v>
+        <v>1280.08</v>
       </c>
       <c r="AI2">
-        <v>1373.98</v>
+        <v>1358.5</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>60.66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1540</v>
+        <v>1515</v>
       </c>
       <c r="D3">
-        <v>-0.88</v>
+        <v>-1.62</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1037,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-24.33</v>
+        <v>-25.56</v>
       </c>
       <c r="H3">
-        <v>7.87</v>
+        <v>6.11</v>
       </c>
       <c r="I3">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="J3">
-        <v>-3.03</v>
+        <v>-3.01</v>
       </c>
       <c r="K3">
-        <v>-11.58</v>
+        <v>-13.8</v>
       </c>
       <c r="L3">
-        <v>-18.15</v>
+        <v>-18.78</v>
       </c>
       <c r="M3">
-        <v>0.44</v>
+        <v>-0.37</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P3">
-        <v>1530.26</v>
+        <v>1537.26</v>
       </c>
       <c r="Q3">
-        <v>1502.6</v>
+        <v>1500</v>
       </c>
       <c r="R3">
-        <v>1580.28</v>
+        <v>1578.15</v>
       </c>
       <c r="S3">
-        <v>1769.18</v>
+        <v>1767.11</v>
       </c>
       <c r="T3">
-        <v>-12.95</v>
+        <v>-14.27</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,34 +1091,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>50.93</v>
+        <v>47.1</v>
       </c>
       <c r="Z3">
-        <v>-17</v>
+        <v>-15.77</v>
       </c>
       <c r="AA3">
-        <v>-32.27</v>
+        <v>-28.97</v>
       </c>
       <c r="AB3">
-        <v>15.27</v>
+        <v>13.2</v>
       </c>
       <c r="AC3">
-        <v>91.91</v>
+        <v>83.87</v>
       </c>
       <c r="AD3">
-        <v>94.29000000000001</v>
+        <v>90.77</v>
       </c>
       <c r="AE3">
-        <v>39.16</v>
+        <v>40.07</v>
       </c>
       <c r="AF3">
-        <v>-46.67</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="AG3">
-        <v>1589.92</v>
+        <v>1582.21</v>
       </c>
       <c r="AH3">
-        <v>1415.28</v>
+        <v>1417.8</v>
       </c>
       <c r="AI3">
         <v>1449.16</v>
@@ -1099,7 +1127,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>41.68</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,58 +1138,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>458.7</v>
+        <v>444.55</v>
       </c>
       <c r="D4">
-        <v>-0.93</v>
+        <v>-3.08</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
       </c>
       <c r="F4">
-        <v>457.6</v>
+        <v>444.55</v>
       </c>
       <c r="G4">
-        <v>-33.14</v>
+        <v>-35.2</v>
       </c>
       <c r="H4">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-6.96</v>
+        <v>-8.65</v>
       </c>
       <c r="J4">
-        <v>-10.06</v>
+        <v>-12.14</v>
       </c>
       <c r="K4">
-        <v>-5.99</v>
+        <v>-9.82</v>
       </c>
       <c r="L4">
-        <v>-23.39</v>
+        <v>-25.23</v>
       </c>
       <c r="M4">
-        <v>-6.99</v>
+        <v>-7.81</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>471.47</v>
+        <v>463.05</v>
       </c>
       <c r="Q4">
-        <v>480.35</v>
+        <v>476.72</v>
       </c>
       <c r="R4">
-        <v>496.51</v>
+        <v>495.43</v>
       </c>
       <c r="S4">
-        <v>554.33</v>
+        <v>553.35</v>
       </c>
       <c r="T4">
-        <v>-17.25</v>
+        <v>-19.66</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,43 +1204,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.33</v>
+        <v>31.51</v>
       </c>
       <c r="Z4">
-        <v>-8.16</v>
+        <v>-10.01</v>
       </c>
       <c r="AA4">
-        <v>-6.88</v>
+        <v>-7.51</v>
       </c>
       <c r="AB4">
-        <v>-1.27</v>
+        <v>-2.5</v>
       </c>
       <c r="AC4">
-        <v>35.65</v>
+        <v>24.83</v>
       </c>
       <c r="AD4">
-        <v>52.11</v>
+        <v>37.63</v>
       </c>
       <c r="AE4">
-        <v>15.22</v>
+        <v>15.25</v>
       </c>
       <c r="AF4">
-        <v>-19.61</v>
+        <v>69.12</v>
       </c>
       <c r="AG4">
-        <v>513.3099999999999</v>
+        <v>508.62</v>
       </c>
       <c r="AH4">
-        <v>447.39</v>
+        <v>444.83</v>
       </c>
       <c r="AI4">
-        <v>502.26</v>
+        <v>494.96</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>33.72</v>
+        <v>37.2</v>
       </c>
     </row>
   </sheetData>
@@ -1373,12 +1401,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1386,428 +1449,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-7.22</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-9.77</v>
       </c>
-      <c r="E7" s="6">
-        <v>-2.55</v>
+      <c r="D7" s="6">
+        <v>-9.18</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.59</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-2.71</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-3.03</v>
       </c>
-      <c r="E8" s="6">
-        <v>-0.32</v>
+      <c r="D8" s="6">
+        <v>-3.01</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-10.11</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-10.06</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.05</v>
+      <c r="D9" s="6">
+        <v>-12.14</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-0.9</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-3.2</v>
       </c>
-      <c r="E10" s="6">
-        <v>-2.3</v>
+      <c r="D10" s="6">
+        <v>-3.54</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>6.56</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>2.05</v>
       </c>
-      <c r="E11" s="6">
-        <v>-4.51</v>
+      <c r="D11" s="6">
+        <v>2.36</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.31</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-5.89</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-6.96</v>
       </c>
-      <c r="E12" s="6">
-        <v>-1.07</v>
+      <c r="D12" s="6">
+        <v>-8.65</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-5.33</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-6.62</v>
       </c>
-      <c r="E13" s="6">
-        <v>-1.29</v>
+      <c r="D13" s="6">
+        <v>-6.55</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-17.05</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-18.15</v>
       </c>
-      <c r="E14" s="6">
-        <v>-1.1</v>
+      <c r="D14" s="6">
+        <v>-18.78</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-23.77</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-23.39</v>
       </c>
-      <c r="E15" s="7">
-        <v>0.38</v>
+      <c r="D15" s="6">
+        <v>-25.23</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-4.38</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-5.32</v>
       </c>
-      <c r="E16" s="6">
-        <v>-0.9399999999999999</v>
+      <c r="D16" s="6">
+        <v>-6.35</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-12.13</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-11.58</v>
       </c>
-      <c r="E17" s="7">
-        <v>0.55</v>
+      <c r="D17" s="6">
+        <v>-13.8</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-5.41</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-5.99</v>
       </c>
-      <c r="E18" s="6">
-        <v>-0.58</v>
+      <c r="D18" s="6">
+        <v>-9.82</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-3.83</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-9.32</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-11.01</v>
       </c>
-      <c r="E19" s="6">
-        <v>-1.69</v>
+      <c r="D19" s="6">
+        <v>-11.68</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-23.66</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-24.33</v>
       </c>
-      <c r="E20" s="6">
-        <v>-0.67</v>
+      <c r="D20" s="6">
+        <v>-25.56</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-32.51</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-33.14</v>
       </c>
-      <c r="E21" s="6">
-        <v>-0.63</v>
+      <c r="D21" s="6">
+        <v>-35.2</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>1326.8</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>1302</v>
       </c>
-      <c r="E22" s="6">
-        <v>-24.8</v>
+      <c r="D22" s="6">
+        <v>1292.2</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-9.800000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>1553.7</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>1540</v>
       </c>
-      <c r="E23" s="6">
-        <v>-13.7</v>
+      <c r="D23" s="6">
+        <v>1515</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-25</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>463</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>458.7</v>
       </c>
-      <c r="E24" s="6">
-        <v>-4.3</v>
+      <c r="D24" s="6">
+        <v>444.55</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-14.15</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>29</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>24.19</v>
       </c>
-      <c r="E25" s="6">
-        <v>-4.81</v>
+      <c r="D25" s="6">
+        <v>22.6</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>53.12</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>50.93</v>
       </c>
-      <c r="E26" s="6">
-        <v>-2.19</v>
+      <c r="D26" s="6">
+        <v>47.1</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-3.83</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>37.97</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>36.33</v>
       </c>
-      <c r="E27" s="6">
-        <v>-1.64</v>
+      <c r="D27" s="6">
+        <v>31.51</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-4.82</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>20.85</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>-31.88</v>
       </c>
-      <c r="E28" s="6">
-        <v>-52.73</v>
+      <c r="D28" s="6">
+        <v>63.72</v>
+      </c>
+      <c r="E28" s="7">
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-21.19</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-46.67</v>
       </c>
-      <c r="E29" s="6">
-        <v>-25.48</v>
+      <c r="D29" s="6">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="E29" s="7">
+        <v>37.7</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-33.57</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-19.61</v>
       </c>
+      <c r="D30" s="6">
+        <v>69.12</v>
+      </c>
       <c r="E30" s="7">
-        <v>13.96</v>
+        <v>88.73</v>
       </c>
     </row>
   </sheetData>
@@ -1833,60 +1896,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>37.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>33.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-7.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-7.6</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-8.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-10</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1988,25 +2051,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1336</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0044</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0699</v>
+      <c r="A2" s="14">
+        <v>0.1343</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0037</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0781</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,19 +175,31 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>22.6 → 36.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>36.2</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.9 → 47.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.9</t>
+    <t>47.1 → 57.4</t>
   </si>
   <si>
     <t>47.1</t>
+  </si>
+  <si>
+    <t>57.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,8 +411,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -912,10 +924,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1292.2</v>
+        <v>1321.7</v>
       </c>
       <c r="D2">
-        <v>-0.75</v>
+        <v>2.28</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,46 +936,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-11.68</v>
+        <v>-9.66</v>
       </c>
       <c r="H2">
-        <v>7.16</v>
+        <v>9.6</v>
       </c>
       <c r="I2">
-        <v>-3.54</v>
+        <v>-1.37</v>
       </c>
       <c r="J2">
-        <v>-9.18</v>
+        <v>-9.1</v>
       </c>
       <c r="K2">
-        <v>-6.35</v>
+        <v>-5.59</v>
       </c>
       <c r="L2">
-        <v>-6.55</v>
+        <v>-3.93</v>
       </c>
       <c r="M2">
-        <v>13.43</v>
+        <v>14.22</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P2">
-        <v>1319.1</v>
+        <v>1315.44</v>
       </c>
       <c r="Q2">
-        <v>1368.67</v>
+        <v>1362.85</v>
       </c>
       <c r="R2">
-        <v>1406.74</v>
+        <v>1403.91</v>
       </c>
       <c r="S2">
-        <v>1353.51</v>
+        <v>1353.32</v>
       </c>
       <c r="T2">
-        <v>-4.53</v>
+        <v>-2.34</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +990,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>22.6</v>
+        <v>36.22</v>
       </c>
       <c r="Z2">
-        <v>-28.58</v>
+        <v>-27.76</v>
       </c>
       <c r="AA2">
-        <v>-21.63</v>
+        <v>-22.86</v>
       </c>
       <c r="AB2">
-        <v>-6.95</v>
+        <v>-4.91</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>28.56</v>
       </c>
       <c r="AD2">
-        <v>1.36</v>
+        <v>9.75</v>
       </c>
       <c r="AE2">
-        <v>20.2</v>
+        <v>21.96</v>
       </c>
       <c r="AF2">
-        <v>63.72</v>
+        <v>50.98</v>
       </c>
       <c r="AG2">
-        <v>1457.25</v>
+        <v>1447.45</v>
       </c>
       <c r="AH2">
-        <v>1280.08</v>
+        <v>1278.25</v>
       </c>
       <c r="AI2">
         <v>1358.5</v>
@@ -1014,7 +1026,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>64</v>
+        <v>57.64</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +1037,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1515</v>
+        <v>1590</v>
       </c>
       <c r="D3">
-        <v>-1.62</v>
+        <v>4.95</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1037,46 +1049,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-25.56</v>
+        <v>-21.87</v>
       </c>
       <c r="H3">
-        <v>6.11</v>
+        <v>11.37</v>
       </c>
       <c r="I3">
-        <v>2.36</v>
+        <v>5.96</v>
       </c>
       <c r="J3">
-        <v>-3.01</v>
+        <v>1.47</v>
       </c>
       <c r="K3">
-        <v>-13.8</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L3">
-        <v>-18.78</v>
+        <v>-14.91</v>
       </c>
       <c r="M3">
-        <v>-0.37</v>
+        <v>0.74</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="P3">
-        <v>1537.26</v>
+        <v>1555.14</v>
       </c>
       <c r="Q3">
-        <v>1500</v>
+        <v>1501.16</v>
       </c>
       <c r="R3">
-        <v>1578.15</v>
+        <v>1577.47</v>
       </c>
       <c r="S3">
-        <v>1767.11</v>
+        <v>1765.4</v>
       </c>
       <c r="T3">
-        <v>-14.27</v>
+        <v>-9.94</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1091,34 +1103,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>47.1</v>
+        <v>57.43</v>
       </c>
       <c r="Z3">
-        <v>-15.77</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="AA3">
-        <v>-28.97</v>
+        <v>-24.9</v>
       </c>
       <c r="AB3">
-        <v>13.2</v>
+        <v>16.26</v>
       </c>
       <c r="AC3">
-        <v>83.87</v>
+        <v>87.02</v>
       </c>
       <c r="AD3">
-        <v>90.77</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AE3">
-        <v>40.07</v>
+        <v>42.8</v>
       </c>
       <c r="AF3">
-        <v>-8.970000000000001</v>
+        <v>136.31</v>
       </c>
       <c r="AG3">
-        <v>1582.21</v>
+        <v>1587.85</v>
       </c>
       <c r="AH3">
-        <v>1417.8</v>
+        <v>1414.47</v>
       </c>
       <c r="AI3">
         <v>1449.16</v>
@@ -1127,7 +1139,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>36.94</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,34 +1150,34 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>444.55</v>
+        <v>443.8</v>
       </c>
       <c r="D4">
-        <v>-3.08</v>
+        <v>-0.17</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
       </c>
       <c r="F4">
-        <v>444.55</v>
+        <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-35.2</v>
+        <v>-35.31</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-8.65</v>
+        <v>-8.4</v>
       </c>
       <c r="J4">
-        <v>-12.14</v>
+        <v>-14.17</v>
       </c>
       <c r="K4">
-        <v>-9.82</v>
+        <v>-10.52</v>
       </c>
       <c r="L4">
-        <v>-25.23</v>
+        <v>-25.15</v>
       </c>
       <c r="M4">
         <v>-7.81</v>
@@ -1174,19 +1186,19 @@
         <v>34</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>463.05</v>
+        <v>454.91</v>
       </c>
       <c r="Q4">
-        <v>476.72</v>
+        <v>474.14</v>
       </c>
       <c r="R4">
-        <v>495.43</v>
+        <v>494.3</v>
       </c>
       <c r="S4">
-        <v>553.35</v>
+        <v>552.4</v>
       </c>
       <c r="T4">
         <v>-19.66</v>
@@ -1204,43 +1216,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.51</v>
+        <v>31.27</v>
       </c>
       <c r="Z4">
-        <v>-10.01</v>
+        <v>-11.41</v>
       </c>
       <c r="AA4">
-        <v>-7.51</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="AB4">
-        <v>-2.5</v>
+        <v>-3.12</v>
       </c>
       <c r="AC4">
-        <v>24.83</v>
+        <v>12.43</v>
       </c>
       <c r="AD4">
-        <v>37.63</v>
+        <v>24.3</v>
       </c>
       <c r="AE4">
-        <v>15.25</v>
+        <v>14.68</v>
       </c>
       <c r="AF4">
-        <v>69.12</v>
+        <v>-52.95</v>
       </c>
       <c r="AG4">
-        <v>508.62</v>
+        <v>507.96</v>
       </c>
       <c r="AH4">
-        <v>444.83</v>
+        <v>440.32</v>
       </c>
       <c r="AI4">
-        <v>494.96</v>
+        <v>490.44</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>37.2</v>
+        <v>40.22</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1421,7 +1433,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>51</v>
@@ -1439,444 +1451,464 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-9.77</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-9.18</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0.59</v>
+      <c r="B7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-3.03</v>
+        <v>-9.18</v>
       </c>
       <c r="D8" s="6">
-        <v>-3.01</v>
+        <v>-9.1</v>
       </c>
       <c r="E8" s="7">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-10.06</v>
+        <v>-3.01</v>
       </c>
       <c r="D9" s="6">
-        <v>-12.14</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-2.08</v>
+        <v>1.47</v>
+      </c>
+      <c r="E9" s="7">
+        <v>4.48</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-3.2</v>
+        <v>-12.14</v>
       </c>
       <c r="D10" s="6">
-        <v>-3.54</v>
+        <v>-14.17</v>
       </c>
       <c r="E10" s="8">
-        <v>-0.34</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>2.05</v>
+        <v>-3.54</v>
       </c>
       <c r="D11" s="6">
-        <v>2.36</v>
+        <v>-1.37</v>
       </c>
       <c r="E11" s="7">
-        <v>0.31</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.96</v>
+        <v>2.36</v>
       </c>
       <c r="D12" s="6">
-        <v>-8.65</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.69</v>
+        <v>5.96</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3.6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-6.62</v>
+        <v>-8.65</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.55</v>
+        <v>-8.4</v>
       </c>
       <c r="E13" s="7">
-        <v>0.07000000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-18.15</v>
+        <v>-6.55</v>
       </c>
       <c r="D14" s="6">
-        <v>-18.78</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.63</v>
+        <v>-3.93</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-23.39</v>
+        <v>-18.78</v>
       </c>
       <c r="D15" s="6">
-        <v>-25.23</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.84</v>
+        <v>-14.91</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.87</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6">
-        <v>-5.32</v>
+        <v>-25.23</v>
       </c>
       <c r="D16" s="6">
-        <v>-6.35</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.03</v>
+        <v>-25.15</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.08</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-11.58</v>
+        <v>-6.35</v>
       </c>
       <c r="D17" s="6">
-        <v>-13.8</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-2.22</v>
+        <v>-5.59</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.76</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.99</v>
+        <v>-13.8</v>
       </c>
       <c r="D18" s="6">
-        <v>-9.82</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-3.83</v>
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="E18" s="7">
+        <v>4.09</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-11.01</v>
+        <v>-9.82</v>
       </c>
       <c r="D19" s="6">
-        <v>-11.68</v>
+        <v>-10.52</v>
       </c>
       <c r="E19" s="8">
-        <v>-0.67</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-24.33</v>
+        <v>-11.68</v>
       </c>
       <c r="D20" s="6">
-        <v>-25.56</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-1.23</v>
+        <v>-9.66</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.02</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-33.14</v>
+        <v>-25.56</v>
       </c>
       <c r="D21" s="6">
-        <v>-35.2</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-2.06</v>
+        <v>-21.87</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.69</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6">
-        <v>1302</v>
+        <v>-35.2</v>
       </c>
       <c r="D22" s="6">
-        <v>1292.2</v>
+        <v>-35.31</v>
       </c>
       <c r="E22" s="8">
-        <v>-9.800000000000001</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>1540</v>
+        <v>1292.2</v>
       </c>
       <c r="D23" s="6">
-        <v>1515</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-25</v>
+        <v>1321.7</v>
+      </c>
+      <c r="E23" s="7">
+        <v>29.5</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>458.7</v>
+        <v>1515</v>
       </c>
       <c r="D24" s="6">
-        <v>444.55</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-14.15</v>
+        <v>1590</v>
+      </c>
+      <c r="E24" s="7">
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C25" s="6">
-        <v>24.19</v>
+        <v>444.55</v>
       </c>
       <c r="D25" s="6">
-        <v>22.6</v>
+        <v>443.8</v>
       </c>
       <c r="E25" s="8">
-        <v>-1.59</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>50.93</v>
+        <v>22.6</v>
       </c>
       <c r="D26" s="6">
-        <v>47.1</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-3.83</v>
+        <v>36.22</v>
+      </c>
+      <c r="E26" s="7">
+        <v>13.62</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>36.33</v>
+        <v>47.1</v>
       </c>
       <c r="D27" s="6">
-        <v>31.51</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-4.82</v>
+        <v>57.43</v>
+      </c>
+      <c r="E27" s="7">
+        <v>10.33</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C28" s="6">
-        <v>-31.88</v>
+        <v>31.51</v>
       </c>
       <c r="D28" s="6">
-        <v>63.72</v>
-      </c>
-      <c r="E28" s="7">
-        <v>95.59999999999999</v>
+        <v>31.27</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>-46.67</v>
+        <v>63.72</v>
       </c>
       <c r="D29" s="6">
-        <v>-8.970000000000001</v>
-      </c>
-      <c r="E29" s="7">
-        <v>37.7</v>
+        <v>50.98</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-12.74</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-19.61</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="D30" s="6">
+        <v>136.31</v>
+      </c>
+      <c r="E30" s="7">
+        <v>145.28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6">
         <v>69.12</v>
       </c>
-      <c r="E30" s="7">
-        <v>88.73</v>
+      <c r="D31" s="6">
+        <v>-52.95</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-122.07</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1900,28 +1932,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1935,16 +1967,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>33.7</v>
+        <v>41.6</v>
       </c>
       <c r="E2" s="11">
         <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>-8.1</v>
+        <v>-7.3</v>
       </c>
       <c r="G2" s="11">
-        <v>-10</v>
+        <v>-8.6</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2063,10 +2095,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1343</v>
+        <v>0.1422</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0037</v>
+        <v>0.0074</v>
       </c>
       <c r="C2" s="14">
         <v>-0.0781</v>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,46 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>22.6 → 36.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>22.6</t>
-  </si>
-  <si>
-    <t>36.2</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>47.1 → 57.4</t>
-  </si>
-  <si>
-    <t>47.1</t>
-  </si>
-  <si>
-    <t>57.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -401,15 +362,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -924,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1321.7</v>
+        <v>1310.6</v>
       </c>
       <c r="D2">
-        <v>2.28</v>
+        <v>-0.84</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -936,46 +896,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-9.66</v>
+        <v>-10.42</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>8.68</v>
       </c>
       <c r="I2">
-        <v>-1.37</v>
+        <v>-1.79</v>
       </c>
       <c r="J2">
-        <v>-9.1</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="K2">
-        <v>-5.59</v>
+        <v>-7.14</v>
       </c>
       <c r="L2">
-        <v>-3.93</v>
+        <v>-3.6</v>
       </c>
       <c r="M2">
-        <v>14.22</v>
+        <v>14.31</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P2">
-        <v>1315.44</v>
+        <v>1310.66</v>
       </c>
       <c r="Q2">
-        <v>1362.85</v>
+        <v>1357.05</v>
       </c>
       <c r="R2">
-        <v>1403.91</v>
+        <v>1401.31</v>
       </c>
       <c r="S2">
-        <v>1353.32</v>
+        <v>1353.04</v>
       </c>
       <c r="T2">
-        <v>-2.34</v>
+        <v>-3.14</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -990,34 +950,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>36.22</v>
+        <v>33.81</v>
       </c>
       <c r="Z2">
-        <v>-27.76</v>
+        <v>-27.7</v>
       </c>
       <c r="AA2">
-        <v>-22.86</v>
+        <v>-23.82</v>
       </c>
       <c r="AB2">
-        <v>-4.91</v>
+        <v>-3.87</v>
       </c>
       <c r="AC2">
-        <v>28.56</v>
+        <v>54.17</v>
       </c>
       <c r="AD2">
-        <v>9.75</v>
+        <v>27.58</v>
       </c>
       <c r="AE2">
-        <v>21.96</v>
+        <v>21.92</v>
       </c>
       <c r="AF2">
-        <v>50.98</v>
+        <v>39.93</v>
       </c>
       <c r="AG2">
-        <v>1447.45</v>
+        <v>1439.14</v>
       </c>
       <c r="AH2">
-        <v>1278.25</v>
+        <v>1274.97</v>
       </c>
       <c r="AI2">
         <v>1358.5</v>
@@ -1026,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>57.64</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1590</v>
+        <v>1563</v>
       </c>
       <c r="D3">
-        <v>4.95</v>
+        <v>-1.7</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1049,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-21.87</v>
+        <v>-23.2</v>
       </c>
       <c r="H3">
-        <v>11.37</v>
+        <v>9.48</v>
       </c>
       <c r="I3">
-        <v>5.96</v>
+        <v>-0.89</v>
       </c>
       <c r="J3">
-        <v>1.47</v>
+        <v>-0.25</v>
       </c>
       <c r="K3">
-        <v>-9.710000000000001</v>
+        <v>-11.83</v>
       </c>
       <c r="L3">
-        <v>-14.91</v>
+        <v>-16.89</v>
       </c>
       <c r="M3">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P3">
-        <v>1555.14</v>
+        <v>1552.34</v>
       </c>
       <c r="Q3">
-        <v>1501.16</v>
+        <v>1502.46</v>
       </c>
       <c r="R3">
-        <v>1577.47</v>
+        <v>1577.06</v>
       </c>
       <c r="S3">
-        <v>1765.4</v>
+        <v>1763.57</v>
       </c>
       <c r="T3">
-        <v>-9.94</v>
+        <v>-11.37</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1103,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>57.43</v>
+        <v>53.39</v>
       </c>
       <c r="Z3">
-        <v>-8.640000000000001</v>
+        <v>-5.11</v>
       </c>
       <c r="AA3">
-        <v>-24.9</v>
+        <v>-20.94</v>
       </c>
       <c r="AB3">
-        <v>16.26</v>
+        <v>15.83</v>
       </c>
       <c r="AC3">
-        <v>87.02</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="AD3">
-        <v>87.59999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="AE3">
-        <v>42.8</v>
+        <v>42.04</v>
       </c>
       <c r="AF3">
-        <v>136.31</v>
+        <v>39.63</v>
       </c>
       <c r="AG3">
-        <v>1587.85</v>
+        <v>1592.14</v>
       </c>
       <c r="AH3">
-        <v>1414.47</v>
+        <v>1412.78</v>
       </c>
       <c r="AI3">
-        <v>1449.16</v>
+        <v>1452.53</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>35.78</v>
+        <v>35.07</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>443.8</v>
+        <v>448.05</v>
       </c>
       <c r="D4">
-        <v>-0.17</v>
+        <v>0.96</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1162,46 +1122,46 @@
         <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-35.31</v>
+        <v>-34.69</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="I4">
-        <v>-8.4</v>
+        <v>-3.54</v>
       </c>
       <c r="J4">
-        <v>-14.17</v>
+        <v>-9.57</v>
       </c>
       <c r="K4">
-        <v>-10.52</v>
+        <v>-7.67</v>
       </c>
       <c r="L4">
-        <v>-25.15</v>
+        <v>-23.21</v>
       </c>
       <c r="M4">
-        <v>-7.81</v>
+        <v>-7.53</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="P4">
-        <v>454.91</v>
+        <v>451.62</v>
       </c>
       <c r="Q4">
-        <v>474.14</v>
+        <v>471.57</v>
       </c>
       <c r="R4">
-        <v>494.3</v>
+        <v>493.27</v>
       </c>
       <c r="S4">
-        <v>552.4</v>
+        <v>551.41</v>
       </c>
       <c r="T4">
-        <v>-19.66</v>
+        <v>-18.75</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1216,43 +1176,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.27</v>
+        <v>34.29</v>
       </c>
       <c r="Z4">
-        <v>-11.41</v>
+        <v>-12.03</v>
       </c>
       <c r="AA4">
-        <v>-8.289999999999999</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="AB4">
-        <v>-3.12</v>
+        <v>-3</v>
       </c>
       <c r="AC4">
-        <v>12.43</v>
+        <v>7.5</v>
       </c>
       <c r="AD4">
-        <v>24.3</v>
+        <v>14.92</v>
       </c>
       <c r="AE4">
-        <v>14.68</v>
+        <v>14.26</v>
       </c>
       <c r="AF4">
-        <v>-52.95</v>
+        <v>-23.63</v>
       </c>
       <c r="AG4">
-        <v>507.96</v>
+        <v>505.1</v>
       </c>
       <c r="AH4">
-        <v>440.32</v>
+        <v>438.04</v>
       </c>
       <c r="AI4">
-        <v>490.44</v>
+        <v>488.94</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>40.22</v>
+        <v>42.96</v>
       </c>
     </row>
   </sheetData>
@@ -1393,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1413,502 +1373,447 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-9.1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.24</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1.47</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-14.17</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-9.57</v>
+      </c>
+      <c r="E9" s="6">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-9.18</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-9.1</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-1.37</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-1.79</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-3.01</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1.47</v>
-      </c>
-      <c r="E9" s="7">
-        <v>4.48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>5.96</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-0.89</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-6.85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-12.14</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-14.17</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-8.4</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-3.54</v>
+      </c>
+      <c r="E12" s="6">
+        <v>4.86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-3.54</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-1.37</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-3.93</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-3.6</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>2.36</v>
-      </c>
-      <c r="D12" s="6">
-        <v>5.96</v>
-      </c>
-      <c r="E12" s="7">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-14.91</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-16.89</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-8.65</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-8.4</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-25.15</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-23.21</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-6.55</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-3.93</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2.62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-5.59</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-7.14</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-18.78</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-14.91</v>
-      </c>
-      <c r="E15" s="7">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-11.83</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-25.23</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-25.15</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-10.52</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-7.67</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-6.35</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-5.59</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-9.66</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-10.42</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-13.8</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="E18" s="7">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-21.87</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-23.2</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-9.82</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-10.52</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-35.31</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-34.69</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-11.68</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-9.66</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1321.7</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1310.6</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-25.56</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-21.87</v>
-      </c>
-      <c r="E21" s="7">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1590</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1563</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-35.2</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-35.31</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>443.8</v>
+      </c>
+      <c r="D24" s="5">
+        <v>448.05</v>
+      </c>
+      <c r="E24" s="6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1292.2</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1321.7</v>
-      </c>
-      <c r="E23" s="7">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>36.22</v>
+      </c>
+      <c r="D25" s="5">
+        <v>33.81</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1515</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1590</v>
-      </c>
-      <c r="E24" s="7">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>57.43</v>
+      </c>
+      <c r="D26" s="5">
+        <v>53.39</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-4.04</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>444.55</v>
-      </c>
-      <c r="D25" s="6">
-        <v>443.8</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>31.27</v>
+      </c>
+      <c r="D27" s="5">
+        <v>34.29</v>
+      </c>
+      <c r="E27" s="6">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>22.6</v>
-      </c>
-      <c r="D26" s="6">
-        <v>36.22</v>
-      </c>
-      <c r="E26" s="7">
-        <v>13.62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>50.98</v>
+      </c>
+      <c r="D28" s="5">
+        <v>39.93</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-11.05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>47.1</v>
-      </c>
-      <c r="D27" s="6">
-        <v>57.43</v>
-      </c>
-      <c r="E27" s="7">
-        <v>10.33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>136.31</v>
+      </c>
+      <c r="D29" s="5">
+        <v>39.63</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-96.68000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>31.51</v>
-      </c>
-      <c r="D28" s="6">
-        <v>31.27</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>63.72</v>
-      </c>
-      <c r="D29" s="6">
-        <v>50.98</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-12.74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-8.970000000000001</v>
-      </c>
-      <c r="D30" s="6">
-        <v>136.31</v>
-      </c>
-      <c r="E30" s="7">
-        <v>145.28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>69.12</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C30" s="5">
         <v>-52.95</v>
       </c>
-      <c r="E31" s="8">
-        <v>-122.07</v>
+      <c r="D30" s="5">
+        <v>-23.63</v>
+      </c>
+      <c r="E30" s="6">
+        <v>29.32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1928,60 +1833,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>41.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>40.5</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-7.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-8.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-6.2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2083,25 +1988,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1422</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0074</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0781</v>
+      <c r="A2" s="13">
+        <v>0.1431</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0048</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.07530000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -744,7 +744,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -884,10 +885,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1310.6</v>
+        <v>1332</v>
       </c>
       <c r="D2">
-        <v>-0.84</v>
+        <v>1.63</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,46 +897,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-10.42</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="H2">
-        <v>8.68</v>
+        <v>10.46</v>
       </c>
       <c r="I2">
-        <v>-1.79</v>
+        <v>0.39</v>
       </c>
       <c r="J2">
-        <v>-8.859999999999999</v>
+        <v>-6.62</v>
       </c>
       <c r="K2">
-        <v>-7.14</v>
+        <v>-6.65</v>
       </c>
       <c r="L2">
-        <v>-3.6</v>
+        <v>-1.19</v>
       </c>
       <c r="M2">
-        <v>14.31</v>
+        <v>14.52</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="P2">
-        <v>1310.66</v>
+        <v>1311.7</v>
       </c>
       <c r="Q2">
-        <v>1357.05</v>
+        <v>1352.15</v>
       </c>
       <c r="R2">
-        <v>1401.31</v>
+        <v>1399.26</v>
       </c>
       <c r="S2">
-        <v>1353.04</v>
+        <v>1352.87</v>
       </c>
       <c r="T2">
-        <v>-3.14</v>
+        <v>-1.54</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +951,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>33.81</v>
+        <v>41.85</v>
       </c>
       <c r="Z2">
-        <v>-27.7</v>
+        <v>-25.62</v>
       </c>
       <c r="AA2">
-        <v>-23.82</v>
+        <v>-24.18</v>
       </c>
       <c r="AB2">
-        <v>-3.87</v>
+        <v>-1.44</v>
       </c>
       <c r="AC2">
-        <v>54.17</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="AD2">
-        <v>27.58</v>
+        <v>56.75</v>
       </c>
       <c r="AE2">
-        <v>21.92</v>
+        <v>22.57</v>
       </c>
       <c r="AF2">
-        <v>39.93</v>
+        <v>40.83</v>
       </c>
       <c r="AG2">
-        <v>1439.14</v>
+        <v>1427.31</v>
       </c>
       <c r="AH2">
-        <v>1274.97</v>
+        <v>1277</v>
       </c>
       <c r="AI2">
         <v>1358.5</v>
@@ -986,7 +987,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>52.12</v>
+        <v>46.27</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +998,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1563</v>
+        <v>1600</v>
       </c>
       <c r="D3">
-        <v>-1.7</v>
+        <v>2.37</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1010,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-23.2</v>
+        <v>-21.38</v>
       </c>
       <c r="H3">
-        <v>9.48</v>
+        <v>12.07</v>
       </c>
       <c r="I3">
-        <v>-0.89</v>
+        <v>2.98</v>
       </c>
       <c r="J3">
-        <v>-0.25</v>
+        <v>4.1</v>
       </c>
       <c r="K3">
-        <v>-11.83</v>
+        <v>-10.38</v>
       </c>
       <c r="L3">
-        <v>-16.89</v>
+        <v>-15.35</v>
       </c>
       <c r="M3">
-        <v>0.48</v>
+        <v>1.39</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="P3">
-        <v>1552.34</v>
+        <v>1561.6</v>
       </c>
       <c r="Q3">
-        <v>1502.46</v>
+        <v>1506.37</v>
       </c>
       <c r="R3">
-        <v>1577.06</v>
+        <v>1576.68</v>
       </c>
       <c r="S3">
-        <v>1763.57</v>
+        <v>1761.84</v>
       </c>
       <c r="T3">
-        <v>-11.37</v>
+        <v>-9.19</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,43 +1064,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>53.39</v>
+        <v>57.78</v>
       </c>
       <c r="Z3">
-        <v>-5.11</v>
+        <v>0.66</v>
       </c>
       <c r="AA3">
-        <v>-20.94</v>
+        <v>-16.62</v>
       </c>
       <c r="AB3">
-        <v>15.83</v>
+        <v>17.28</v>
       </c>
       <c r="AC3">
-        <v>88.70999999999999</v>
+        <v>96.75</v>
       </c>
       <c r="AD3">
-        <v>86.53</v>
+        <v>90.83</v>
       </c>
       <c r="AE3">
-        <v>42.04</v>
+        <v>42.39</v>
       </c>
       <c r="AF3">
-        <v>39.63</v>
+        <v>34.83</v>
       </c>
       <c r="AG3">
-        <v>1592.14</v>
+        <v>1605.89</v>
       </c>
       <c r="AH3">
-        <v>1412.78</v>
+        <v>1406.86</v>
       </c>
       <c r="AI3">
-        <v>1452.53</v>
+        <v>1457.39</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>35.07</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1111,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>448.05</v>
+        <v>454.9</v>
       </c>
       <c r="D4">
-        <v>0.96</v>
+        <v>1.53</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1122,46 +1123,46 @@
         <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-34.69</v>
+        <v>-33.69</v>
       </c>
       <c r="H4">
-        <v>0.96</v>
+        <v>2.5</v>
       </c>
       <c r="I4">
-        <v>-3.54</v>
+        <v>-1.75</v>
       </c>
       <c r="J4">
-        <v>-9.57</v>
+        <v>-8.93</v>
       </c>
       <c r="K4">
-        <v>-7.67</v>
+        <v>-6.23</v>
       </c>
       <c r="L4">
-        <v>-23.21</v>
+        <v>-22.52</v>
       </c>
       <c r="M4">
-        <v>-7.53</v>
+        <v>-7.55</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P4">
-        <v>451.62</v>
+        <v>450</v>
       </c>
       <c r="Q4">
-        <v>471.57</v>
+        <v>469.56</v>
       </c>
       <c r="R4">
-        <v>493.27</v>
+        <v>492.34</v>
       </c>
       <c r="S4">
-        <v>551.41</v>
+        <v>550.46</v>
       </c>
       <c r="T4">
-        <v>-18.75</v>
+        <v>-17.36</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1177,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.29</v>
+        <v>38.94</v>
       </c>
       <c r="Z4">
-        <v>-12.03</v>
+        <v>-11.84</v>
       </c>
       <c r="AA4">
-        <v>-9.039999999999999</v>
+        <v>-9.6</v>
       </c>
       <c r="AB4">
-        <v>-3</v>
+        <v>-2.24</v>
       </c>
       <c r="AC4">
-        <v>7.5</v>
+        <v>17.64</v>
       </c>
       <c r="AD4">
-        <v>14.92</v>
+        <v>12.52</v>
       </c>
       <c r="AE4">
-        <v>14.26</v>
+        <v>14.02</v>
       </c>
       <c r="AF4">
-        <v>-23.63</v>
+        <v>-24.17</v>
       </c>
       <c r="AG4">
-        <v>505.1</v>
+        <v>501.96</v>
       </c>
       <c r="AH4">
-        <v>438.04</v>
+        <v>437.17</v>
       </c>
       <c r="AI4">
         <v>488.94</v>
@@ -1212,7 +1213,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>42.96</v>
+        <v>42.45</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1411,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-9.1</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="D7" s="5">
-        <v>-8.859999999999999</v>
+        <v>-6.62</v>
       </c>
       <c r="E7" s="6">
-        <v>0.24</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1428,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>1.47</v>
+        <v>-0.25</v>
       </c>
       <c r="D8" s="5">
-        <v>-0.25</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.72</v>
+        <v>4.1</v>
+      </c>
+      <c r="E8" s="6">
+        <v>4.35</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1445,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-14.17</v>
+        <v>-9.57</v>
       </c>
       <c r="D9" s="5">
-        <v>-9.57</v>
+        <v>-8.93</v>
       </c>
       <c r="E9" s="6">
-        <v>4.6</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1462,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-1.37</v>
+        <v>-1.79</v>
       </c>
       <c r="D10" s="5">
-        <v>-1.79</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.42</v>
+        <v>0.39</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.18</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1479,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>5.96</v>
+        <v>-0.89</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.89</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-6.85</v>
+        <v>2.98</v>
+      </c>
+      <c r="E11" s="6">
+        <v>3.87</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1496,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-8.4</v>
+        <v>-3.54</v>
       </c>
       <c r="D12" s="5">
-        <v>-3.54</v>
+        <v>-1.75</v>
       </c>
       <c r="E12" s="6">
-        <v>4.86</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1513,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-3.93</v>
+        <v>-3.6</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.6</v>
+        <v>-1.19</v>
       </c>
       <c r="E13" s="6">
-        <v>0.33</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1530,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-14.91</v>
+        <v>-16.89</v>
       </c>
       <c r="D14" s="5">
-        <v>-16.89</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.98</v>
+        <v>-15.35</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.54</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1547,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-25.15</v>
+        <v>-23.21</v>
       </c>
       <c r="D15" s="5">
-        <v>-23.21</v>
+        <v>-22.52</v>
       </c>
       <c r="E15" s="6">
-        <v>1.94</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1564,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-5.59</v>
+        <v>-7.14</v>
       </c>
       <c r="D16" s="5">
-        <v>-7.14</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.55</v>
+        <v>-6.65</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.49</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1581,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-9.710000000000001</v>
+        <v>-11.83</v>
       </c>
       <c r="D17" s="5">
-        <v>-11.83</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.12</v>
+        <v>-10.38</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.45</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1598,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-10.52</v>
+        <v>-7.67</v>
       </c>
       <c r="D18" s="5">
-        <v>-7.67</v>
+        <v>-6.23</v>
       </c>
       <c r="E18" s="6">
-        <v>2.85</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1615,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-9.66</v>
+        <v>-10.42</v>
       </c>
       <c r="D19" s="5">
-        <v>-10.42</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.76</v>
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1.46</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1632,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-21.87</v>
+        <v>-23.2</v>
       </c>
       <c r="D20" s="5">
-        <v>-23.2</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.33</v>
+        <v>-21.38</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.82</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1649,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-35.31</v>
+        <v>-34.69</v>
       </c>
       <c r="D21" s="5">
-        <v>-34.69</v>
+        <v>-33.69</v>
       </c>
       <c r="E21" s="6">
-        <v>0.62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1666,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1321.7</v>
+        <v>1310.6</v>
       </c>
       <c r="D22" s="5">
-        <v>1310.6</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-11.1</v>
+        <v>1332</v>
+      </c>
+      <c r="E22" s="6">
+        <v>21.4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1683,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1590</v>
+        <v>1563</v>
       </c>
       <c r="D23" s="5">
-        <v>1563</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-27</v>
+        <v>1600</v>
+      </c>
+      <c r="E23" s="6">
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1700,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>443.8</v>
+        <v>448.05</v>
       </c>
       <c r="D24" s="5">
-        <v>448.05</v>
+        <v>454.9</v>
       </c>
       <c r="E24" s="6">
-        <v>4.25</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1716,13 +1717,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>36.22</v>
+        <v>33.81</v>
       </c>
       <c r="D25" s="5">
-        <v>33.81</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.41</v>
+        <v>41.85</v>
+      </c>
+      <c r="E25" s="6">
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1734,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>57.43</v>
+        <v>53.39</v>
       </c>
       <c r="D26" s="5">
-        <v>53.39</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-4.04</v>
+        <v>57.78</v>
+      </c>
+      <c r="E26" s="6">
+        <v>4.39</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1751,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>31.27</v>
+        <v>34.29</v>
       </c>
       <c r="D27" s="5">
-        <v>34.29</v>
+        <v>38.94</v>
       </c>
       <c r="E27" s="6">
-        <v>3.02</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1768,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>50.98</v>
+        <v>39.93</v>
       </c>
       <c r="D28" s="5">
-        <v>39.93</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-11.05</v>
+        <v>40.83</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.9</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1785,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>136.31</v>
+        <v>39.63</v>
       </c>
       <c r="D29" s="5">
-        <v>39.63</v>
+        <v>34.83</v>
       </c>
       <c r="E29" s="7">
-        <v>-96.68000000000001</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1802,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-52.95</v>
+        <v>-23.63</v>
       </c>
       <c r="D30" s="5">
-        <v>-23.63</v>
-      </c>
-      <c r="E30" s="6">
-        <v>29.32</v>
+        <v>-24.17</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -1872,16 +1873,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>40.5</v>
+        <v>46.2</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.2</v>
+        <v>-3.8</v>
       </c>
       <c r="G2" s="10">
-        <v>-8.9</v>
+        <v>-7.8</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2000,13 +2001,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1431</v>
+        <v>0.1452</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0048</v>
+        <v>0.0139</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.07530000000000001</v>
+        <v>-0.0755</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -744,8 +744,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -885,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1332</v>
+        <v>1342.8</v>
       </c>
       <c r="D2">
-        <v>1.63</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -897,25 +896,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-8.960000000000001</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="H2">
-        <v>10.46</v>
+        <v>11.35</v>
       </c>
       <c r="I2">
-        <v>0.39</v>
+        <v>3.13</v>
       </c>
       <c r="J2">
-        <v>-6.62</v>
+        <v>-6.1</v>
       </c>
       <c r="K2">
-        <v>-6.65</v>
+        <v>-5.08</v>
       </c>
       <c r="L2">
-        <v>-1.19</v>
+        <v>-0.39</v>
       </c>
       <c r="M2">
-        <v>14.52</v>
+        <v>14.96</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -924,19 +923,19 @@
         <v>55</v>
       </c>
       <c r="P2">
-        <v>1311.7</v>
+        <v>1319.86</v>
       </c>
       <c r="Q2">
-        <v>1352.15</v>
+        <v>1348.14</v>
       </c>
       <c r="R2">
-        <v>1399.26</v>
+        <v>1397.46</v>
       </c>
       <c r="S2">
-        <v>1352.87</v>
+        <v>1352.76</v>
       </c>
       <c r="T2">
-        <v>-1.54</v>
+        <v>-0.74</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -951,34 +950,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>41.85</v>
+        <v>45.45</v>
       </c>
       <c r="Z2">
-        <v>-25.62</v>
+        <v>-22.84</v>
       </c>
       <c r="AA2">
-        <v>-24.18</v>
+        <v>-23.91</v>
       </c>
       <c r="AB2">
-        <v>-1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AC2">
-        <v>87.51000000000001</v>
+        <v>92.28</v>
       </c>
       <c r="AD2">
-        <v>56.75</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="AE2">
-        <v>22.57</v>
+        <v>22.07</v>
       </c>
       <c r="AF2">
-        <v>40.83</v>
+        <v>26.89</v>
       </c>
       <c r="AG2">
-        <v>1427.31</v>
+        <v>1415.49</v>
       </c>
       <c r="AH2">
-        <v>1277</v>
+        <v>1280.78</v>
       </c>
       <c r="AI2">
         <v>1358.5</v>
@@ -987,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>46.27</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -998,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1600</v>
+        <v>1598.3</v>
       </c>
       <c r="D3">
-        <v>2.37</v>
+        <v>-0.11</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1010,43 +1009,43 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-21.38</v>
+        <v>-21.47</v>
       </c>
       <c r="H3">
-        <v>12.07</v>
+        <v>11.95</v>
       </c>
       <c r="I3">
-        <v>2.98</v>
+        <v>3.79</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>5.03</v>
       </c>
       <c r="K3">
-        <v>-10.38</v>
+        <v>-10.92</v>
       </c>
       <c r="L3">
-        <v>-15.35</v>
+        <v>-14.83</v>
       </c>
       <c r="M3">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P3">
-        <v>1561.6</v>
+        <v>1573.26</v>
       </c>
       <c r="Q3">
-        <v>1506.37</v>
+        <v>1510.79</v>
       </c>
       <c r="R3">
-        <v>1576.68</v>
+        <v>1575.41</v>
       </c>
       <c r="S3">
-        <v>1761.84</v>
+        <v>1760.12</v>
       </c>
       <c r="T3">
         <v>-9.19</v>
@@ -1064,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>57.78</v>
+        <v>57.51</v>
       </c>
       <c r="Z3">
-        <v>0.66</v>
+        <v>5.04</v>
       </c>
       <c r="AA3">
-        <v>-16.62</v>
+        <v>-12.29</v>
       </c>
       <c r="AB3">
-        <v>17.28</v>
+        <v>17.33</v>
       </c>
       <c r="AC3">
-        <v>96.75</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="AD3">
-        <v>90.83</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="AE3">
-        <v>42.39</v>
+        <v>41.5</v>
       </c>
       <c r="AF3">
-        <v>34.83</v>
+        <v>-63.54</v>
       </c>
       <c r="AG3">
-        <v>1605.89</v>
+        <v>1618.48</v>
       </c>
       <c r="AH3">
-        <v>1406.86</v>
+        <v>1403.1</v>
       </c>
       <c r="AI3">
-        <v>1457.39</v>
+        <v>1466.49</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>35.3</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1111,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>454.9</v>
+        <v>459.5</v>
       </c>
       <c r="D4">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1123,46 +1122,46 @@
         <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-33.69</v>
+        <v>-33.02</v>
       </c>
       <c r="H4">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="I4">
-        <v>-1.75</v>
+        <v>0.17</v>
       </c>
       <c r="J4">
-        <v>-8.93</v>
+        <v>-7.18</v>
       </c>
       <c r="K4">
-        <v>-6.23</v>
+        <v>-5.81</v>
       </c>
       <c r="L4">
-        <v>-22.52</v>
+        <v>-22.53</v>
       </c>
       <c r="M4">
-        <v>-7.55</v>
+        <v>-7.36</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P4">
-        <v>450</v>
+        <v>450.16</v>
       </c>
       <c r="Q4">
-        <v>469.56</v>
+        <v>467.81</v>
       </c>
       <c r="R4">
-        <v>492.34</v>
+        <v>491.52</v>
       </c>
       <c r="S4">
-        <v>550.46</v>
+        <v>549.58</v>
       </c>
       <c r="T4">
-        <v>-17.36</v>
+        <v>-16.39</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1177,34 +1176,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.94</v>
+        <v>41.92</v>
       </c>
       <c r="Z4">
-        <v>-11.84</v>
+        <v>-11.19</v>
       </c>
       <c r="AA4">
-        <v>-9.6</v>
+        <v>-9.92</v>
       </c>
       <c r="AB4">
-        <v>-2.24</v>
+        <v>-1.27</v>
       </c>
       <c r="AC4">
-        <v>17.64</v>
+        <v>35.09</v>
       </c>
       <c r="AD4">
-        <v>12.52</v>
+        <v>20.08</v>
       </c>
       <c r="AE4">
-        <v>14.02</v>
+        <v>13.69</v>
       </c>
       <c r="AF4">
-        <v>-24.17</v>
+        <v>-63.29</v>
       </c>
       <c r="AG4">
-        <v>501.96</v>
+        <v>498.25</v>
       </c>
       <c r="AH4">
-        <v>437.17</v>
+        <v>437.37</v>
       </c>
       <c r="AI4">
         <v>488.94</v>
@@ -1213,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>42.45</v>
+        <v>39.69</v>
       </c>
     </row>
   </sheetData>
@@ -1411,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.859999999999999</v>
+        <v>-6.62</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.62</v>
+        <v>-6.1</v>
       </c>
       <c r="E7" s="6">
-        <v>2.24</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1428,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-0.25</v>
+        <v>4.1</v>
       </c>
       <c r="D8" s="5">
-        <v>4.1</v>
+        <v>5.03</v>
       </c>
       <c r="E8" s="6">
-        <v>4.35</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1445,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-9.57</v>
+        <v>-8.93</v>
       </c>
       <c r="D9" s="5">
-        <v>-8.93</v>
+        <v>-7.18</v>
       </c>
       <c r="E9" s="6">
-        <v>0.64</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1462,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-1.79</v>
+        <v>0.39</v>
       </c>
       <c r="D10" s="5">
-        <v>0.39</v>
+        <v>3.13</v>
       </c>
       <c r="E10" s="6">
-        <v>2.18</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1479,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-0.89</v>
+        <v>2.98</v>
       </c>
       <c r="D11" s="5">
-        <v>2.98</v>
+        <v>3.79</v>
       </c>
       <c r="E11" s="6">
-        <v>3.87</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1496,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-3.54</v>
+        <v>-1.75</v>
       </c>
       <c r="D12" s="5">
-        <v>-1.75</v>
+        <v>0.17</v>
       </c>
       <c r="E12" s="6">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1513,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-3.6</v>
+        <v>-1.19</v>
       </c>
       <c r="D13" s="5">
-        <v>-1.19</v>
+        <v>-0.39</v>
       </c>
       <c r="E13" s="6">
-        <v>2.41</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1530,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-16.89</v>
+        <v>-15.35</v>
       </c>
       <c r="D14" s="5">
-        <v>-15.35</v>
+        <v>-14.83</v>
       </c>
       <c r="E14" s="6">
-        <v>1.54</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1547,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-23.21</v>
+        <v>-22.52</v>
       </c>
       <c r="D15" s="5">
-        <v>-22.52</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.6899999999999999</v>
+        <v>-22.53</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1564,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-7.14</v>
+        <v>-6.65</v>
       </c>
       <c r="D16" s="5">
-        <v>-6.65</v>
+        <v>-5.08</v>
       </c>
       <c r="E16" s="6">
-        <v>0.49</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1581,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-11.83</v>
+        <v>-10.38</v>
       </c>
       <c r="D17" s="5">
-        <v>-10.38</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1.45</v>
+        <v>-10.92</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1598,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-7.67</v>
+        <v>-6.23</v>
       </c>
       <c r="D18" s="5">
-        <v>-6.23</v>
+        <v>-5.81</v>
       </c>
       <c r="E18" s="6">
-        <v>1.44</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1615,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-10.42</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="D19" s="5">
-        <v>-8.960000000000001</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="E19" s="6">
-        <v>1.46</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1632,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-23.2</v>
+        <v>-21.38</v>
       </c>
       <c r="D20" s="5">
-        <v>-21.38</v>
-      </c>
-      <c r="E20" s="6">
-        <v>1.82</v>
+        <v>-21.47</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1649,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-34.69</v>
+        <v>-33.69</v>
       </c>
       <c r="D21" s="5">
-        <v>-33.69</v>
+        <v>-33.02</v>
       </c>
       <c r="E21" s="6">
-        <v>1</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1666,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1310.6</v>
+        <v>1332</v>
       </c>
       <c r="D22" s="5">
-        <v>1332</v>
+        <v>1342.8</v>
       </c>
       <c r="E22" s="6">
-        <v>21.4</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1683,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1563</v>
+        <v>1600</v>
       </c>
       <c r="D23" s="5">
-        <v>1600</v>
-      </c>
-      <c r="E23" s="6">
-        <v>37</v>
+        <v>1598.3</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1700,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>448.05</v>
+        <v>454.9</v>
       </c>
       <c r="D24" s="5">
-        <v>454.9</v>
+        <v>459.5</v>
       </c>
       <c r="E24" s="6">
-        <v>6.85</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1717,13 +1716,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>33.81</v>
+        <v>41.85</v>
       </c>
       <c r="D25" s="5">
-        <v>41.85</v>
+        <v>45.45</v>
       </c>
       <c r="E25" s="6">
-        <v>8.039999999999999</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1734,13 +1733,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>53.39</v>
+        <v>57.78</v>
       </c>
       <c r="D26" s="5">
-        <v>57.78</v>
-      </c>
-      <c r="E26" s="6">
-        <v>4.39</v>
+        <v>57.51</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1751,13 +1750,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>34.29</v>
+        <v>38.94</v>
       </c>
       <c r="D27" s="5">
-        <v>38.94</v>
+        <v>41.92</v>
       </c>
       <c r="E27" s="6">
-        <v>4.65</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1768,13 +1767,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>39.93</v>
+        <v>40.83</v>
       </c>
       <c r="D28" s="5">
-        <v>40.83</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0.9</v>
+        <v>26.89</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-13.94</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1785,13 +1784,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>39.63</v>
+        <v>34.83</v>
       </c>
       <c r="D29" s="5">
-        <v>34.83</v>
+        <v>-63.54</v>
       </c>
       <c r="E29" s="7">
-        <v>-4.8</v>
+        <v>-98.37</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1802,13 +1801,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-23.63</v>
+        <v>-24.17</v>
       </c>
       <c r="D30" s="5">
-        <v>-24.17</v>
+        <v>-63.29</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.54</v>
+        <v>-39.12</v>
       </c>
     </row>
   </sheetData>
@@ -1873,16 +1872,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>46.2</v>
+        <v>48.3</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-3.8</v>
+        <v>-2.8</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.8</v>
+        <v>-7.3</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2001,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1452</v>
+        <v>0.1496</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0139</v>
+        <v>0.013</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0755</v>
+        <v>-0.0736</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1342.8</v>
+        <v>1357.5</v>
       </c>
       <c r="D2">
-        <v>0.8100000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,46 +896,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-8.220000000000001</v>
+        <v>-7.22</v>
       </c>
       <c r="H2">
-        <v>11.35</v>
+        <v>12.57</v>
       </c>
       <c r="I2">
-        <v>3.13</v>
+        <v>5.05</v>
       </c>
       <c r="J2">
-        <v>-6.1</v>
+        <v>-4.62</v>
       </c>
       <c r="K2">
-        <v>-5.08</v>
+        <v>-1.67</v>
       </c>
       <c r="L2">
-        <v>-0.39</v>
+        <v>-1.06</v>
       </c>
       <c r="M2">
-        <v>14.96</v>
+        <v>14.79</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="P2">
-        <v>1319.86</v>
+        <v>1332.92</v>
       </c>
       <c r="Q2">
-        <v>1348.14</v>
+        <v>1344.64</v>
       </c>
       <c r="R2">
-        <v>1397.46</v>
+        <v>1395.69</v>
       </c>
       <c r="S2">
-        <v>1352.76</v>
+        <v>1352.78</v>
       </c>
       <c r="T2">
-        <v>-0.74</v>
+        <v>0.35</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,37 +947,37 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>45.45</v>
+        <v>49.99</v>
       </c>
       <c r="Z2">
-        <v>-22.84</v>
+        <v>-19.23</v>
       </c>
       <c r="AA2">
-        <v>-23.91</v>
+        <v>-22.98</v>
       </c>
       <c r="AB2">
-        <v>1.07</v>
+        <v>3.75</v>
       </c>
       <c r="AC2">
-        <v>92.28</v>
+        <v>100</v>
       </c>
       <c r="AD2">
-        <v>77.98999999999999</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="AE2">
-        <v>22.07</v>
+        <v>22.65</v>
       </c>
       <c r="AF2">
-        <v>26.89</v>
+        <v>52.36</v>
       </c>
       <c r="AG2">
-        <v>1415.49</v>
+        <v>1401</v>
       </c>
       <c r="AH2">
-        <v>1280.78</v>
+        <v>1288.27</v>
       </c>
       <c r="AI2">
         <v>1358.5</v>
@@ -986,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>40.84</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1598.3</v>
+        <v>1590</v>
       </c>
       <c r="D3">
-        <v>-0.11</v>
+        <v>-0.52</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-21.47</v>
+        <v>-21.87</v>
       </c>
       <c r="H3">
-        <v>11.95</v>
+        <v>11.37</v>
       </c>
       <c r="I3">
-        <v>3.79</v>
+        <v>4.95</v>
       </c>
       <c r="J3">
-        <v>5.03</v>
+        <v>5.3</v>
       </c>
       <c r="K3">
-        <v>-10.92</v>
+        <v>-11.87</v>
       </c>
       <c r="L3">
-        <v>-14.83</v>
+        <v>-15.88</v>
       </c>
       <c r="M3">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P3">
-        <v>1573.26</v>
+        <v>1588.26</v>
       </c>
       <c r="Q3">
-        <v>1510.79</v>
+        <v>1515.62</v>
       </c>
       <c r="R3">
-        <v>1575.41</v>
+        <v>1573.59</v>
       </c>
       <c r="S3">
-        <v>1760.12</v>
+        <v>1758.37</v>
       </c>
       <c r="T3">
-        <v>-9.19</v>
+        <v>-9.58</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>57.51</v>
+        <v>56.14</v>
       </c>
       <c r="Z3">
-        <v>5.04</v>
+        <v>7.75</v>
       </c>
       <c r="AA3">
-        <v>-12.29</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AB3">
-        <v>17.33</v>
+        <v>16.03</v>
       </c>
       <c r="AC3">
-        <v>96.51000000000001</v>
+        <v>97.59</v>
       </c>
       <c r="AD3">
-        <v>93.98999999999999</v>
+        <v>96.95</v>
       </c>
       <c r="AE3">
-        <v>41.5</v>
+        <v>40.42</v>
       </c>
       <c r="AF3">
-        <v>-63.54</v>
+        <v>-3.3</v>
       </c>
       <c r="AG3">
-        <v>1618.48</v>
+        <v>1628.56</v>
       </c>
       <c r="AH3">
-        <v>1403.1</v>
+        <v>1402.68</v>
       </c>
       <c r="AI3">
-        <v>1466.49</v>
+        <v>1466.53</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>35.5</v>
+        <v>35.44</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>459.5</v>
+        <v>457.5</v>
       </c>
       <c r="D4">
-        <v>1.01</v>
+        <v>-0.44</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1122,25 +1122,25 @@
         <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-33.02</v>
+        <v>-33.32</v>
       </c>
       <c r="H4">
-        <v>3.54</v>
+        <v>3.09</v>
       </c>
       <c r="I4">
-        <v>0.17</v>
+        <v>2.91</v>
       </c>
       <c r="J4">
-        <v>-7.18</v>
+        <v>-7.49</v>
       </c>
       <c r="K4">
-        <v>-5.81</v>
+        <v>-4.7</v>
       </c>
       <c r="L4">
-        <v>-22.53</v>
+        <v>-23.05</v>
       </c>
       <c r="M4">
-        <v>-7.36</v>
+        <v>-7.52</v>
       </c>
       <c r="N4">
         <v>34</v>
@@ -1149,19 +1149,19 @@
         <v>36</v>
       </c>
       <c r="P4">
-        <v>450.16</v>
+        <v>452.75</v>
       </c>
       <c r="Q4">
-        <v>467.81</v>
+        <v>467.15</v>
       </c>
       <c r="R4">
-        <v>491.52</v>
+        <v>490.47</v>
       </c>
       <c r="S4">
-        <v>549.58</v>
+        <v>548.72</v>
       </c>
       <c r="T4">
-        <v>-16.39</v>
+        <v>-16.62</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1176,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>41.92</v>
+        <v>40.98</v>
       </c>
       <c r="Z4">
-        <v>-11.19</v>
+        <v>-10.71</v>
       </c>
       <c r="AA4">
-        <v>-9.92</v>
+        <v>-10.07</v>
       </c>
       <c r="AB4">
-        <v>-1.27</v>
+        <v>-0.63</v>
       </c>
       <c r="AC4">
-        <v>35.09</v>
+        <v>46.06</v>
       </c>
       <c r="AD4">
-        <v>20.08</v>
+        <v>32.93</v>
       </c>
       <c r="AE4">
-        <v>13.69</v>
+        <v>13.12</v>
       </c>
       <c r="AF4">
-        <v>-63.29</v>
+        <v>-48.49</v>
       </c>
       <c r="AG4">
-        <v>498.25</v>
+        <v>497.9</v>
       </c>
       <c r="AH4">
-        <v>437.37</v>
+        <v>436.41</v>
       </c>
       <c r="AI4">
         <v>488.94</v>
@@ -1212,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>39.69</v>
+        <v>37.3</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.62</v>
+        <v>-6.1</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.1</v>
+        <v>-4.62</v>
       </c>
       <c r="E7" s="6">
-        <v>0.52</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>4.1</v>
+        <v>5.03</v>
       </c>
       <c r="D8" s="5">
-        <v>5.03</v>
+        <v>5.3</v>
       </c>
       <c r="E8" s="6">
-        <v>0.93</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-8.93</v>
+        <v>-7.18</v>
       </c>
       <c r="D9" s="5">
-        <v>-7.18</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1.75</v>
+        <v>-7.49</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>0.39</v>
+        <v>3.13</v>
       </c>
       <c r="D10" s="5">
-        <v>3.13</v>
+        <v>5.05</v>
       </c>
       <c r="E10" s="6">
-        <v>2.74</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>2.98</v>
+        <v>3.79</v>
       </c>
       <c r="D11" s="5">
-        <v>3.79</v>
+        <v>4.95</v>
       </c>
       <c r="E11" s="6">
-        <v>0.8100000000000001</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-1.75</v>
+        <v>0.17</v>
       </c>
       <c r="D12" s="5">
-        <v>0.17</v>
+        <v>2.91</v>
       </c>
       <c r="E12" s="6">
-        <v>1.92</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-1.19</v>
+        <v>-0.39</v>
       </c>
       <c r="D13" s="5">
-        <v>-0.39</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.8</v>
+        <v>-1.06</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-15.35</v>
+        <v>-14.83</v>
       </c>
       <c r="D14" s="5">
-        <v>-14.83</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.52</v>
+        <v>-15.88</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-22.52</v>
+        <v>-22.53</v>
       </c>
       <c r="D15" s="5">
-        <v>-22.53</v>
+        <v>-23.05</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.01</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.65</v>
+        <v>-5.08</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.08</v>
+        <v>-1.67</v>
       </c>
       <c r="E16" s="6">
-        <v>1.57</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-10.38</v>
+        <v>-10.92</v>
       </c>
       <c r="D17" s="5">
-        <v>-10.92</v>
+        <v>-11.87</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.54</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-6.23</v>
+        <v>-5.81</v>
       </c>
       <c r="D18" s="5">
-        <v>-5.81</v>
+        <v>-4.7</v>
       </c>
       <c r="E18" s="6">
-        <v>0.42</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-8.960000000000001</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="D19" s="5">
-        <v>-8.220000000000001</v>
+        <v>-7.22</v>
       </c>
       <c r="E19" s="6">
-        <v>0.74</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-21.38</v>
+        <v>-21.47</v>
       </c>
       <c r="D20" s="5">
-        <v>-21.47</v>
+        <v>-21.87</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.09</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-33.69</v>
+        <v>-33.02</v>
       </c>
       <c r="D21" s="5">
-        <v>-33.02</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.67</v>
+        <v>-33.32</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1332</v>
+        <v>1342.8</v>
       </c>
       <c r="D22" s="5">
-        <v>1342.8</v>
+        <v>1357.5</v>
       </c>
       <c r="E22" s="6">
-        <v>10.8</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1600</v>
+        <v>1598.3</v>
       </c>
       <c r="D23" s="5">
-        <v>1598.3</v>
+        <v>1590</v>
       </c>
       <c r="E23" s="7">
-        <v>-1.7</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>454.9</v>
+        <v>459.5</v>
       </c>
       <c r="D24" s="5">
-        <v>459.5</v>
-      </c>
-      <c r="E24" s="6">
-        <v>4.6</v>
+        <v>457.5</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1716,13 +1716,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>41.85</v>
+        <v>45.45</v>
       </c>
       <c r="D25" s="5">
-        <v>45.45</v>
+        <v>49.99</v>
       </c>
       <c r="E25" s="6">
-        <v>3.6</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1733,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>57.78</v>
+        <v>57.51</v>
       </c>
       <c r="D26" s="5">
-        <v>57.51</v>
+        <v>56.14</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.27</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1750,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>38.94</v>
+        <v>41.92</v>
       </c>
       <c r="D27" s="5">
-        <v>41.92</v>
-      </c>
-      <c r="E27" s="6">
-        <v>2.98</v>
+        <v>40.98</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1767,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>40.83</v>
+        <v>26.89</v>
       </c>
       <c r="D28" s="5">
-        <v>26.89</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-13.94</v>
+        <v>52.36</v>
+      </c>
+      <c r="E28" s="6">
+        <v>25.47</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1784,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>34.83</v>
+        <v>-63.54</v>
       </c>
       <c r="D29" s="5">
-        <v>-63.54</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-98.37</v>
+        <v>-3.3</v>
+      </c>
+      <c r="E29" s="6">
+        <v>60.24</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1801,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-24.17</v>
+        <v>-63.29</v>
       </c>
       <c r="D30" s="5">
-        <v>-63.29</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-39.12</v>
+        <v>-48.49</v>
+      </c>
+      <c r="E30" s="6">
+        <v>14.8</v>
       </c>
     </row>
   </sheetData>
@@ -1866,22 +1866,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="10">
-        <v>36.52</v>
+        <v>48.52</v>
       </c>
       <c r="C2" s="11">
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>48.3</v>
+        <v>49</v>
       </c>
       <c r="E2" s="10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2" s="10">
-        <v>-2.8</v>
+        <v>-2.3</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.3</v>
+        <v>-6.1</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1496</v>
+        <v>0.1479</v>
       </c>
       <c r="B2" s="13">
-        <v>0.013</v>
+        <v>0.0126</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0736</v>
+        <v>-0.07519999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1357.5</v>
+        <v>1349</v>
       </c>
       <c r="D2">
-        <v>1.09</v>
+        <v>-0.63</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,46 +896,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-7.22</v>
+        <v>-7.8</v>
       </c>
       <c r="H2">
-        <v>12.57</v>
+        <v>11.87</v>
       </c>
       <c r="I2">
-        <v>5.05</v>
+        <v>2.07</v>
       </c>
       <c r="J2">
-        <v>-4.62</v>
+        <v>-5.5</v>
       </c>
       <c r="K2">
-        <v>-1.67</v>
+        <v>-2.3</v>
       </c>
       <c r="L2">
-        <v>-1.06</v>
+        <v>-1.19</v>
       </c>
       <c r="M2">
-        <v>14.79</v>
+        <v>14.61</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>1332.92</v>
+        <v>1338.38</v>
       </c>
       <c r="Q2">
-        <v>1344.64</v>
+        <v>1342.12</v>
       </c>
       <c r="R2">
-        <v>1395.69</v>
+        <v>1394.06</v>
       </c>
       <c r="S2">
-        <v>1352.78</v>
+        <v>1352.75</v>
       </c>
       <c r="T2">
-        <v>0.35</v>
+        <v>-0.28</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,37 +947,37 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>49.99</v>
+        <v>47.52</v>
       </c>
       <c r="Z2">
-        <v>-19.23</v>
+        <v>-16.86</v>
       </c>
       <c r="AA2">
-        <v>-22.98</v>
+        <v>-21.75</v>
       </c>
       <c r="AB2">
-        <v>3.75</v>
+        <v>4.89</v>
       </c>
       <c r="AC2">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AD2">
-        <v>93.26000000000001</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="AE2">
-        <v>22.65</v>
+        <v>22.52</v>
       </c>
       <c r="AF2">
-        <v>52.36</v>
+        <v>11.84</v>
       </c>
       <c r="AG2">
-        <v>1401</v>
+        <v>1392.34</v>
       </c>
       <c r="AH2">
-        <v>1288.27</v>
+        <v>1291.89</v>
       </c>
       <c r="AI2">
         <v>1358.5</v>
@@ -986,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>38.86</v>
+        <v>37.27</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1590</v>
+        <v>1624</v>
       </c>
       <c r="D3">
-        <v>-0.52</v>
+        <v>2.14</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-21.87</v>
+        <v>-20.2</v>
       </c>
       <c r="H3">
-        <v>11.37</v>
+        <v>13.75</v>
       </c>
       <c r="I3">
-        <v>4.95</v>
+        <v>2.14</v>
       </c>
       <c r="J3">
-        <v>5.3</v>
+        <v>8.75</v>
       </c>
       <c r="K3">
-        <v>-11.87</v>
+        <v>-9.51</v>
       </c>
       <c r="L3">
-        <v>-15.88</v>
+        <v>-14.45</v>
       </c>
       <c r="M3">
-        <v>1.26</v>
+        <v>1.95</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="P3">
-        <v>1588.26</v>
+        <v>1595.06</v>
       </c>
       <c r="Q3">
-        <v>1515.62</v>
+        <v>1522.6</v>
       </c>
       <c r="R3">
-        <v>1573.59</v>
+        <v>1572.39</v>
       </c>
       <c r="S3">
-        <v>1758.37</v>
+        <v>1756.78</v>
       </c>
       <c r="T3">
-        <v>-9.58</v>
+        <v>-7.56</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>56.14</v>
+        <v>60.31</v>
       </c>
       <c r="Z3">
-        <v>7.75</v>
+        <v>12.5</v>
       </c>
       <c r="AA3">
-        <v>-8.279999999999999</v>
+        <v>-4.13</v>
       </c>
       <c r="AB3">
-        <v>16.03</v>
+        <v>16.63</v>
       </c>
       <c r="AC3">
         <v>97.59</v>
       </c>
       <c r="AD3">
-        <v>96.95</v>
+        <v>97.23</v>
       </c>
       <c r="AE3">
-        <v>40.42</v>
+        <v>40.34</v>
       </c>
       <c r="AF3">
-        <v>-3.3</v>
+        <v>-1.35</v>
       </c>
       <c r="AG3">
-        <v>1628.56</v>
+        <v>1644.33</v>
       </c>
       <c r="AH3">
-        <v>1402.68</v>
+        <v>1400.87</v>
       </c>
       <c r="AI3">
-        <v>1466.53</v>
+        <v>1487.92</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>35.44</v>
+        <v>37.33</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>457.5</v>
+        <v>457</v>
       </c>
       <c r="D4">
-        <v>-0.44</v>
+        <v>-0.11</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1122,46 +1122,46 @@
         <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-33.32</v>
+        <v>-33.39</v>
       </c>
       <c r="H4">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="I4">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="J4">
-        <v>-7.49</v>
+        <v>-2.9</v>
       </c>
       <c r="K4">
-        <v>-4.7</v>
+        <v>-6.87</v>
       </c>
       <c r="L4">
-        <v>-23.05</v>
+        <v>-23.71</v>
       </c>
       <c r="M4">
-        <v>-7.52</v>
+        <v>-6.95</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P4">
-        <v>452.75</v>
+        <v>455.39</v>
       </c>
       <c r="Q4">
-        <v>467.15</v>
+        <v>466.54</v>
       </c>
       <c r="R4">
-        <v>490.47</v>
+        <v>489.41</v>
       </c>
       <c r="S4">
-        <v>548.72</v>
+        <v>547.79</v>
       </c>
       <c r="T4">
-        <v>-16.62</v>
+        <v>-16.57</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1176,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.98</v>
+        <v>40.74</v>
       </c>
       <c r="Z4">
-        <v>-10.71</v>
+        <v>-10.25</v>
       </c>
       <c r="AA4">
-        <v>-10.07</v>
+        <v>-10.11</v>
       </c>
       <c r="AB4">
-        <v>-0.63</v>
+        <v>-0.14</v>
       </c>
       <c r="AC4">
-        <v>46.06</v>
+        <v>48.99</v>
       </c>
       <c r="AD4">
-        <v>32.93</v>
+        <v>43.38</v>
       </c>
       <c r="AE4">
-        <v>13.12</v>
+        <v>12.85</v>
       </c>
       <c r="AF4">
-        <v>-48.49</v>
+        <v>-9.68</v>
       </c>
       <c r="AG4">
-        <v>497.9</v>
+        <v>497.59</v>
       </c>
       <c r="AH4">
-        <v>436.41</v>
+        <v>435.48</v>
       </c>
       <c r="AI4">
         <v>488.94</v>
@@ -1212,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>37.3</v>
+        <v>36.51</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.1</v>
+        <v>-4.62</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.62</v>
+        <v>-5.5</v>
       </c>
       <c r="E7" s="6">
-        <v>1.48</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>5.03</v>
+        <v>5.3</v>
       </c>
       <c r="D8" s="5">
-        <v>5.3</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0.27</v>
+        <v>8.75</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3.45</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-7.18</v>
+        <v>-7.49</v>
       </c>
       <c r="D9" s="5">
-        <v>-7.49</v>
+        <v>-2.9</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.31</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>3.13</v>
+        <v>5.05</v>
       </c>
       <c r="D10" s="5">
-        <v>5.05</v>
+        <v>2.07</v>
       </c>
       <c r="E10" s="6">
-        <v>1.92</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>3.79</v>
+        <v>4.95</v>
       </c>
       <c r="D11" s="5">
-        <v>4.95</v>
+        <v>2.14</v>
       </c>
       <c r="E11" s="6">
-        <v>1.16</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>0.17</v>
+        <v>2.91</v>
       </c>
       <c r="D12" s="5">
-        <v>2.91</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2.74</v>
+        <v>2.97</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-0.39</v>
+        <v>-1.06</v>
       </c>
       <c r="D13" s="5">
-        <v>-1.06</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.67</v>
+        <v>-1.19</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-14.83</v>
+        <v>-15.88</v>
       </c>
       <c r="D14" s="5">
-        <v>-15.88</v>
+        <v>-14.45</v>
       </c>
       <c r="E14" s="7">
-        <v>-1.05</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-22.53</v>
+        <v>-23.05</v>
       </c>
       <c r="D15" s="5">
-        <v>-23.05</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.52</v>
+        <v>-23.71</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-5.08</v>
+        <v>-1.67</v>
       </c>
       <c r="D16" s="5">
-        <v>-1.67</v>
+        <v>-2.3</v>
       </c>
       <c r="E16" s="6">
-        <v>3.41</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-10.92</v>
+        <v>-11.87</v>
       </c>
       <c r="D17" s="5">
-        <v>-11.87</v>
+        <v>-9.51</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.95</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-5.81</v>
+        <v>-4.7</v>
       </c>
       <c r="D18" s="5">
-        <v>-4.7</v>
+        <v>-6.87</v>
       </c>
       <c r="E18" s="6">
-        <v>1.11</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-8.220000000000001</v>
+        <v>-7.22</v>
       </c>
       <c r="D19" s="5">
-        <v>-7.22</v>
+        <v>-7.8</v>
       </c>
       <c r="E19" s="6">
-        <v>1</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-21.47</v>
+        <v>-21.87</v>
       </c>
       <c r="D20" s="5">
-        <v>-21.87</v>
+        <v>-20.2</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.4</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-33.02</v>
+        <v>-33.32</v>
       </c>
       <c r="D21" s="5">
-        <v>-33.32</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.3</v>
+        <v>-33.39</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1342.8</v>
+        <v>1357.5</v>
       </c>
       <c r="D22" s="5">
-        <v>1357.5</v>
+        <v>1349</v>
       </c>
       <c r="E22" s="6">
-        <v>14.7</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1598.3</v>
+        <v>1590</v>
       </c>
       <c r="D23" s="5">
-        <v>1590</v>
+        <v>1624</v>
       </c>
       <c r="E23" s="7">
-        <v>-8.300000000000001</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>459.5</v>
+        <v>457.5</v>
       </c>
       <c r="D24" s="5">
-        <v>457.5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2</v>
+        <v>457</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1716,13 +1716,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>45.45</v>
+        <v>49.99</v>
       </c>
       <c r="D25" s="5">
-        <v>49.99</v>
+        <v>47.52</v>
       </c>
       <c r="E25" s="6">
-        <v>4.54</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1733,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>57.51</v>
+        <v>56.14</v>
       </c>
       <c r="D26" s="5">
-        <v>56.14</v>
+        <v>60.31</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.37</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1750,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>41.92</v>
+        <v>40.98</v>
       </c>
       <c r="D27" s="5">
-        <v>40.98</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.9399999999999999</v>
+        <v>40.74</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1767,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>26.89</v>
+        <v>52.36</v>
       </c>
       <c r="D28" s="5">
-        <v>52.36</v>
+        <v>11.84</v>
       </c>
       <c r="E28" s="6">
-        <v>25.47</v>
+        <v>-40.52</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1784,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-63.54</v>
+        <v>-3.3</v>
       </c>
       <c r="D29" s="5">
-        <v>-3.3</v>
-      </c>
-      <c r="E29" s="6">
-        <v>60.24</v>
+        <v>-1.35</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.95</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1801,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-63.29</v>
+        <v>-48.49</v>
       </c>
       <c r="D30" s="5">
-        <v>-48.49</v>
-      </c>
-      <c r="E30" s="6">
-        <v>14.8</v>
+        <v>-9.68</v>
+      </c>
+      <c r="E30" s="7">
+        <v>38.81</v>
       </c>
     </row>
   </sheetData>
@@ -1866,22 +1866,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="10">
-        <v>48.52</v>
+        <v>36.52</v>
       </c>
       <c r="C2" s="11">
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="E2" s="10">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-2.3</v>
+        <v>0.1</v>
       </c>
       <c r="G2" s="10">
-        <v>-6.1</v>
+        <v>-6.2</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1479</v>
+        <v>0.1461</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0126</v>
+        <v>0.0195</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.07519999999999999</v>
+        <v>-0.06950000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="57">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,16 +166,7 @@
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -206,13 +197,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,22 +233,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,24 +250,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,33 +319,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1353,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1386,428 +1337,8 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-4.62</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-5.5</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>5.3</v>
-      </c>
-      <c r="D8" s="5">
-        <v>8.75</v>
-      </c>
-      <c r="E8" s="7">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-7.49</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-2.9</v>
-      </c>
-      <c r="E9" s="7">
-        <v>4.59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5">
-        <v>5.05</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2.07</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-2.98</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>4.95</v>
-      </c>
-      <c r="D11" s="5">
-        <v>2.14</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>2.91</v>
-      </c>
-      <c r="D12" s="5">
-        <v>2.97</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-1.06</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-1.19</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-15.88</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-14.45</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-23.05</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-23.71</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-1.67</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-2.3</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-11.87</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-9.51</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-4.7</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-6.87</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-7.22</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-7.8</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-21.87</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-20.2</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-33.32</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-33.39</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1357.5</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1349</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-8.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1590</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1624</v>
-      </c>
-      <c r="E23" s="7">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>457.5</v>
-      </c>
-      <c r="D24" s="5">
-        <v>457</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5">
-        <v>49.99</v>
-      </c>
-      <c r="D25" s="5">
-        <v>47.52</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5">
-        <v>56.14</v>
-      </c>
-      <c r="D26" s="5">
-        <v>60.31</v>
-      </c>
-      <c r="E26" s="7">
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>40.98</v>
-      </c>
-      <c r="D27" s="5">
-        <v>40.74</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="5">
-        <v>52.36</v>
-      </c>
-      <c r="D28" s="5">
-        <v>11.84</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-40.52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-3.3</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-1.35</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-48.49</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-9.68</v>
-      </c>
-      <c r="E30" s="7">
-        <v>38.81</v>
       </c>
     </row>
   </sheetData>
@@ -1833,60 +1364,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="F1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="G1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="H1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="6">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="7">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="6">
         <v>49.5</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="6">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="6">
         <v>0.1</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="6">
         <v>-6.2</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="6">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1988,24 +1519,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
+      <c r="A2" s="9">
         <v>0.1461</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="9">
         <v>0.0195</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="9">
         <v>-0.06950000000000001</v>
       </c>
     </row>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,16 @@
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -197,11 +206,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,8 +244,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -250,6 +275,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -319,27 +362,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -835,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="D2">
-        <v>-0.63</v>
+        <v>0.44</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -847,25 +896,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-7.8</v>
+        <v>-7.39</v>
       </c>
       <c r="H2">
-        <v>11.87</v>
+        <v>12.36</v>
       </c>
       <c r="I2">
-        <v>2.07</v>
+        <v>3.39</v>
       </c>
       <c r="J2">
-        <v>-5.5</v>
+        <v>-3.17</v>
       </c>
       <c r="K2">
-        <v>-2.3</v>
+        <v>-3.3</v>
       </c>
       <c r="L2">
-        <v>-1.19</v>
+        <v>-0.62</v>
       </c>
       <c r="M2">
-        <v>14.61</v>
+        <v>14.41</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -874,19 +923,19 @@
         <v>63</v>
       </c>
       <c r="P2">
-        <v>1338.38</v>
+        <v>1347.26</v>
       </c>
       <c r="Q2">
-        <v>1342.12</v>
+        <v>1340.41</v>
       </c>
       <c r="R2">
-        <v>1394.06</v>
+        <v>1392.4</v>
       </c>
       <c r="S2">
         <v>1352.75</v>
       </c>
       <c r="T2">
-        <v>-0.28</v>
+        <v>0.17</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -898,37 +947,37 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>47.52</v>
+        <v>49.42</v>
       </c>
       <c r="Z2">
-        <v>-16.86</v>
+        <v>-14.33</v>
       </c>
       <c r="AA2">
-        <v>-21.75</v>
+        <v>-20.27</v>
       </c>
       <c r="AB2">
-        <v>4.89</v>
+        <v>5.94</v>
       </c>
       <c r="AC2">
-        <v>97</v>
+        <v>96.31</v>
       </c>
       <c r="AD2">
-        <v>96.43000000000001</v>
+        <v>97.77</v>
       </c>
       <c r="AE2">
-        <v>22.52</v>
+        <v>22.13</v>
       </c>
       <c r="AF2">
-        <v>11.84</v>
+        <v>-46.2</v>
       </c>
       <c r="AG2">
-        <v>1392.34</v>
+        <v>1386.03</v>
       </c>
       <c r="AH2">
-        <v>1291.89</v>
+        <v>1294.79</v>
       </c>
       <c r="AI2">
         <v>1358.5</v>
@@ -937,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>37.27</v>
+        <v>35.88</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -948,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1624</v>
+        <v>1690.2</v>
       </c>
       <c r="D3">
-        <v>2.14</v>
+        <v>4.08</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -960,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-20.2</v>
+        <v>-16.95</v>
       </c>
       <c r="H3">
-        <v>13.75</v>
+        <v>18.39</v>
       </c>
       <c r="I3">
-        <v>2.14</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="J3">
-        <v>8.75</v>
+        <v>13.86</v>
       </c>
       <c r="K3">
-        <v>-9.51</v>
+        <v>-7.45</v>
       </c>
       <c r="L3">
-        <v>-14.45</v>
+        <v>-11.61</v>
       </c>
       <c r="M3">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="P3">
-        <v>1595.06</v>
+        <v>1620.5</v>
       </c>
       <c r="Q3">
-        <v>1522.6</v>
+        <v>1533.41</v>
       </c>
       <c r="R3">
-        <v>1572.39</v>
+        <v>1573.22</v>
       </c>
       <c r="S3">
-        <v>1756.78</v>
+        <v>1755.49</v>
       </c>
       <c r="T3">
-        <v>-7.56</v>
+        <v>-3.72</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1014,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>60.31</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Z3">
-        <v>12.5</v>
+        <v>21.36</v>
       </c>
       <c r="AA3">
-        <v>-4.13</v>
+        <v>0.97</v>
       </c>
       <c r="AB3">
-        <v>16.63</v>
+        <v>20.39</v>
       </c>
       <c r="AC3">
-        <v>97.59</v>
+        <v>97.83</v>
       </c>
       <c r="AD3">
-        <v>97.23</v>
+        <v>97.67</v>
       </c>
       <c r="AE3">
-        <v>40.34</v>
+        <v>43.13</v>
       </c>
       <c r="AF3">
-        <v>-1.35</v>
+        <v>66.2</v>
       </c>
       <c r="AG3">
-        <v>1644.33</v>
+        <v>1673.92</v>
       </c>
       <c r="AH3">
-        <v>1400.87</v>
+        <v>1392.9</v>
       </c>
       <c r="AI3">
-        <v>1487.92</v>
+        <v>1530.3</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>37.33</v>
+        <v>41.64</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1061,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>457</v>
+        <v>460.55</v>
       </c>
       <c r="D4">
-        <v>-0.11</v>
+        <v>0.78</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1073,46 +1122,46 @@
         <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-33.39</v>
+        <v>-32.87</v>
       </c>
       <c r="H4">
-        <v>2.97</v>
+        <v>3.77</v>
       </c>
       <c r="I4">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="J4">
-        <v>-2.9</v>
+        <v>-1.86</v>
       </c>
       <c r="K4">
-        <v>-6.87</v>
+        <v>-9.76</v>
       </c>
       <c r="L4">
-        <v>-23.71</v>
+        <v>-23.03</v>
       </c>
       <c r="M4">
-        <v>-6.95</v>
+        <v>-6.85</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P4">
-        <v>455.39</v>
+        <v>457.89</v>
       </c>
       <c r="Q4">
-        <v>466.54</v>
+        <v>466.44</v>
       </c>
       <c r="R4">
-        <v>489.41</v>
+        <v>488.39</v>
       </c>
       <c r="S4">
-        <v>547.79</v>
+        <v>546.85</v>
       </c>
       <c r="T4">
-        <v>-16.57</v>
+        <v>-15.78</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1127,34 +1176,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.74</v>
+        <v>43.32</v>
       </c>
       <c r="Z4">
-        <v>-10.25</v>
+        <v>-9.49</v>
       </c>
       <c r="AA4">
-        <v>-10.11</v>
+        <v>-9.98</v>
       </c>
       <c r="AB4">
-        <v>-0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AC4">
-        <v>48.99</v>
+        <v>51.3</v>
       </c>
       <c r="AD4">
-        <v>43.38</v>
+        <v>48.78</v>
       </c>
       <c r="AE4">
-        <v>12.85</v>
+        <v>12.77</v>
       </c>
       <c r="AF4">
-        <v>-9.68</v>
+        <v>-58.41</v>
       </c>
       <c r="AG4">
-        <v>497.59</v>
+        <v>497.56</v>
       </c>
       <c r="AH4">
-        <v>435.48</v>
+        <v>435.32</v>
       </c>
       <c r="AI4">
         <v>488.94</v>
@@ -1163,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>36.51</v>
+        <v>33.05</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1337,8 +1386,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-5.5</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-3.17</v>
+      </c>
+      <c r="E7" s="6">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>8.75</v>
+      </c>
+      <c r="D8" s="5">
+        <v>13.86</v>
+      </c>
+      <c r="E8" s="6">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-2.9</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-1.86</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2.07</v>
+      </c>
+      <c r="D10" s="5">
+        <v>3.39</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2.14</v>
+      </c>
+      <c r="D11" s="5">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="E11" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2.97</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2.79</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-1.19</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.62</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-14.45</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-11.61</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-23.71</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-23.03</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.3</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.3</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-9.51</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-7.45</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-6.87</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-9.76</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-7.8</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-7.39</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-20.2</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-16.95</v>
+      </c>
+      <c r="E20" s="6">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-33.39</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-32.87</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1349</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1355</v>
+      </c>
+      <c r="E22" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1624</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1690.2</v>
+      </c>
+      <c r="E23" s="6">
+        <v>66.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>457</v>
+      </c>
+      <c r="D24" s="5">
+        <v>460.55</v>
+      </c>
+      <c r="E24" s="6">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>47.52</v>
+      </c>
+      <c r="D25" s="5">
+        <v>49.42</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>60.31</v>
+      </c>
+      <c r="D26" s="5">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="E26" s="6">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>40.74</v>
+      </c>
+      <c r="D27" s="5">
+        <v>43.32</v>
+      </c>
+      <c r="E27" s="6">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>11.84</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-46.2</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-58.04</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-1.35</v>
+      </c>
+      <c r="D29" s="5">
+        <v>66.2</v>
+      </c>
+      <c r="E29" s="6">
+        <v>67.55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-9.68</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-58.41</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-48.73</v>
       </c>
     </row>
   </sheetData>
@@ -1364,60 +1833,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="B1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="D1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="F1" s="8" t="s">
         <v>56</v>
       </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="6">
-        <v>36.52</v>
-      </c>
-      <c r="C2" s="7">
+      <c r="B2" s="10">
+        <v>48.52</v>
+      </c>
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="6">
-        <v>49.5</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-6.2</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="D2" s="10">
+        <v>53.2</v>
+      </c>
+      <c r="E2" s="10">
+        <v>30</v>
+      </c>
+      <c r="F2" s="10">
+        <v>2.9</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-6.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1519,25 +1988,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="9">
-        <v>0.1461</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.0195</v>
-      </c>
-      <c r="C2" s="9">
-        <v>-0.06950000000000001</v>
+      <c r="A2" s="13">
+        <v>0.1441</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0267</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.06849999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1355</v>
+        <v>1340</v>
       </c>
       <c r="D2">
-        <v>0.44</v>
+        <v>-1.11</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,46 +896,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-7.39</v>
+        <v>-8.41</v>
       </c>
       <c r="H2">
-        <v>12.36</v>
+        <v>11.12</v>
       </c>
       <c r="I2">
-        <v>3.39</v>
+        <v>0.6</v>
       </c>
       <c r="J2">
-        <v>-3.17</v>
+        <v>-3.53</v>
       </c>
       <c r="K2">
-        <v>-3.3</v>
+        <v>-4.93</v>
       </c>
       <c r="L2">
-        <v>-0.62</v>
+        <v>-2.61</v>
       </c>
       <c r="M2">
-        <v>14.41</v>
+        <v>14.29</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>1347.26</v>
+        <v>1348.86</v>
       </c>
       <c r="Q2">
-        <v>1340.41</v>
+        <v>1338.19</v>
       </c>
       <c r="R2">
-        <v>1392.4</v>
+        <v>1390.52</v>
       </c>
       <c r="S2">
-        <v>1352.75</v>
+        <v>1352.61</v>
       </c>
       <c r="T2">
-        <v>0.17</v>
+        <v>-0.93</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,37 +947,37 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>49.42</v>
+        <v>45.04</v>
       </c>
       <c r="Z2">
-        <v>-14.33</v>
+        <v>-13.38</v>
       </c>
       <c r="AA2">
-        <v>-20.27</v>
+        <v>-18.89</v>
       </c>
       <c r="AB2">
-        <v>5.94</v>
+        <v>5.51</v>
       </c>
       <c r="AC2">
-        <v>96.31</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AD2">
-        <v>97.77</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="AE2">
-        <v>22.13</v>
+        <v>22.22</v>
       </c>
       <c r="AF2">
-        <v>-46.2</v>
+        <v>-13.29</v>
       </c>
       <c r="AG2">
-        <v>1386.03</v>
+        <v>1378.81</v>
       </c>
       <c r="AH2">
-        <v>1294.79</v>
+        <v>1297.56</v>
       </c>
       <c r="AI2">
         <v>1358.5</v>
@@ -986,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>35.88</v>
+        <v>32.41</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1690.2</v>
+        <v>1674</v>
       </c>
       <c r="D3">
-        <v>4.08</v>
+        <v>-0.96</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,25 +1009,25 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-16.95</v>
+        <v>-17.75</v>
       </c>
       <c r="H3">
-        <v>18.39</v>
+        <v>17.25</v>
       </c>
       <c r="I3">
-        <v>8.140000000000001</v>
+        <v>4.62</v>
       </c>
       <c r="J3">
-        <v>13.86</v>
+        <v>13.57</v>
       </c>
       <c r="K3">
-        <v>-7.45</v>
+        <v>-6.34</v>
       </c>
       <c r="L3">
-        <v>-11.61</v>
+        <v>-11.55</v>
       </c>
       <c r="M3">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="N3">
         <v>66</v>
@@ -1036,19 +1036,19 @@
         <v>58</v>
       </c>
       <c r="P3">
-        <v>1620.5</v>
+        <v>1635.3</v>
       </c>
       <c r="Q3">
-        <v>1533.41</v>
+        <v>1543.86</v>
       </c>
       <c r="R3">
-        <v>1573.22</v>
+        <v>1573.94</v>
       </c>
       <c r="S3">
-        <v>1755.49</v>
+        <v>1754.15</v>
       </c>
       <c r="T3">
-        <v>-3.72</v>
+        <v>-4.57</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,34 +1063,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>66.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="Z3">
-        <v>21.36</v>
+        <v>26.77</v>
       </c>
       <c r="AA3">
-        <v>0.97</v>
+        <v>6.13</v>
       </c>
       <c r="AB3">
-        <v>20.39</v>
+        <v>20.63</v>
       </c>
       <c r="AC3">
-        <v>97.83</v>
+        <v>96.47</v>
       </c>
       <c r="AD3">
-        <v>97.67</v>
+        <v>97.3</v>
       </c>
       <c r="AE3">
-        <v>43.13</v>
+        <v>44.28</v>
       </c>
       <c r="AF3">
-        <v>66.2</v>
+        <v>-23.78</v>
       </c>
       <c r="AG3">
-        <v>1673.92</v>
+        <v>1693.72</v>
       </c>
       <c r="AH3">
-        <v>1392.9</v>
+        <v>1394</v>
       </c>
       <c r="AI3">
         <v>1530.3</v>
@@ -1099,7 +1099,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>41.64</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>460.55</v>
+        <v>463.4</v>
       </c>
       <c r="D4">
-        <v>0.78</v>
+        <v>0.62</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1122,46 +1122,46 @@
         <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-32.87</v>
+        <v>-32.46</v>
       </c>
       <c r="H4">
-        <v>3.77</v>
+        <v>4.42</v>
       </c>
       <c r="I4">
-        <v>2.79</v>
+        <v>1.87</v>
       </c>
       <c r="J4">
-        <v>-1.86</v>
+        <v>0.19</v>
       </c>
       <c r="K4">
-        <v>-9.76</v>
+        <v>-10.83</v>
       </c>
       <c r="L4">
-        <v>-23.03</v>
+        <v>-22.95</v>
       </c>
       <c r="M4">
-        <v>-6.85</v>
+        <v>-6.73</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P4">
-        <v>457.89</v>
+        <v>459.59</v>
       </c>
       <c r="Q4">
-        <v>466.44</v>
+        <v>466.06</v>
       </c>
       <c r="R4">
-        <v>488.39</v>
+        <v>487.44</v>
       </c>
       <c r="S4">
-        <v>546.85</v>
+        <v>545.9299999999999</v>
       </c>
       <c r="T4">
-        <v>-15.78</v>
+        <v>-15.12</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1176,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.32</v>
+        <v>45.38</v>
       </c>
       <c r="Z4">
-        <v>-9.49</v>
+        <v>-8.56</v>
       </c>
       <c r="AA4">
-        <v>-9.98</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AB4">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="AC4">
-        <v>51.3</v>
+        <v>62.96</v>
       </c>
       <c r="AD4">
-        <v>48.78</v>
+        <v>54.42</v>
       </c>
       <c r="AE4">
-        <v>12.77</v>
+        <v>12.52</v>
       </c>
       <c r="AF4">
-        <v>-58.41</v>
+        <v>-71.51000000000001</v>
       </c>
       <c r="AG4">
-        <v>497.56</v>
+        <v>497.13</v>
       </c>
       <c r="AH4">
-        <v>435.32</v>
+        <v>434.99</v>
       </c>
       <c r="AI4">
         <v>488.94</v>
@@ -1212,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>33.05</v>
+        <v>29.41</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-5.5</v>
+        <v>-3.17</v>
       </c>
       <c r="D7" s="5">
-        <v>-3.17</v>
+        <v>-3.53</v>
       </c>
       <c r="E7" s="6">
-        <v>2.33</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>8.75</v>
+        <v>13.86</v>
       </c>
       <c r="D8" s="5">
-        <v>13.86</v>
+        <v>13.57</v>
       </c>
       <c r="E8" s="6">
-        <v>5.11</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-2.9</v>
+        <v>-1.86</v>
       </c>
       <c r="D9" s="5">
-        <v>-1.86</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1.04</v>
+        <v>0.19</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.05</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>2.07</v>
+        <v>3.39</v>
       </c>
       <c r="D10" s="5">
-        <v>3.39</v>
+        <v>0.6</v>
       </c>
       <c r="E10" s="6">
-        <v>1.32</v>
+        <v>-2.79</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>2.14</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="D11" s="5">
-        <v>8.140000000000001</v>
+        <v>4.62</v>
       </c>
       <c r="E11" s="6">
-        <v>6</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="D12" s="5">
-        <v>2.79</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.18</v>
+        <v>1.87</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-1.19</v>
+        <v>-0.62</v>
       </c>
       <c r="D13" s="5">
-        <v>-0.62</v>
+        <v>-2.61</v>
       </c>
       <c r="E13" s="6">
-        <v>0.57</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-14.45</v>
+        <v>-11.61</v>
       </c>
       <c r="D14" s="5">
-        <v>-11.61</v>
-      </c>
-      <c r="E14" s="6">
-        <v>2.84</v>
+        <v>-11.55</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-23.71</v>
+        <v>-23.03</v>
       </c>
       <c r="D15" s="5">
-        <v>-23.03</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.68</v>
+        <v>-22.95</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.08</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-2.3</v>
+        <v>-3.3</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.3</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1</v>
+        <v>-4.93</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-9.51</v>
+        <v>-7.45</v>
       </c>
       <c r="D17" s="5">
-        <v>-7.45</v>
-      </c>
-      <c r="E17" s="6">
-        <v>2.06</v>
+        <v>-6.34</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.11</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-6.87</v>
+        <v>-9.76</v>
       </c>
       <c r="D18" s="5">
-        <v>-9.76</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.89</v>
+        <v>-10.83</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-7.8</v>
+        <v>-7.39</v>
       </c>
       <c r="D19" s="5">
-        <v>-7.39</v>
+        <v>-8.41</v>
       </c>
       <c r="E19" s="6">
-        <v>0.41</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-20.2</v>
+        <v>-16.95</v>
       </c>
       <c r="D20" s="5">
-        <v>-16.95</v>
+        <v>-17.75</v>
       </c>
       <c r="E20" s="6">
-        <v>3.25</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-33.39</v>
+        <v>-32.87</v>
       </c>
       <c r="D21" s="5">
-        <v>-32.87</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.52</v>
+        <v>-32.46</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.41</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="D22" s="5">
-        <v>1355</v>
+        <v>1340</v>
       </c>
       <c r="E22" s="6">
-        <v>6</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1624</v>
+        <v>1690.2</v>
       </c>
       <c r="D23" s="5">
-        <v>1690.2</v>
+        <v>1674</v>
       </c>
       <c r="E23" s="6">
-        <v>66.2</v>
+        <v>-16.2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>457</v>
+        <v>460.55</v>
       </c>
       <c r="D24" s="5">
-        <v>460.55</v>
-      </c>
-      <c r="E24" s="6">
-        <v>3.55</v>
+        <v>463.4</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.85</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1716,13 +1716,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>47.52</v>
+        <v>49.42</v>
       </c>
       <c r="D25" s="5">
-        <v>49.42</v>
+        <v>45.04</v>
       </c>
       <c r="E25" s="6">
-        <v>1.9</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1733,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>60.31</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D26" s="5">
-        <v>66.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E26" s="6">
-        <v>6.59</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1750,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>40.74</v>
+        <v>43.32</v>
       </c>
       <c r="D27" s="5">
-        <v>43.32</v>
-      </c>
-      <c r="E27" s="6">
-        <v>2.58</v>
+        <v>45.38</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.06</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1767,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>11.84</v>
+        <v>-46.2</v>
       </c>
       <c r="D28" s="5">
-        <v>-46.2</v>
+        <v>-13.29</v>
       </c>
       <c r="E28" s="7">
-        <v>-58.04</v>
+        <v>32.91</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1784,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-1.35</v>
+        <v>66.2</v>
       </c>
       <c r="D29" s="5">
-        <v>66.2</v>
+        <v>-23.78</v>
       </c>
       <c r="E29" s="6">
-        <v>67.55</v>
+        <v>-89.98</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1801,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-9.68</v>
+        <v>-58.41</v>
       </c>
       <c r="D30" s="5">
-        <v>-58.41</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-48.73</v>
+        <v>-71.51000000000001</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-13.1</v>
       </c>
     </row>
   </sheetData>
@@ -1866,22 +1866,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="10">
-        <v>48.52</v>
+        <v>36.52</v>
       </c>
       <c r="C2" s="11">
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>53.2</v>
+        <v>51.5</v>
       </c>
       <c r="E2" s="10">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-6.8</v>
+        <v>-7.4</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1441</v>
+        <v>0.1429</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0267</v>
+        <v>0.0252</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.06849999999999999</v>
+        <v>-0.0673</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -151,16 +151,43 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.0 → 51.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>45.0</t>
+  </si>
+  <si>
+    <t>51.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -246,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,14 +389,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -884,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1340</v>
+        <v>1360.2</v>
       </c>
       <c r="D2">
-        <v>-1.11</v>
+        <v>1.51</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,46 +924,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-8.41</v>
+        <v>-7.03</v>
       </c>
       <c r="H2">
-        <v>11.12</v>
+        <v>12.8</v>
       </c>
       <c r="I2">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J2">
-        <v>-3.53</v>
+        <v>-1.76</v>
       </c>
       <c r="K2">
-        <v>-4.93</v>
+        <v>-3.37</v>
       </c>
       <c r="L2">
-        <v>-2.61</v>
+        <v>-0.74</v>
       </c>
       <c r="M2">
-        <v>14.29</v>
+        <v>14.58</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>1348.86</v>
+        <v>1352.34</v>
       </c>
       <c r="Q2">
-        <v>1338.19</v>
+        <v>1337.23</v>
       </c>
       <c r="R2">
-        <v>1390.52</v>
+        <v>1389.02</v>
       </c>
       <c r="S2">
-        <v>1352.61</v>
+        <v>1352.59</v>
       </c>
       <c r="T2">
-        <v>-0.93</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,46 +975,46 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>45.04</v>
+        <v>51.3</v>
       </c>
       <c r="Z2">
-        <v>-13.38</v>
+        <v>-10.88</v>
       </c>
       <c r="AA2">
-        <v>-18.89</v>
+        <v>-17.29</v>
       </c>
       <c r="AB2">
-        <v>5.51</v>
+        <v>6.41</v>
       </c>
       <c r="AC2">
-        <v>90.29000000000001</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="AD2">
-        <v>94.54000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AE2">
-        <v>22.22</v>
+        <v>23.15</v>
       </c>
       <c r="AF2">
-        <v>-13.29</v>
+        <v>-40.3</v>
       </c>
       <c r="AG2">
-        <v>1378.81</v>
+        <v>1374.55</v>
       </c>
       <c r="AH2">
-        <v>1297.56</v>
+        <v>1299.91</v>
       </c>
       <c r="AI2">
-        <v>1358.5</v>
+        <v>1284.46</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>32.41</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1674</v>
+        <v>1691.8</v>
       </c>
       <c r="D3">
-        <v>-0.96</v>
+        <v>1.06</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1037,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-17.75</v>
+        <v>-16.87</v>
       </c>
       <c r="H3">
-        <v>17.25</v>
+        <v>18.5</v>
       </c>
       <c r="I3">
-        <v>4.62</v>
+        <v>5.85</v>
       </c>
       <c r="J3">
-        <v>13.57</v>
+        <v>15.48</v>
       </c>
       <c r="K3">
-        <v>-6.34</v>
+        <v>-5.39</v>
       </c>
       <c r="L3">
-        <v>-11.55</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="M3">
-        <v>2.52</v>
+        <v>2.91</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P3">
-        <v>1635.3</v>
+        <v>1654</v>
       </c>
       <c r="Q3">
-        <v>1543.86</v>
+        <v>1555.46</v>
       </c>
       <c r="R3">
-        <v>1573.94</v>
+        <v>1575.3</v>
       </c>
       <c r="S3">
-        <v>1754.15</v>
+        <v>1752.84</v>
       </c>
       <c r="T3">
-        <v>-4.57</v>
+        <v>-3.48</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,43 +1091,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>64.09999999999999</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="Z3">
-        <v>26.77</v>
+        <v>32.11</v>
       </c>
       <c r="AA3">
-        <v>6.13</v>
+        <v>11.33</v>
       </c>
       <c r="AB3">
-        <v>20.63</v>
+        <v>20.79</v>
       </c>
       <c r="AC3">
-        <v>96.47</v>
+        <v>94.8</v>
       </c>
       <c r="AD3">
-        <v>97.3</v>
+        <v>96.37</v>
       </c>
       <c r="AE3">
-        <v>44.28</v>
+        <v>44.3</v>
       </c>
       <c r="AF3">
-        <v>-23.78</v>
+        <v>-37.99</v>
       </c>
       <c r="AG3">
-        <v>1693.72</v>
+        <v>1713.61</v>
       </c>
       <c r="AH3">
-        <v>1394</v>
+        <v>1397.31</v>
       </c>
       <c r="AI3">
-        <v>1530.3</v>
+        <v>1548.79</v>
       </c>
       <c r="AJ3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AK3">
-        <v>45.38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>463.4</v>
+        <v>447</v>
       </c>
       <c r="D4">
-        <v>0.62</v>
+        <v>-3.54</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1122,46 +1150,46 @@
         <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-32.46</v>
+        <v>-34.85</v>
       </c>
       <c r="H4">
-        <v>4.42</v>
+        <v>0.72</v>
       </c>
       <c r="I4">
-        <v>1.87</v>
+        <v>-2.72</v>
       </c>
       <c r="J4">
-        <v>0.19</v>
+        <v>-5.1</v>
       </c>
       <c r="K4">
-        <v>-10.83</v>
+        <v>-11.3</v>
       </c>
       <c r="L4">
-        <v>-22.95</v>
+        <v>-24.35</v>
       </c>
       <c r="M4">
-        <v>-6.73</v>
+        <v>-7.26</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P4">
-        <v>459.59</v>
+        <v>457.09</v>
       </c>
       <c r="Q4">
-        <v>466.06</v>
+        <v>464.83</v>
       </c>
       <c r="R4">
-        <v>487.44</v>
+        <v>486.07</v>
       </c>
       <c r="S4">
-        <v>545.9299999999999</v>
+        <v>544.92</v>
       </c>
       <c r="T4">
-        <v>-15.12</v>
+        <v>-17.97</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,43 +1204,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>45.38</v>
+        <v>37.04</v>
       </c>
       <c r="Z4">
-        <v>-8.56</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="AA4">
-        <v>-9.699999999999999</v>
+        <v>-9.57</v>
       </c>
       <c r="AB4">
-        <v>1.14</v>
+        <v>0.53</v>
       </c>
       <c r="AC4">
-        <v>62.96</v>
+        <v>59.46</v>
       </c>
       <c r="AD4">
-        <v>54.42</v>
+        <v>57.91</v>
       </c>
       <c r="AE4">
-        <v>12.52</v>
+        <v>12.98</v>
       </c>
       <c r="AF4">
-        <v>-71.51000000000001</v>
+        <v>96.95</v>
       </c>
       <c r="AG4">
-        <v>497.13</v>
+        <v>496.92</v>
       </c>
       <c r="AH4">
-        <v>434.99</v>
+        <v>432.75</v>
       </c>
       <c r="AI4">
         <v>488.94</v>
       </c>
       <c r="AJ4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AK4">
-        <v>29.41</v>
+        <v>29.35</v>
       </c>
     </row>
   </sheetData>
@@ -1373,12 +1401,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1386,428 +1449,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-3.17</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-3.53</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.36</v>
+      <c r="D7" s="6">
+        <v>-1.76</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.77</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>13.86</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>13.57</v>
       </c>
-      <c r="E8" s="6">
-        <v>-0.29</v>
+      <c r="D8" s="6">
+        <v>15.48</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.91</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-1.86</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>0.19</v>
       </c>
-      <c r="E9" s="7">
-        <v>2.05</v>
+      <c r="D9" s="6">
+        <v>-5.1</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-5.29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>3.39</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>0.6</v>
       </c>
-      <c r="E10" s="6">
-        <v>-2.79</v>
+      <c r="D10" s="6">
+        <v>1.3</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>4.62</v>
       </c>
-      <c r="E11" s="6">
-        <v>-3.52</v>
+      <c r="D11" s="6">
+        <v>5.85</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.23</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>2.79</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>1.87</v>
       </c>
-      <c r="E12" s="6">
-        <v>-0.92</v>
+      <c r="D12" s="6">
+        <v>-2.72</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-4.59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-0.62</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-2.61</v>
       </c>
-      <c r="E13" s="6">
-        <v>-1.99</v>
+      <c r="D13" s="6">
+        <v>-0.74</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.87</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-11.61</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-11.55</v>
       </c>
+      <c r="D14" s="6">
+        <v>-9.279999999999999</v>
+      </c>
       <c r="E14" s="7">
-        <v>0.06</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-23.03</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-22.95</v>
       </c>
-      <c r="E15" s="7">
-        <v>0.08</v>
+      <c r="D15" s="6">
+        <v>-24.35</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-3.3</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-4.93</v>
       </c>
-      <c r="E16" s="6">
-        <v>-1.63</v>
+      <c r="D16" s="6">
+        <v>-3.37</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.56</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-7.45</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-6.34</v>
       </c>
+      <c r="D17" s="6">
+        <v>-5.39</v>
+      </c>
       <c r="E17" s="7">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-9.76</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-10.83</v>
       </c>
-      <c r="E18" s="6">
-        <v>-1.07</v>
+      <c r="D18" s="6">
+        <v>-11.3</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-7.39</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-8.41</v>
       </c>
-      <c r="E19" s="6">
-        <v>-1.02</v>
+      <c r="D19" s="6">
+        <v>-7.03</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.38</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-16.95</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-17.75</v>
       </c>
-      <c r="E20" s="6">
-        <v>-0.8</v>
+      <c r="D20" s="6">
+        <v>-16.87</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.88</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-32.87</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-32.46</v>
       </c>
-      <c r="E21" s="7">
-        <v>0.41</v>
+      <c r="D21" s="6">
+        <v>-34.85</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>1355</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>1340</v>
       </c>
-      <c r="E22" s="6">
-        <v>-15</v>
+      <c r="D22" s="6">
+        <v>1360.2</v>
+      </c>
+      <c r="E22" s="7">
+        <v>20.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>1690.2</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>1674</v>
       </c>
-      <c r="E23" s="6">
-        <v>-16.2</v>
+      <c r="D23" s="6">
+        <v>1691.8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>17.8</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>460.55</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>463.4</v>
       </c>
-      <c r="E24" s="7">
-        <v>2.85</v>
+      <c r="D24" s="6">
+        <v>447</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-16.4</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>49.42</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>45.04</v>
       </c>
-      <c r="E25" s="6">
-        <v>-4.38</v>
+      <c r="D25" s="6">
+        <v>51.3</v>
+      </c>
+      <c r="E25" s="7">
+        <v>6.26</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>64.09999999999999</v>
       </c>
-      <c r="E26" s="6">
-        <v>-2.8</v>
+      <c r="D26" s="6">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.69</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>43.32</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>45.38</v>
       </c>
-      <c r="E27" s="7">
-        <v>2.06</v>
+      <c r="D27" s="6">
+        <v>37.04</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-8.34</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-46.2</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>-13.29</v>
       </c>
-      <c r="E28" s="7">
-        <v>32.91</v>
+      <c r="D28" s="6">
+        <v>-40.3</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-27.01</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>66.2</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-23.78</v>
       </c>
-      <c r="E29" s="6">
-        <v>-89.98</v>
+      <c r="D29" s="6">
+        <v>-37.99</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-14.21</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-58.41</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-71.51000000000001</v>
       </c>
-      <c r="E30" s="6">
-        <v>-13.1</v>
+      <c r="D30" s="6">
+        <v>96.95</v>
+      </c>
+      <c r="E30" s="7">
+        <v>168.46</v>
       </c>
     </row>
   </sheetData>
@@ -1833,60 +1896,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
-        <v>36.52</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="11">
+        <v>48.52</v>
+      </c>
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>51.5</v>
-      </c>
-      <c r="E2" s="10">
-        <v>0</v>
-      </c>
-      <c r="F2" s="10">
-        <v>3.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-7.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="11">
+        <v>51.4</v>
+      </c>
+      <c r="E2" s="11">
+        <v>30</v>
+      </c>
+      <c r="F2" s="11">
+        <v>2.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-6.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1988,25 +2051,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1429</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0252</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0673</v>
+      <c r="A2" s="14">
+        <v>0.1458</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0291</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0726</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,16 +178,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.0 → 51.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.0</t>
+    <t>51.3 → 45.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>51.3</t>
+  </si>
+  <si>
+    <t>45.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -912,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1360.2</v>
+        <v>1338.6</v>
       </c>
       <c r="D2">
-        <v>1.51</v>
+        <v>-1.59</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,46 +924,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-7.03</v>
+        <v>-8.51</v>
       </c>
       <c r="H2">
-        <v>12.8</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>1.3</v>
+        <v>-1.39</v>
       </c>
       <c r="J2">
-        <v>-1.76</v>
+        <v>-2.95</v>
       </c>
       <c r="K2">
-        <v>-3.37</v>
+        <v>-5.48</v>
       </c>
       <c r="L2">
-        <v>-0.74</v>
+        <v>-2.73</v>
       </c>
       <c r="M2">
-        <v>14.58</v>
+        <v>13.67</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P2">
-        <v>1352.34</v>
+        <v>1348.56</v>
       </c>
       <c r="Q2">
-        <v>1337.23</v>
+        <v>1336.64</v>
       </c>
       <c r="R2">
-        <v>1389.02</v>
+        <v>1386.59</v>
       </c>
       <c r="S2">
-        <v>1352.59</v>
+        <v>1352.49</v>
       </c>
       <c r="T2">
-        <v>0.5600000000000001</v>
+        <v>-1.03</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,37 +975,37 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>51.3</v>
+        <v>45.35</v>
       </c>
       <c r="Z2">
-        <v>-10.88</v>
+        <v>-10.51</v>
       </c>
       <c r="AA2">
-        <v>-17.29</v>
+        <v>-15.93</v>
       </c>
       <c r="AB2">
-        <v>6.41</v>
+        <v>5.42</v>
       </c>
       <c r="AC2">
-        <v>93.29000000000001</v>
+        <v>87.08</v>
       </c>
       <c r="AD2">
-        <v>93.3</v>
+        <v>90.22</v>
       </c>
       <c r="AE2">
-        <v>23.15</v>
+        <v>23.11</v>
       </c>
       <c r="AF2">
-        <v>-40.3</v>
+        <v>-12.47</v>
       </c>
       <c r="AG2">
-        <v>1374.55</v>
+        <v>1373.46</v>
       </c>
       <c r="AH2">
-        <v>1299.91</v>
+        <v>1299.82</v>
       </c>
       <c r="AI2">
         <v>1284.46</v>
@@ -1014,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>30.81</v>
+        <v>29.43</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1691.8</v>
+        <v>1713</v>
       </c>
       <c r="D3">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1037,46 +1037,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-16.87</v>
+        <v>-15.83</v>
       </c>
       <c r="H3">
-        <v>18.5</v>
+        <v>19.98</v>
       </c>
       <c r="I3">
-        <v>5.85</v>
+        <v>7.74</v>
       </c>
       <c r="J3">
-        <v>15.48</v>
+        <v>17.34</v>
       </c>
       <c r="K3">
-        <v>-5.39</v>
+        <v>-5.6</v>
       </c>
       <c r="L3">
-        <v>-9.279999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="M3">
-        <v>2.91</v>
+        <v>3.16</v>
       </c>
       <c r="N3">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="O3">
         <v>60</v>
       </c>
       <c r="P3">
-        <v>1654</v>
+        <v>1678.6</v>
       </c>
       <c r="Q3">
-        <v>1555.46</v>
+        <v>1569.72</v>
       </c>
       <c r="R3">
-        <v>1575.3</v>
+        <v>1576.06</v>
       </c>
       <c r="S3">
-        <v>1752.84</v>
+        <v>1751.65</v>
       </c>
       <c r="T3">
-        <v>-3.48</v>
+        <v>-2.21</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1091,43 +1091,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>65.79000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="Z3">
-        <v>32.11</v>
+        <v>37.63</v>
       </c>
       <c r="AA3">
-        <v>11.33</v>
+        <v>16.59</v>
       </c>
       <c r="AB3">
-        <v>20.79</v>
+        <v>21.04</v>
       </c>
       <c r="AC3">
         <v>94.8</v>
       </c>
       <c r="AD3">
-        <v>96.37</v>
+        <v>95.36</v>
       </c>
       <c r="AE3">
-        <v>44.3</v>
+        <v>46.3</v>
       </c>
       <c r="AF3">
-        <v>-37.99</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="AG3">
-        <v>1713.61</v>
+        <v>1730.8</v>
       </c>
       <c r="AH3">
-        <v>1397.31</v>
+        <v>1408.65</v>
       </c>
       <c r="AI3">
-        <v>1548.79</v>
+        <v>1578.24</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>49</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D4">
-        <v>-3.54</v>
+        <v>-0.45</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,46 +1150,46 @@
         <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-34.85</v>
+        <v>-35.14</v>
       </c>
       <c r="H4">
-        <v>0.72</v>
+        <v>0.27</v>
       </c>
       <c r="I4">
-        <v>-2.72</v>
+        <v>-2.73</v>
       </c>
       <c r="J4">
-        <v>-5.1</v>
+        <v>-5.62</v>
       </c>
       <c r="K4">
-        <v>-11.3</v>
+        <v>-15.26</v>
       </c>
       <c r="L4">
-        <v>-24.35</v>
+        <v>-24.75</v>
       </c>
       <c r="M4">
-        <v>-7.26</v>
+        <v>-7.21</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>457.09</v>
+        <v>454.59</v>
       </c>
       <c r="Q4">
-        <v>464.83</v>
+        <v>464.2</v>
       </c>
       <c r="R4">
-        <v>486.07</v>
+        <v>484.53</v>
       </c>
       <c r="S4">
-        <v>544.92</v>
+        <v>543.89</v>
       </c>
       <c r="T4">
-        <v>-17.97</v>
+        <v>-18.18</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,34 +1204,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.04</v>
+        <v>36.16</v>
       </c>
       <c r="Z4">
-        <v>-9.039999999999999</v>
+        <v>-9.48</v>
       </c>
       <c r="AA4">
-        <v>-9.57</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="AB4">
-        <v>0.53</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC4">
-        <v>59.46</v>
+        <v>51.22</v>
       </c>
       <c r="AD4">
-        <v>57.91</v>
+        <v>57.88</v>
       </c>
       <c r="AE4">
-        <v>12.98</v>
+        <v>13.2</v>
       </c>
       <c r="AF4">
-        <v>96.95</v>
+        <v>46.18</v>
       </c>
       <c r="AG4">
-        <v>496.92</v>
+        <v>497.36</v>
       </c>
       <c r="AH4">
-        <v>432.75</v>
+        <v>431.05</v>
       </c>
       <c r="AI4">
         <v>488.94</v>
@@ -1240,7 +1240,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>29.35</v>
+        <v>29.82</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1473,13 +1473,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-3.53</v>
+        <v>-1.76</v>
       </c>
       <c r="D7" s="6">
-        <v>-1.76</v>
+        <v>-2.95</v>
       </c>
       <c r="E7" s="7">
-        <v>1.77</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1490,13 +1490,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>13.57</v>
+        <v>15.48</v>
       </c>
       <c r="D8" s="6">
-        <v>15.48</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.91</v>
+        <v>17.34</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.86</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1507,13 +1507,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>0.19</v>
+        <v>-5.1</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.1</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-5.29</v>
+        <v>-5.62</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1524,13 +1524,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="D10" s="6">
-        <v>1.3</v>
+        <v>-1.39</v>
       </c>
       <c r="E10" s="7">
-        <v>0.7</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1541,13 +1541,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>4.62</v>
+        <v>5.85</v>
       </c>
       <c r="D11" s="6">
-        <v>5.85</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.23</v>
+        <v>7.74</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.89</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1558,13 +1558,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>1.87</v>
+        <v>-2.72</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.72</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-4.59</v>
+        <v>-2.73</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1575,13 +1575,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.61</v>
+        <v>-0.74</v>
       </c>
       <c r="D13" s="6">
-        <v>-0.74</v>
+        <v>-2.73</v>
       </c>
       <c r="E13" s="7">
-        <v>1.87</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1592,13 +1592,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-11.55</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="D14" s="6">
-        <v>-9.279999999999999</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2.27</v>
+        <v>-8.369999999999999</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.91</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1609,13 +1609,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-22.95</v>
+        <v>-24.35</v>
       </c>
       <c r="D15" s="6">
-        <v>-24.35</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.4</v>
+        <v>-24.75</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1626,13 +1626,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.93</v>
+        <v>-3.37</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.37</v>
+        <v>-5.48</v>
       </c>
       <c r="E16" s="7">
-        <v>1.56</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1643,13 +1643,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-6.34</v>
+        <v>-5.39</v>
       </c>
       <c r="D17" s="6">
-        <v>-5.39</v>
+        <v>-5.6</v>
       </c>
       <c r="E17" s="7">
-        <v>0.95</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1660,13 +1660,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-10.83</v>
+        <v>-11.3</v>
       </c>
       <c r="D18" s="6">
-        <v>-11.3</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.47</v>
+        <v>-15.26</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-3.96</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1677,13 +1677,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-8.41</v>
+        <v>-7.03</v>
       </c>
       <c r="D19" s="6">
-        <v>-7.03</v>
+        <v>-8.51</v>
       </c>
       <c r="E19" s="7">
-        <v>1.38</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1694,13 +1694,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-17.75</v>
+        <v>-16.87</v>
       </c>
       <c r="D20" s="6">
-        <v>-16.87</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.88</v>
+        <v>-15.83</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.04</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1711,13 +1711,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-32.46</v>
+        <v>-34.85</v>
       </c>
       <c r="D21" s="6">
-        <v>-34.85</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-2.39</v>
+        <v>-35.14</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1728,13 +1728,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>1340</v>
+        <v>1360.2</v>
       </c>
       <c r="D22" s="6">
-        <v>1360.2</v>
+        <v>1338.6</v>
       </c>
       <c r="E22" s="7">
-        <v>20.2</v>
+        <v>-21.6</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1745,13 +1745,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>1674</v>
+        <v>1691.8</v>
       </c>
       <c r="D23" s="6">
-        <v>1691.8</v>
-      </c>
-      <c r="E23" s="7">
-        <v>17.8</v>
+        <v>1713</v>
+      </c>
+      <c r="E23" s="8">
+        <v>21.2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1762,13 +1762,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>463.4</v>
+        <v>447</v>
       </c>
       <c r="D24" s="6">
-        <v>447</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-16.4</v>
+        <v>445</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1776,16 +1776,16 @@
         <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C25" s="6">
-        <v>45.04</v>
+        <v>99</v>
       </c>
       <c r="D25" s="6">
-        <v>51.3</v>
+        <v>66</v>
       </c>
       <c r="E25" s="7">
-        <v>6.26</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1793,84 +1793,118 @@
         <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C26" s="6">
-        <v>64.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="D26" s="6">
-        <v>65.79000000000001</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.69</v>
+        <v>99</v>
+      </c>
+      <c r="E26" s="8">
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>45.38</v>
+        <v>51.3</v>
       </c>
       <c r="D27" s="6">
-        <v>37.04</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-8.34</v>
+        <v>45.35</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-5.95</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C28" s="6">
-        <v>-13.29</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="D28" s="6">
-        <v>-40.3</v>
+        <v>67.75</v>
       </c>
       <c r="E28" s="8">
-        <v>-27.01</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C29" s="6">
-        <v>-23.78</v>
+        <v>37.04</v>
       </c>
       <c r="D29" s="6">
-        <v>-37.99</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-14.21</v>
+        <v>36.16</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-71.51000000000001</v>
+        <v>-40.3</v>
       </c>
       <c r="D30" s="6">
+        <v>-12.47</v>
+      </c>
+      <c r="E30" s="8">
+        <v>27.83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-37.99</v>
+      </c>
+      <c r="D31" s="6">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="E31" s="8">
+        <v>108.34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="6">
         <v>96.95</v>
       </c>
-      <c r="E30" s="7">
-        <v>168.46</v>
+      <c r="D32" s="6">
+        <v>46.18</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-50.77</v>
       </c>
     </row>
   </sheetData>
@@ -1929,22 +1963,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="11">
-        <v>48.52</v>
+        <v>36.52</v>
       </c>
       <c r="C2" s="12">
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>51.4</v>
+        <v>49.8</v>
       </c>
       <c r="E2" s="11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F2" s="11">
         <v>2.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-6.7</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2063,13 +2097,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1458</v>
+        <v>0.1367</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0291</v>
+        <v>0.0316</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0726</v>
+        <v>-0.0721</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,16 +178,22 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.3 → 45.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.3</t>
+    <t>45.4 → 57.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>45.4</t>
+  </si>
+  <si>
+    <t>57.8</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,8 +784,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -912,10 +917,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1338.6</v>
+        <v>1389.4</v>
       </c>
       <c r="D2">
-        <v>-1.59</v>
+        <v>3.8</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,46 +929,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-8.51</v>
+        <v>-5.04</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>15.22</v>
       </c>
       <c r="I2">
-        <v>-1.39</v>
+        <v>2.99</v>
       </c>
       <c r="J2">
-        <v>-2.95</v>
+        <v>2.89</v>
       </c>
       <c r="K2">
-        <v>-5.48</v>
+        <v>-2.03</v>
       </c>
       <c r="L2">
-        <v>-2.73</v>
+        <v>0.66</v>
       </c>
       <c r="M2">
-        <v>13.67</v>
+        <v>13.98</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>1348.56</v>
+        <v>1356.64</v>
       </c>
       <c r="Q2">
-        <v>1336.64</v>
+        <v>1338.17</v>
       </c>
       <c r="R2">
-        <v>1386.59</v>
+        <v>1385.29</v>
       </c>
       <c r="S2">
-        <v>1352.49</v>
+        <v>1352.68</v>
       </c>
       <c r="T2">
-        <v>-1.03</v>
+        <v>2.71</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,46 +980,46 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>45.35</v>
+        <v>57.75</v>
       </c>
       <c r="Z2">
-        <v>-10.51</v>
+        <v>-6.06</v>
       </c>
       <c r="AA2">
-        <v>-15.93</v>
+        <v>-13.96</v>
       </c>
       <c r="AB2">
-        <v>5.42</v>
+        <v>7.9</v>
       </c>
       <c r="AC2">
-        <v>87.08</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AD2">
-        <v>90.22</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="AE2">
-        <v>23.11</v>
+        <v>25.09</v>
       </c>
       <c r="AF2">
-        <v>-12.47</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="AG2">
-        <v>1373.46</v>
+        <v>1380.93</v>
       </c>
       <c r="AH2">
-        <v>1299.82</v>
+        <v>1295.41</v>
       </c>
       <c r="AI2">
-        <v>1284.46</v>
+        <v>1290.49</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>29.43</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +1030,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1713</v>
+        <v>1691.5</v>
       </c>
       <c r="D3">
-        <v>1.25</v>
+        <v>-1.26</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1037,49 +1042,49 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-15.83</v>
+        <v>-16.89</v>
       </c>
       <c r="H3">
-        <v>19.98</v>
+        <v>18.48</v>
       </c>
       <c r="I3">
-        <v>7.74</v>
+        <v>4.16</v>
       </c>
       <c r="J3">
-        <v>17.34</v>
+        <v>18.48</v>
       </c>
       <c r="K3">
-        <v>-5.6</v>
+        <v>4.17</v>
       </c>
       <c r="L3">
-        <v>-8.369999999999999</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="M3">
-        <v>3.16</v>
+        <v>2.92</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>1678.6</v>
+        <v>1692.1</v>
       </c>
       <c r="Q3">
-        <v>1569.72</v>
+        <v>1582.3</v>
       </c>
       <c r="R3">
-        <v>1576.06</v>
+        <v>1577</v>
       </c>
       <c r="S3">
-        <v>1751.65</v>
+        <v>1750.39</v>
       </c>
       <c r="T3">
-        <v>-2.21</v>
+        <v>-3.36</v>
       </c>
       <c r="U3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V3" t="s">
         <v>41</v>
@@ -1088,46 +1093,46 @@
         <v>41</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>67.75</v>
+        <v>63.77</v>
       </c>
       <c r="Z3">
-        <v>37.63</v>
+        <v>39.81</v>
       </c>
       <c r="AA3">
-        <v>16.59</v>
+        <v>21.23</v>
       </c>
       <c r="AB3">
-        <v>21.04</v>
+        <v>18.58</v>
       </c>
       <c r="AC3">
-        <v>94.8</v>
+        <v>91.91</v>
       </c>
       <c r="AD3">
-        <v>95.36</v>
+        <v>93.84</v>
       </c>
       <c r="AE3">
-        <v>46.3</v>
+        <v>50.33</v>
       </c>
       <c r="AF3">
-        <v>70.34999999999999</v>
+        <v>185.03</v>
       </c>
       <c r="AG3">
-        <v>1730.8</v>
+        <v>1739.96</v>
       </c>
       <c r="AH3">
-        <v>1408.65</v>
+        <v>1424.64</v>
       </c>
       <c r="AI3">
-        <v>1578.24</v>
+        <v>1583.65</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>53.16</v>
+        <v>57.22</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1143,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D4">
-        <v>-0.45</v>
+        <v>0.9</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,46 +1155,46 @@
         <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-35.14</v>
+        <v>-34.55</v>
       </c>
       <c r="H4">
-        <v>0.27</v>
+        <v>1.17</v>
       </c>
       <c r="I4">
-        <v>-2.73</v>
+        <v>-1.75</v>
       </c>
       <c r="J4">
-        <v>-5.62</v>
+        <v>-1.88</v>
       </c>
       <c r="K4">
-        <v>-15.26</v>
+        <v>-11.76</v>
       </c>
       <c r="L4">
-        <v>-24.75</v>
+        <v>-24.62</v>
       </c>
       <c r="M4">
-        <v>-7.21</v>
+        <v>-7.66</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>454.59</v>
+        <v>452.99</v>
       </c>
       <c r="Q4">
-        <v>464.2</v>
+        <v>463.15</v>
       </c>
       <c r="R4">
-        <v>484.53</v>
+        <v>483.24</v>
       </c>
       <c r="S4">
-        <v>543.89</v>
+        <v>542.9</v>
       </c>
       <c r="T4">
-        <v>-18.18</v>
+        <v>-17.3</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,43 +1209,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.16</v>
+        <v>39.25</v>
       </c>
       <c r="Z4">
-        <v>-9.48</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="AA4">
-        <v>-9.550000000000001</v>
+        <v>-9.52</v>
       </c>
       <c r="AB4">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AC4">
-        <v>51.22</v>
+        <v>42.46</v>
       </c>
       <c r="AD4">
-        <v>57.88</v>
+        <v>51.05</v>
       </c>
       <c r="AE4">
-        <v>13.2</v>
+        <v>12.71</v>
       </c>
       <c r="AF4">
-        <v>46.18</v>
+        <v>96.3</v>
       </c>
       <c r="AG4">
-        <v>497.36</v>
+        <v>496.87</v>
       </c>
       <c r="AH4">
-        <v>431.05</v>
+        <v>429.44</v>
       </c>
       <c r="AI4">
-        <v>488.94</v>
+        <v>486.59</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>29.82</v>
+        <v>30.22</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1439,478 +1444,464 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-1.76</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-2.95</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-1.19</v>
+      <c r="D7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>15.48</v>
+        <v>-2.95</v>
       </c>
       <c r="D8" s="6">
-        <v>17.34</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.86</v>
+        <v>2.89</v>
+      </c>
+      <c r="E8" s="7">
+        <v>5.84</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5.1</v>
+        <v>17.34</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.62</v>
+        <v>18.48</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.52</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>1.3</v>
+        <v>-5.62</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.39</v>
+        <v>-1.88</v>
       </c>
       <c r="E10" s="7">
-        <v>-2.69</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>5.85</v>
+        <v>-1.39</v>
       </c>
       <c r="D11" s="6">
-        <v>7.74</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.89</v>
+        <v>2.99</v>
+      </c>
+      <c r="E11" s="7">
+        <v>4.38</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.72</v>
+        <v>7.74</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.73</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.01</v>
+        <v>4.16</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-3.58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.74</v>
+        <v>-2.73</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.73</v>
+        <v>-1.75</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-9.279999999999999</v>
+        <v>-2.73</v>
       </c>
       <c r="D14" s="6">
-        <v>-8.369999999999999</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.91</v>
+        <v>0.66</v>
+      </c>
+      <c r="E14" s="7">
+        <v>3.39</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-24.35</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="D15" s="6">
-        <v>-24.75</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.4</v>
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.37</v>
+        <v>-24.75</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.48</v>
+        <v>-24.62</v>
       </c>
       <c r="E16" s="7">
-        <v>-2.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.39</v>
+        <v>-5.48</v>
       </c>
       <c r="D17" s="6">
-        <v>-5.6</v>
+        <v>-2.03</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.21</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-11.3</v>
+        <v>-5.6</v>
       </c>
       <c r="D18" s="6">
-        <v>-15.26</v>
+        <v>4.17</v>
       </c>
       <c r="E18" s="7">
-        <v>-3.96</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.03</v>
+        <v>-15.26</v>
       </c>
       <c r="D19" s="6">
-        <v>-8.51</v>
+        <v>-11.76</v>
       </c>
       <c r="E19" s="7">
-        <v>-1.48</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-16.87</v>
+        <v>-8.51</v>
       </c>
       <c r="D20" s="6">
-        <v>-15.83</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.04</v>
+        <v>-5.04</v>
+      </c>
+      <c r="E20" s="7">
+        <v>3.47</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-34.85</v>
+        <v>-15.83</v>
       </c>
       <c r="D21" s="6">
-        <v>-35.14</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.29</v>
+        <v>-16.89</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6">
-        <v>1360.2</v>
+        <v>-35.14</v>
       </c>
       <c r="D22" s="6">
-        <v>1338.6</v>
+        <v>-34.55</v>
       </c>
       <c r="E22" s="7">
-        <v>-21.6</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>1691.8</v>
+        <v>1338.6</v>
       </c>
       <c r="D23" s="6">
-        <v>1713</v>
-      </c>
-      <c r="E23" s="8">
-        <v>21.2</v>
+        <v>1389.4</v>
+      </c>
+      <c r="E23" s="7">
+        <v>50.8</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>447</v>
+        <v>1713</v>
       </c>
       <c r="D24" s="6">
-        <v>445</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2</v>
+        <v>1691.5</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-21.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C25" s="6">
-        <v>99</v>
+        <v>445</v>
       </c>
       <c r="D25" s="6">
-        <v>66</v>
+        <v>449</v>
       </c>
       <c r="E25" s="7">
-        <v>-33</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>66</v>
+        <v>45.35</v>
       </c>
       <c r="D26" s="6">
-        <v>99</v>
-      </c>
-      <c r="E26" s="8">
-        <v>33</v>
+        <v>57.75</v>
+      </c>
+      <c r="E26" s="7">
+        <v>12.4</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>51.3</v>
+        <v>67.75</v>
       </c>
       <c r="D27" s="6">
-        <v>45.35</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-5.95</v>
+        <v>63.77</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-3.98</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="6">
-        <v>65.79000000000001</v>
+        <v>36.16</v>
       </c>
       <c r="D28" s="6">
-        <v>67.75</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.96</v>
+        <v>39.25</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3.09</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>37.04</v>
+        <v>-12.47</v>
       </c>
       <c r="D29" s="6">
-        <v>36.16</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.88</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-40.3</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="D30" s="6">
-        <v>-12.47</v>
-      </c>
-      <c r="E30" s="8">
-        <v>27.83</v>
+        <v>185.03</v>
+      </c>
+      <c r="E30" s="7">
+        <v>114.68</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="6">
-        <v>-37.99</v>
+        <v>46.18</v>
       </c>
       <c r="D31" s="6">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="E31" s="8">
-        <v>108.34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="6">
-        <v>96.95</v>
-      </c>
-      <c r="D32" s="6">
-        <v>46.18</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-50.77</v>
+        <v>96.3</v>
+      </c>
+      <c r="E31" s="7">
+        <v>50.12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1934,28 +1925,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1963,22 +1954,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="11">
-        <v>36.52</v>
+        <v>48.52</v>
       </c>
       <c r="C2" s="12">
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>49.8</v>
+        <v>53.6</v>
       </c>
       <c r="E2" s="11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="G2" s="11">
-        <v>-8.800000000000001</v>
+        <v>-3.2</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2097,13 +2088,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1367</v>
+        <v>0.1398</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0316</v>
+        <v>0.0292</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0721</v>
+        <v>-0.0766</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,40 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.4 → 57.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.4</t>
-  </si>
-  <si>
-    <t>57.8</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -279,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -319,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,15 +362,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -917,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1389.4</v>
+        <v>1397</v>
       </c>
       <c r="D2">
-        <v>3.8</v>
+        <v>0.55</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -929,46 +895,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-5.04</v>
+        <v>-4.52</v>
       </c>
       <c r="H2">
-        <v>15.22</v>
+        <v>15.85</v>
       </c>
       <c r="I2">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="J2">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="K2">
-        <v>-2.03</v>
+        <v>-3.27</v>
       </c>
       <c r="L2">
-        <v>0.66</v>
+        <v>1.28</v>
       </c>
       <c r="M2">
-        <v>13.98</v>
+        <v>14.1</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P2">
-        <v>1356.64</v>
+        <v>1365.04</v>
       </c>
       <c r="Q2">
-        <v>1338.17</v>
+        <v>1340.64</v>
       </c>
       <c r="R2">
-        <v>1385.29</v>
+        <v>1384.22</v>
       </c>
       <c r="S2">
-        <v>1352.68</v>
+        <v>1352.95</v>
       </c>
       <c r="T2">
-        <v>2.71</v>
+        <v>3.26</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -983,43 +949,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>57.75</v>
+        <v>59.24</v>
       </c>
       <c r="Z2">
-        <v>-6.06</v>
+        <v>-1.89</v>
       </c>
       <c r="AA2">
-        <v>-13.96</v>
+        <v>-11.54</v>
       </c>
       <c r="AB2">
-        <v>7.9</v>
+        <v>9.66</v>
       </c>
       <c r="AC2">
         <v>93.09999999999999</v>
       </c>
       <c r="AD2">
-        <v>91.15000000000001</v>
+        <v>91.09</v>
       </c>
       <c r="AE2">
-        <v>25.09</v>
+        <v>24.64</v>
       </c>
       <c r="AF2">
-        <v>80.43000000000001</v>
+        <v>51.97</v>
       </c>
       <c r="AG2">
-        <v>1380.93</v>
+        <v>1390.76</v>
       </c>
       <c r="AH2">
-        <v>1295.41</v>
+        <v>1290.52</v>
       </c>
       <c r="AI2">
-        <v>1290.49</v>
+        <v>1315.49</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>32.44</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1030,10 +996,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1691.5</v>
+        <v>1680.1</v>
       </c>
       <c r="D3">
-        <v>-1.26</v>
+        <v>-0.67</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1042,25 +1008,25 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-16.89</v>
+        <v>-17.45</v>
       </c>
       <c r="H3">
-        <v>18.48</v>
+        <v>17.68</v>
       </c>
       <c r="I3">
-        <v>4.16</v>
+        <v>-0.6</v>
       </c>
       <c r="J3">
-        <v>18.48</v>
+        <v>16.67</v>
       </c>
       <c r="K3">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="L3">
-        <v>-8.550000000000001</v>
+        <v>-7.71</v>
       </c>
       <c r="M3">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1069,19 +1035,19 @@
         <v>66</v>
       </c>
       <c r="P3">
-        <v>1692.1</v>
+        <v>1690.08</v>
       </c>
       <c r="Q3">
-        <v>1582.3</v>
+        <v>1591.97</v>
       </c>
       <c r="R3">
-        <v>1577</v>
+        <v>1576.92</v>
       </c>
       <c r="S3">
-        <v>1750.39</v>
+        <v>1749.11</v>
       </c>
       <c r="T3">
-        <v>-3.36</v>
+        <v>-3.95</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1096,34 +1062,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>63.77</v>
+        <v>61.7</v>
       </c>
       <c r="Z3">
-        <v>39.81</v>
+        <v>40.15</v>
       </c>
       <c r="AA3">
-        <v>21.23</v>
+        <v>25.02</v>
       </c>
       <c r="AB3">
-        <v>18.58</v>
+        <v>15.14</v>
       </c>
       <c r="AC3">
-        <v>91.91</v>
+        <v>83.8</v>
       </c>
       <c r="AD3">
-        <v>93.84</v>
+        <v>90.17</v>
       </c>
       <c r="AE3">
-        <v>50.33</v>
+        <v>49.8</v>
       </c>
       <c r="AF3">
-        <v>185.03</v>
+        <v>37.35</v>
       </c>
       <c r="AG3">
-        <v>1739.96</v>
+        <v>1748.67</v>
       </c>
       <c r="AH3">
-        <v>1424.64</v>
+        <v>1435.27</v>
       </c>
       <c r="AI3">
         <v>1583.65</v>
@@ -1132,7 +1098,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>57.22</v>
+        <v>57.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1143,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D4">
-        <v>0.9</v>
+        <v>-0.89</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1155,46 +1121,46 @@
         <v>443.8</v>
       </c>
       <c r="G4">
-        <v>-34.55</v>
+        <v>-35.14</v>
       </c>
       <c r="H4">
-        <v>1.17</v>
+        <v>0.27</v>
       </c>
       <c r="I4">
-        <v>-1.75</v>
+        <v>-3.38</v>
       </c>
       <c r="J4">
-        <v>-1.88</v>
+        <v>-5.32</v>
       </c>
       <c r="K4">
-        <v>-11.76</v>
+        <v>-10.49</v>
       </c>
       <c r="L4">
-        <v>-24.62</v>
+        <v>-24.77</v>
       </c>
       <c r="M4">
-        <v>-7.66</v>
+        <v>-7.82</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>452.99</v>
+        <v>449.88</v>
       </c>
       <c r="Q4">
-        <v>463.15</v>
+        <v>460.88</v>
       </c>
       <c r="R4">
-        <v>483.24</v>
+        <v>481.8</v>
       </c>
       <c r="S4">
-        <v>542.9</v>
+        <v>541.88</v>
       </c>
       <c r="T4">
-        <v>-17.3</v>
+        <v>-17.88</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1209,43 +1175,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.25</v>
+        <v>37.31</v>
       </c>
       <c r="Z4">
-        <v>-9.390000000000001</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="AA4">
         <v>-9.52</v>
       </c>
       <c r="AB4">
-        <v>0.13</v>
+        <v>-0.01</v>
       </c>
       <c r="AC4">
-        <v>42.46</v>
+        <v>44.67</v>
       </c>
       <c r="AD4">
-        <v>51.05</v>
+        <v>46.12</v>
       </c>
       <c r="AE4">
-        <v>12.71</v>
+        <v>12.95</v>
       </c>
       <c r="AF4">
-        <v>96.3</v>
+        <v>122.26</v>
       </c>
       <c r="AG4">
-        <v>496.87</v>
+        <v>492.92</v>
       </c>
       <c r="AH4">
-        <v>429.44</v>
+        <v>428.84</v>
       </c>
       <c r="AI4">
-        <v>486.59</v>
+        <v>482.11</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>30.22</v>
+        <v>32.87</v>
       </c>
     </row>
   </sheetData>
@@ -1386,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1406,502 +1372,447 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>62</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2.89</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2.81</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>18.48</v>
+      </c>
+      <c r="D8" s="5">
+        <v>16.67</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-1.88</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-5.32</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-2.95</v>
-      </c>
-      <c r="D8" s="6">
-        <v>2.89</v>
-      </c>
-      <c r="E8" s="7">
-        <v>5.84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2.99</v>
+      </c>
+      <c r="D10" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>17.34</v>
-      </c>
-      <c r="D9" s="6">
-        <v>18.48</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4.16</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-0.6</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-4.76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-5.62</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-1.88</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-1.75</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-3.38</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-1.39</v>
-      </c>
-      <c r="D11" s="6">
-        <v>2.99</v>
-      </c>
-      <c r="E11" s="7">
-        <v>4.38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.66</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1.28</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>7.74</v>
-      </c>
-      <c r="D12" s="6">
-        <v>4.16</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-3.58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-7.71</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-2.73</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-1.75</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-24.62</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-24.77</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.73</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.66</v>
-      </c>
-      <c r="E14" s="7">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.03</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.27</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-8.369999999999999</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-8.550000000000001</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>4.17</v>
+      </c>
+      <c r="D17" s="5">
+        <v>4.21</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-24.75</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-24.62</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-11.76</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-10.49</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-5.48</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.03</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-5.04</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-4.52</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-5.6</v>
-      </c>
-      <c r="D18" s="6">
-        <v>4.17</v>
-      </c>
-      <c r="E18" s="7">
-        <v>9.77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-16.89</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-17.45</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-15.26</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-11.76</v>
-      </c>
-      <c r="E19" s="7">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-34.55</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-35.14</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-8.51</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-5.04</v>
-      </c>
-      <c r="E20" s="7">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1389.4</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1397</v>
+      </c>
+      <c r="E22" s="7">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-15.83</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-16.89</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1691.5</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1680.1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-11.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-35.14</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-34.55</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>449</v>
+      </c>
+      <c r="D24" s="5">
+        <v>445</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1338.6</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1389.4</v>
-      </c>
-      <c r="E23" s="7">
-        <v>50.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>57.75</v>
+      </c>
+      <c r="D25" s="5">
+        <v>59.24</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1713</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1691.5</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-21.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>63.77</v>
+      </c>
+      <c r="D26" s="5">
+        <v>61.7</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>445</v>
-      </c>
-      <c r="D25" s="6">
-        <v>449</v>
-      </c>
-      <c r="E25" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>39.25</v>
+      </c>
+      <c r="D27" s="5">
+        <v>37.31</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>45.35</v>
-      </c>
-      <c r="D26" s="6">
-        <v>57.75</v>
-      </c>
-      <c r="E26" s="7">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>80.43000000000001</v>
+      </c>
+      <c r="D28" s="5">
+        <v>51.97</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-28.46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>67.75</v>
-      </c>
-      <c r="D27" s="6">
-        <v>63.77</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-3.98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>185.03</v>
+      </c>
+      <c r="D29" s="5">
+        <v>37.35</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-147.68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>36.16</v>
-      </c>
-      <c r="D28" s="6">
-        <v>39.25</v>
-      </c>
-      <c r="E28" s="7">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-12.47</v>
-      </c>
-      <c r="D29" s="6">
-        <v>80.43000000000001</v>
-      </c>
-      <c r="E29" s="7">
-        <v>92.90000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="D30" s="6">
-        <v>185.03</v>
+      <c r="C30" s="5">
+        <v>96.3</v>
+      </c>
+      <c r="D30" s="5">
+        <v>122.26</v>
       </c>
       <c r="E30" s="7">
-        <v>114.68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>46.18</v>
-      </c>
-      <c r="D31" s="6">
-        <v>96.3</v>
-      </c>
-      <c r="E31" s="7">
-        <v>50.12</v>
+        <v>25.96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1921,60 +1832,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>53.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>52.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>6.5</v>
-      </c>
-      <c r="G2" s="11">
+      <c r="F2" s="10">
+        <v>4.7</v>
+      </c>
+      <c r="G2" s="10">
         <v>-3.2</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2076,25 +1987,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1398</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0292</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0766</v>
+      <c r="A2" s="13">
+        <v>0.141</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0278</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.07820000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -750,7 +750,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -883,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1397</v>
+        <v>1381</v>
       </c>
       <c r="D2">
-        <v>0.55</v>
+        <v>-1.15</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -895,25 +896,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-4.52</v>
+        <v>-5.61</v>
       </c>
       <c r="H2">
-        <v>15.85</v>
+        <v>14.52</v>
       </c>
       <c r="I2">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="J2">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="K2">
-        <v>-3.27</v>
+        <v>-5.42</v>
       </c>
       <c r="L2">
-        <v>1.28</v>
+        <v>-0.22</v>
       </c>
       <c r="M2">
-        <v>14.1</v>
+        <v>13.76</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -922,19 +923,19 @@
         <v>62</v>
       </c>
       <c r="P2">
-        <v>1365.04</v>
+        <v>1373.24</v>
       </c>
       <c r="Q2">
-        <v>1340.64</v>
+        <v>1342.74</v>
       </c>
       <c r="R2">
-        <v>1384.22</v>
+        <v>1382.69</v>
       </c>
       <c r="S2">
-        <v>1352.95</v>
+        <v>1353.14</v>
       </c>
       <c r="T2">
-        <v>3.26</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,43 +950,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>59.24</v>
+        <v>54.86</v>
       </c>
       <c r="Z2">
-        <v>-1.89</v>
+        <v>0.12</v>
       </c>
       <c r="AA2">
-        <v>-11.54</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="AB2">
-        <v>9.66</v>
+        <v>9.33</v>
       </c>
       <c r="AC2">
-        <v>93.09999999999999</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="AD2">
-        <v>91.09</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="AE2">
-        <v>24.64</v>
+        <v>25.3</v>
       </c>
       <c r="AF2">
-        <v>51.97</v>
+        <v>149.68</v>
       </c>
       <c r="AG2">
-        <v>1390.76</v>
+        <v>1396</v>
       </c>
       <c r="AH2">
-        <v>1290.52</v>
+        <v>1289.49</v>
       </c>
       <c r="AI2">
-        <v>1315.49</v>
+        <v>1318.95</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>35.9</v>
+        <v>39.86</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1680.1</v>
+        <v>1650</v>
       </c>
       <c r="D3">
-        <v>-0.67</v>
+        <v>-1.79</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1008,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-17.45</v>
+        <v>-18.93</v>
       </c>
       <c r="H3">
-        <v>17.68</v>
+        <v>15.57</v>
       </c>
       <c r="I3">
-        <v>-0.6</v>
+        <v>-1.43</v>
       </c>
       <c r="J3">
-        <v>16.67</v>
+        <v>10.98</v>
       </c>
       <c r="K3">
-        <v>4.21</v>
+        <v>1.75</v>
       </c>
       <c r="L3">
-        <v>-7.71</v>
+        <v>-10.41</v>
       </c>
       <c r="M3">
-        <v>2.78</v>
+        <v>2.27</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P3">
-        <v>1690.08</v>
+        <v>1685.28</v>
       </c>
       <c r="Q3">
-        <v>1591.97</v>
+        <v>1601.56</v>
       </c>
       <c r="R3">
-        <v>1576.92</v>
+        <v>1576.76</v>
       </c>
       <c r="S3">
-        <v>1749.11</v>
+        <v>1747.62</v>
       </c>
       <c r="T3">
-        <v>-3.95</v>
+        <v>-5.59</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1062,34 +1063,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>61.7</v>
+        <v>56.48</v>
       </c>
       <c r="Z3">
-        <v>40.15</v>
+        <v>37.56</v>
       </c>
       <c r="AA3">
-        <v>25.02</v>
+        <v>27.53</v>
       </c>
       <c r="AB3">
-        <v>15.14</v>
+        <v>10.04</v>
       </c>
       <c r="AC3">
-        <v>83.8</v>
+        <v>65.61</v>
       </c>
       <c r="AD3">
-        <v>90.17</v>
+        <v>80.44</v>
       </c>
       <c r="AE3">
-        <v>49.8</v>
+        <v>49.99</v>
       </c>
       <c r="AF3">
-        <v>37.35</v>
+        <v>-56.74</v>
       </c>
       <c r="AG3">
-        <v>1748.67</v>
+        <v>1746.83</v>
       </c>
       <c r="AH3">
-        <v>1435.27</v>
+        <v>1456.3</v>
       </c>
       <c r="AI3">
         <v>1583.65</v>
@@ -1098,7 +1099,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>57.68</v>
+        <v>55.89</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,58 +1110,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D4">
-        <v>-0.89</v>
+        <v>-1.57</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
       </c>
       <c r="F4">
-        <v>443.8</v>
+        <v>438</v>
       </c>
       <c r="G4">
-        <v>-35.14</v>
+        <v>-36.16</v>
       </c>
       <c r="H4">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-3.38</v>
+        <v>-5.48</v>
       </c>
       <c r="J4">
-        <v>-5.32</v>
+        <v>-10.7</v>
       </c>
       <c r="K4">
-        <v>-10.49</v>
+        <v>-12.12</v>
       </c>
       <c r="L4">
-        <v>-24.77</v>
+        <v>-26.51</v>
       </c>
       <c r="M4">
-        <v>-7.82</v>
+        <v>-7.72</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>449.88</v>
+        <v>444.8</v>
       </c>
       <c r="Q4">
-        <v>460.88</v>
+        <v>458.18</v>
       </c>
       <c r="R4">
-        <v>481.8</v>
+        <v>480.42</v>
       </c>
       <c r="S4">
-        <v>541.88</v>
+        <v>540.8099999999999</v>
       </c>
       <c r="T4">
-        <v>-17.88</v>
+        <v>-19.01</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1175,48 +1176,108 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.31</v>
+        <v>34.13</v>
       </c>
       <c r="Z4">
-        <v>-9.529999999999999</v>
+        <v>-10.09</v>
       </c>
       <c r="AA4">
-        <v>-9.52</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="AB4">
-        <v>-0.01</v>
+        <v>-0.46</v>
       </c>
       <c r="AC4">
-        <v>44.67</v>
+        <v>39.85</v>
       </c>
       <c r="AD4">
-        <v>46.12</v>
+        <v>42.33</v>
       </c>
       <c r="AE4">
         <v>12.95</v>
       </c>
       <c r="AF4">
-        <v>122.26</v>
+        <v>-47.66</v>
       </c>
       <c r="AG4">
-        <v>492.92</v>
+        <v>488.22</v>
       </c>
       <c r="AH4">
-        <v>428.84</v>
+        <v>428.14</v>
       </c>
       <c r="AI4">
-        <v>482.11</v>
+        <v>480.39</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>32.87</v>
+        <v>35.2</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK4"/>
   <conditionalFormatting sqref="AF2:AF4">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D4">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I4">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J4">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K4">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1228,8 +1289,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N4">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1240,72 +1307,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="T2:T4">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>0</formula>
@@ -1315,26 +1316,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U4">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V4">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W4">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1352,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1409,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="D7" s="5">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>18.48</v>
+        <v>16.67</v>
       </c>
       <c r="D8" s="5">
-        <v>16.67</v>
+        <v>10.98</v>
       </c>
       <c r="E8" s="6">
-        <v>-1.81</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-1.88</v>
+        <v>-5.32</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.32</v>
+        <v>-10.7</v>
       </c>
       <c r="E9" s="6">
-        <v>-3.44</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1460,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="D10" s="5">
-        <v>3.1</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.11</v>
+        <v>3.06</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1477,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>4.16</v>
+        <v>-0.6</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.6</v>
+        <v>-1.43</v>
       </c>
       <c r="E11" s="6">
-        <v>-4.76</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1494,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-1.75</v>
+        <v>-3.38</v>
       </c>
       <c r="D12" s="5">
-        <v>-3.38</v>
+        <v>-5.48</v>
       </c>
       <c r="E12" s="6">
-        <v>-1.63</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1511,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>0.66</v>
+        <v>1.28</v>
       </c>
       <c r="D13" s="5">
-        <v>1.28</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.62</v>
+        <v>-0.22</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1528,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-8.550000000000001</v>
+        <v>-7.71</v>
       </c>
       <c r="D14" s="5">
-        <v>-7.71</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.84</v>
+        <v>-10.41</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1545,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-24.62</v>
+        <v>-24.77</v>
       </c>
       <c r="D15" s="5">
-        <v>-24.77</v>
+        <v>-26.51</v>
       </c>
       <c r="E15" s="6">
-        <v>-0.15</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1562,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-2.03</v>
+        <v>-3.27</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.27</v>
+        <v>-5.42</v>
       </c>
       <c r="E16" s="6">
-        <v>-1.24</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1579,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="D17" s="5">
-        <v>4.21</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.04</v>
+        <v>1.75</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1596,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-11.76</v>
+        <v>-10.49</v>
       </c>
       <c r="D18" s="5">
-        <v>-10.49</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.27</v>
+        <v>-12.12</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1613,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-5.04</v>
+        <v>-4.52</v>
       </c>
       <c r="D19" s="5">
-        <v>-4.52</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.52</v>
+        <v>-5.61</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1630,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-16.89</v>
+        <v>-17.45</v>
       </c>
       <c r="D20" s="5">
-        <v>-17.45</v>
+        <v>-18.93</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.5600000000000001</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1647,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-34.55</v>
+        <v>-35.14</v>
       </c>
       <c r="D21" s="5">
-        <v>-35.14</v>
+        <v>-36.16</v>
       </c>
       <c r="E21" s="6">
-        <v>-0.59</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1664,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1389.4</v>
+        <v>1397</v>
       </c>
       <c r="D22" s="5">
-        <v>1397</v>
-      </c>
-      <c r="E22" s="7">
-        <v>7.6</v>
+        <v>1381</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-16</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1681,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1691.5</v>
+        <v>1680.1</v>
       </c>
       <c r="D23" s="5">
-        <v>1680.1</v>
+        <v>1650</v>
       </c>
       <c r="E23" s="6">
-        <v>-11.4</v>
+        <v>-30.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1698,115 +1699,132 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D24" s="5">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="E24" s="6">
-        <v>-4</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C25" s="5">
-        <v>57.75</v>
+        <v>34</v>
       </c>
       <c r="D25" s="5">
-        <v>59.24</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.49</v>
+        <v>33</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>63.77</v>
+        <v>59.24</v>
       </c>
       <c r="D26" s="5">
-        <v>61.7</v>
+        <v>54.86</v>
       </c>
       <c r="E26" s="6">
-        <v>-2.07</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>39.25</v>
+        <v>61.7</v>
       </c>
       <c r="D27" s="5">
-        <v>37.31</v>
+        <v>56.48</v>
       </c>
       <c r="E27" s="6">
-        <v>-1.94</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C28" s="5">
-        <v>80.43000000000001</v>
+        <v>37.31</v>
       </c>
       <c r="D28" s="5">
-        <v>51.97</v>
+        <v>34.13</v>
       </c>
       <c r="E28" s="6">
-        <v>-28.46</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>185.03</v>
+        <v>51.97</v>
       </c>
       <c r="D29" s="5">
-        <v>37.35</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-147.68</v>
+        <v>149.68</v>
+      </c>
+      <c r="E29" s="7">
+        <v>97.70999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>96.3</v>
+        <v>37.35</v>
       </c>
       <c r="D30" s="5">
+        <v>-56.74</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-94.09</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5">
         <v>122.26</v>
       </c>
-      <c r="E30" s="7">
-        <v>25.96</v>
+      <c r="D31" s="5">
+        <v>-47.66</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-169.92</v>
       </c>
     </row>
   </sheetData>
@@ -1865,25 +1883,25 @@
         <v>40</v>
       </c>
       <c r="B2" s="10">
-        <v>48.52</v>
+        <v>49.72</v>
       </c>
       <c r="C2" s="11">
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>52.8</v>
+        <v>48.5</v>
       </c>
       <c r="E2" s="10">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="F2" s="10">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="G2" s="10">
-        <v>-3.2</v>
+        <v>-5.3</v>
       </c>
       <c r="H2" s="10">
-        <v>66.3</v>
+        <v>66</v>
       </c>
       <c r="I2" s="10">
         <v>0</v>
@@ -1999,13 +2017,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.141</v>
+        <v>0.1376</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0278</v>
+        <v>0.0227</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.07820000000000001</v>
+        <v>-0.07719999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="D2">
-        <v>-1.15</v>
+        <v>0.29</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,46 +896,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-5.61</v>
+        <v>-5.34</v>
       </c>
       <c r="H2">
-        <v>14.52</v>
+        <v>14.85</v>
       </c>
       <c r="I2">
-        <v>3.06</v>
+        <v>1.82</v>
       </c>
       <c r="J2">
-        <v>2.48</v>
+        <v>3.44</v>
       </c>
       <c r="K2">
-        <v>-5.42</v>
+        <v>-5.34</v>
       </c>
       <c r="L2">
-        <v>-0.22</v>
+        <v>-0.96</v>
       </c>
       <c r="M2">
-        <v>13.76</v>
+        <v>13.58</v>
       </c>
       <c r="N2">
+        <v>99</v>
+      </c>
+      <c r="O2">
         <v>66</v>
       </c>
-      <c r="O2">
-        <v>62</v>
-      </c>
       <c r="P2">
-        <v>1373.24</v>
+        <v>1378.2</v>
       </c>
       <c r="Q2">
-        <v>1342.74</v>
+        <v>1344.74</v>
       </c>
       <c r="R2">
-        <v>1382.69</v>
+        <v>1381.97</v>
       </c>
       <c r="S2">
-        <v>1353.14</v>
+        <v>1353.35</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,43 +950,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>54.86</v>
+        <v>55.74</v>
       </c>
       <c r="Z2">
-        <v>0.12</v>
+        <v>2.02</v>
       </c>
       <c r="AA2">
-        <v>-9.210000000000001</v>
+        <v>-6.97</v>
       </c>
       <c r="AB2">
-        <v>9.33</v>
+        <v>8.98</v>
       </c>
       <c r="AC2">
-        <v>96.01000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="AD2">
-        <v>94.06999999999999</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="AE2">
-        <v>25.3</v>
+        <v>25.54</v>
       </c>
       <c r="AF2">
-        <v>149.68</v>
+        <v>60.9</v>
       </c>
       <c r="AG2">
-        <v>1396</v>
+        <v>1401.26</v>
       </c>
       <c r="AH2">
-        <v>1289.49</v>
+        <v>1288.23</v>
       </c>
       <c r="AI2">
-        <v>1318.95</v>
+        <v>1319.72</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>39.86</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="D3">
-        <v>-1.79</v>
+        <v>-0.61</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-18.93</v>
+        <v>-19.42</v>
       </c>
       <c r="H3">
-        <v>15.57</v>
+        <v>14.87</v>
       </c>
       <c r="I3">
-        <v>-1.43</v>
+        <v>-3.06</v>
       </c>
       <c r="J3">
-        <v>10.98</v>
+        <v>12.48</v>
       </c>
       <c r="K3">
-        <v>1.75</v>
+        <v>0.99</v>
       </c>
       <c r="L3">
-        <v>-10.41</v>
+        <v>-18.25</v>
       </c>
       <c r="M3">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="O3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>1685.28</v>
+        <v>1674.92</v>
       </c>
       <c r="Q3">
-        <v>1601.56</v>
+        <v>1608.11</v>
       </c>
       <c r="R3">
-        <v>1576.76</v>
+        <v>1576.78</v>
       </c>
       <c r="S3">
-        <v>1747.62</v>
+        <v>1746.05</v>
       </c>
       <c r="T3">
-        <v>-5.59</v>
+        <v>-6.07</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1063,34 +1063,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>56.48</v>
+        <v>54.82</v>
       </c>
       <c r="Z3">
-        <v>37.56</v>
+        <v>34.31</v>
       </c>
       <c r="AA3">
-        <v>27.53</v>
+        <v>28.88</v>
       </c>
       <c r="AB3">
-        <v>10.04</v>
+        <v>5.43</v>
       </c>
       <c r="AC3">
-        <v>65.61</v>
+        <v>42.03</v>
       </c>
       <c r="AD3">
-        <v>80.44</v>
+        <v>63.82</v>
       </c>
       <c r="AE3">
-        <v>49.99</v>
+        <v>49</v>
       </c>
       <c r="AF3">
-        <v>-56.74</v>
+        <v>-53.38</v>
       </c>
       <c r="AG3">
-        <v>1746.83</v>
+        <v>1747.51</v>
       </c>
       <c r="AH3">
-        <v>1456.3</v>
+        <v>1468.71</v>
       </c>
       <c r="AI3">
         <v>1583.65</v>
@@ -1099,7 +1099,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>55.89</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,58 +1110,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>438</v>
+        <v>431.5</v>
       </c>
       <c r="D4">
-        <v>-1.57</v>
+        <v>-1.48</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
       </c>
       <c r="F4">
-        <v>438</v>
+        <v>431.5</v>
       </c>
       <c r="G4">
-        <v>-36.16</v>
+        <v>-37.11</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-5.48</v>
+        <v>-3.47</v>
       </c>
       <c r="J4">
-        <v>-10.7</v>
+        <v>-12.3</v>
       </c>
       <c r="K4">
-        <v>-12.12</v>
+        <v>-13.79</v>
       </c>
       <c r="L4">
-        <v>-26.51</v>
+        <v>-26.36</v>
       </c>
       <c r="M4">
-        <v>-7.72</v>
+        <v>-7.12</v>
       </c>
       <c r="N4">
         <v>33</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>444.8</v>
+        <v>441.7</v>
       </c>
       <c r="Q4">
-        <v>458.18</v>
+        <v>455.1</v>
       </c>
       <c r="R4">
-        <v>480.42</v>
+        <v>479.03</v>
       </c>
       <c r="S4">
-        <v>540.8099999999999</v>
+        <v>539.64</v>
       </c>
       <c r="T4">
-        <v>-19.01</v>
+        <v>-20.04</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,43 +1176,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.13</v>
+        <v>31.44</v>
       </c>
       <c r="Z4">
-        <v>-10.09</v>
+        <v>-10.94</v>
       </c>
       <c r="AA4">
-        <v>-9.640000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="AB4">
-        <v>-0.46</v>
+        <v>-1.04</v>
       </c>
       <c r="AC4">
-        <v>39.85</v>
+        <v>21.42</v>
       </c>
       <c r="AD4">
-        <v>42.33</v>
+        <v>35.31</v>
       </c>
       <c r="AE4">
-        <v>12.95</v>
+        <v>12.98</v>
       </c>
       <c r="AF4">
-        <v>-47.66</v>
+        <v>-32.08</v>
       </c>
       <c r="AG4">
-        <v>488.22</v>
+        <v>482.62</v>
       </c>
       <c r="AH4">
-        <v>428.14</v>
+        <v>427.59</v>
       </c>
       <c r="AI4">
-        <v>480.39</v>
+        <v>471.54</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>35.2</v>
+        <v>38.74</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="D7" s="5">
-        <v>2.48</v>
+        <v>3.44</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.33</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>16.67</v>
+        <v>10.98</v>
       </c>
       <c r="D8" s="5">
-        <v>10.98</v>
+        <v>12.48</v>
       </c>
       <c r="E8" s="6">
-        <v>-5.69</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.32</v>
+        <v>-10.7</v>
       </c>
       <c r="D9" s="5">
-        <v>-10.7</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-5.38</v>
+        <v>-12.3</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="D10" s="5">
-        <v>3.06</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.04</v>
+        <v>1.82</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-0.6</v>
+        <v>-1.43</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.43</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.83</v>
+        <v>-3.06</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-3.38</v>
+        <v>-5.48</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.48</v>
+        <v>-3.47</v>
       </c>
       <c r="E12" s="6">
-        <v>-2.1</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>1.28</v>
+        <v>-0.22</v>
       </c>
       <c r="D13" s="5">
-        <v>-0.22</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-1.5</v>
+        <v>-0.96</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-7.71</v>
+        <v>-10.41</v>
       </c>
       <c r="D14" s="5">
-        <v>-10.41</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-2.7</v>
+        <v>-18.25</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-7.84</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-24.77</v>
+        <v>-26.51</v>
       </c>
       <c r="D15" s="5">
-        <v>-26.51</v>
+        <v>-26.36</v>
       </c>
       <c r="E15" s="6">
-        <v>-1.74</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-3.27</v>
+        <v>-5.42</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.42</v>
+        <v>-5.34</v>
       </c>
       <c r="E16" s="6">
-        <v>-2.15</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>4.21</v>
+        <v>1.75</v>
       </c>
       <c r="D17" s="5">
-        <v>1.75</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-2.46</v>
+        <v>0.99</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-10.49</v>
+        <v>-12.12</v>
       </c>
       <c r="D18" s="5">
-        <v>-12.12</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-1.63</v>
+        <v>-13.79</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-4.52</v>
+        <v>-5.61</v>
       </c>
       <c r="D19" s="5">
-        <v>-5.61</v>
+        <v>-5.34</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.09</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-17.45</v>
+        <v>-18.93</v>
       </c>
       <c r="D20" s="5">
-        <v>-18.93</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.48</v>
+        <v>-19.42</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-35.14</v>
+        <v>-36.16</v>
       </c>
       <c r="D21" s="5">
-        <v>-36.16</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.02</v>
+        <v>-37.11</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1397</v>
+        <v>1381</v>
       </c>
       <c r="D22" s="5">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="E22" s="6">
-        <v>-16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1680.1</v>
+        <v>1650</v>
       </c>
       <c r="D23" s="5">
-        <v>1650</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-30.1</v>
+        <v>1640</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-10</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,132 +1699,149 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D24" s="5">
-        <v>438</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-7</v>
+        <v>431.5</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-6.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C25" s="5">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D25" s="5">
+        <v>99</v>
+      </c>
+      <c r="E25" s="6">
         <v>33</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C26" s="5">
-        <v>59.24</v>
+        <v>99</v>
       </c>
       <c r="D26" s="5">
-        <v>54.86</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-4.38</v>
+        <v>66</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-33</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>61.7</v>
+        <v>54.86</v>
       </c>
       <c r="D27" s="5">
-        <v>56.48</v>
+        <v>55.74</v>
       </c>
       <c r="E27" s="6">
-        <v>-5.22</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="5">
-        <v>37.31</v>
+        <v>56.48</v>
       </c>
       <c r="D28" s="5">
-        <v>34.13</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-3.18</v>
+        <v>54.82</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C29" s="5">
-        <v>51.97</v>
+        <v>34.13</v>
       </c>
       <c r="D29" s="5">
-        <v>149.68</v>
+        <v>31.44</v>
       </c>
       <c r="E29" s="7">
-        <v>97.70999999999999</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>37.35</v>
+        <v>149.68</v>
       </c>
       <c r="D30" s="5">
-        <v>-56.74</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-94.09</v>
+        <v>60.9</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-88.78</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="5">
-        <v>122.26</v>
+        <v>-56.74</v>
       </c>
       <c r="D31" s="5">
+        <v>-53.38</v>
+      </c>
+      <c r="E31" s="6">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="5">
         <v>-47.66</v>
       </c>
-      <c r="E31" s="6">
-        <v>-169.92</v>
+      <c r="D32" s="5">
+        <v>-32.08</v>
+      </c>
+      <c r="E32" s="6">
+        <v>15.58</v>
       </c>
     </row>
   </sheetData>
@@ -1889,16 +1906,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>48.5</v>
+        <v>47.3</v>
       </c>
       <c r="E2" s="10">
         <v>33.3</v>
       </c>
       <c r="F2" s="10">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G2" s="10">
-        <v>-5.3</v>
+        <v>-6</v>
       </c>
       <c r="H2" s="10">
         <v>66</v>
@@ -2017,13 +2034,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1376</v>
+        <v>0.1358</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0227</v>
+        <v>0.0247</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.07719999999999999</v>
+        <v>-0.0712</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1385</v>
+        <v>1398.5</v>
       </c>
       <c r="D2">
-        <v>0.29</v>
+        <v>0.97</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,46 +896,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-5.34</v>
+        <v>-4.42</v>
       </c>
       <c r="H2">
-        <v>14.85</v>
+        <v>15.97</v>
       </c>
       <c r="I2">
-        <v>1.82</v>
+        <v>4.47</v>
       </c>
       <c r="J2">
-        <v>3.44</v>
+        <v>3.98</v>
       </c>
       <c r="K2">
-        <v>-5.34</v>
+        <v>-2.93</v>
       </c>
       <c r="L2">
-        <v>-0.96</v>
+        <v>-1.33</v>
       </c>
       <c r="M2">
-        <v>13.58</v>
+        <v>13.68</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>1378.2</v>
+        <v>1390.18</v>
       </c>
       <c r="Q2">
-        <v>1344.74</v>
+        <v>1347.69</v>
       </c>
       <c r="R2">
-        <v>1381.97</v>
+        <v>1381.31</v>
       </c>
       <c r="S2">
-        <v>1353.35</v>
+        <v>1353.66</v>
       </c>
       <c r="T2">
-        <v>2.34</v>
+        <v>3.31</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +950,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>55.74</v>
+        <v>58.67</v>
       </c>
       <c r="Z2">
-        <v>2.02</v>
+        <v>4.55</v>
       </c>
       <c r="AA2">
-        <v>-6.97</v>
+        <v>-4.66</v>
       </c>
       <c r="AB2">
-        <v>8.98</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AC2">
-        <v>91.42</v>
+        <v>90.67</v>
       </c>
       <c r="AD2">
-        <v>93.51000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="AE2">
-        <v>25.54</v>
+        <v>25.5</v>
       </c>
       <c r="AF2">
-        <v>60.9</v>
+        <v>41.34</v>
       </c>
       <c r="AG2">
-        <v>1401.26</v>
+        <v>1409.01</v>
       </c>
       <c r="AH2">
-        <v>1288.23</v>
+        <v>1286.37</v>
       </c>
       <c r="AI2">
         <v>1319.72</v>
@@ -986,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>43.3</v>
+        <v>43.55</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1640</v>
+        <v>1633</v>
       </c>
       <c r="D3">
-        <v>-0.61</v>
+        <v>-0.43</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-19.42</v>
+        <v>-19.76</v>
       </c>
       <c r="H3">
-        <v>14.87</v>
+        <v>14.38</v>
       </c>
       <c r="I3">
-        <v>-3.06</v>
+        <v>-4.67</v>
       </c>
       <c r="J3">
-        <v>12.48</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="K3">
-        <v>0.99</v>
+        <v>3.13</v>
       </c>
       <c r="L3">
-        <v>-18.25</v>
+        <v>-18.19</v>
       </c>
       <c r="M3">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P3">
-        <v>1674.92</v>
+        <v>1658.92</v>
       </c>
       <c r="Q3">
-        <v>1608.11</v>
+        <v>1615.76</v>
       </c>
       <c r="R3">
-        <v>1576.78</v>
+        <v>1576.46</v>
       </c>
       <c r="S3">
-        <v>1746.05</v>
+        <v>1744.47</v>
       </c>
       <c r="T3">
-        <v>-6.07</v>
+        <v>-6.39</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1063,34 +1063,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>54.82</v>
+        <v>53.64</v>
       </c>
       <c r="Z3">
-        <v>34.31</v>
+        <v>30.81</v>
       </c>
       <c r="AA3">
-        <v>28.88</v>
+        <v>29.27</v>
       </c>
       <c r="AB3">
-        <v>5.43</v>
+        <v>1.54</v>
       </c>
       <c r="AC3">
-        <v>42.03</v>
+        <v>19.04</v>
       </c>
       <c r="AD3">
-        <v>63.82</v>
+        <v>42.23</v>
       </c>
       <c r="AE3">
-        <v>49</v>
+        <v>48.04</v>
       </c>
       <c r="AF3">
-        <v>-53.38</v>
+        <v>-73.44</v>
       </c>
       <c r="AG3">
-        <v>1747.51</v>
+        <v>1741.7</v>
       </c>
       <c r="AH3">
-        <v>1468.71</v>
+        <v>1489.82</v>
       </c>
       <c r="AI3">
         <v>1583.65</v>
@@ -1099,7 +1099,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>52.56</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,58 +1110,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>431.5</v>
+        <v>431</v>
       </c>
       <c r="D4">
-        <v>-1.48</v>
+        <v>-0.12</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
       </c>
       <c r="F4">
-        <v>431.5</v>
+        <v>431</v>
       </c>
       <c r="G4">
-        <v>-37.11</v>
+        <v>-37.18</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-3.47</v>
+        <v>-3.15</v>
       </c>
       <c r="J4">
-        <v>-12.3</v>
+        <v>-12.58</v>
       </c>
       <c r="K4">
-        <v>-13.79</v>
+        <v>-13.71</v>
       </c>
       <c r="L4">
-        <v>-26.36</v>
+        <v>-26.32</v>
       </c>
       <c r="M4">
-        <v>-7.12</v>
+        <v>-6.88</v>
       </c>
       <c r="N4">
         <v>33</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>441.7</v>
+        <v>438.9</v>
       </c>
       <c r="Q4">
-        <v>455.1</v>
+        <v>452.32</v>
       </c>
       <c r="R4">
-        <v>479.03</v>
+        <v>477.66</v>
       </c>
       <c r="S4">
-        <v>539.64</v>
+        <v>538.4299999999999</v>
       </c>
       <c r="T4">
-        <v>-20.04</v>
+        <v>-19.95</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,43 +1176,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.44</v>
+        <v>31.24</v>
       </c>
       <c r="Z4">
-        <v>-10.94</v>
+        <v>-11.52</v>
       </c>
       <c r="AA4">
-        <v>-9.9</v>
+        <v>-10.22</v>
       </c>
       <c r="AB4">
-        <v>-1.04</v>
+        <v>-1.3</v>
       </c>
       <c r="AC4">
-        <v>21.42</v>
+        <v>7.16</v>
       </c>
       <c r="AD4">
-        <v>35.31</v>
+        <v>22.81</v>
       </c>
       <c r="AE4">
-        <v>12.98</v>
+        <v>12.76</v>
       </c>
       <c r="AF4">
-        <v>-32.08</v>
+        <v>-29.67</v>
       </c>
       <c r="AG4">
-        <v>482.62</v>
+        <v>477.57</v>
       </c>
       <c r="AH4">
-        <v>427.59</v>
+        <v>427.08</v>
       </c>
       <c r="AI4">
-        <v>471.54</v>
+        <v>465.78</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>38.74</v>
+        <v>42.27</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>2.48</v>
+        <v>3.44</v>
       </c>
       <c r="D7" s="5">
-        <v>3.44</v>
+        <v>3.98</v>
       </c>
       <c r="E7" s="6">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>10.98</v>
+        <v>12.48</v>
       </c>
       <c r="D8" s="5">
-        <v>12.48</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1.5</v>
+        <v>8.210000000000001</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-4.27</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-10.7</v>
+        <v>-12.3</v>
       </c>
       <c r="D9" s="5">
-        <v>-12.3</v>
+        <v>-12.58</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.6</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>3.06</v>
+        <v>1.82</v>
       </c>
       <c r="D10" s="5">
-        <v>1.82</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.24</v>
+        <v>4.47</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.65</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-1.43</v>
+        <v>-3.06</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.06</v>
+        <v>-4.67</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.63</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.48</v>
+        <v>-3.47</v>
       </c>
       <c r="D12" s="5">
-        <v>-3.47</v>
+        <v>-3.15</v>
       </c>
       <c r="E12" s="6">
-        <v>2.01</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-0.22</v>
+        <v>-0.96</v>
       </c>
       <c r="D13" s="5">
-        <v>-0.96</v>
+        <v>-1.33</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.74</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-10.41</v>
+        <v>-18.25</v>
       </c>
       <c r="D14" s="5">
-        <v>-18.25</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-7.84</v>
+        <v>-18.19</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.06</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-26.51</v>
+        <v>-26.36</v>
       </c>
       <c r="D15" s="5">
-        <v>-26.36</v>
+        <v>-26.32</v>
       </c>
       <c r="E15" s="6">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-5.42</v>
+        <v>-5.34</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.34</v>
+        <v>-2.93</v>
       </c>
       <c r="E16" s="6">
-        <v>0.08</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>1.75</v>
+        <v>0.99</v>
       </c>
       <c r="D17" s="5">
-        <v>0.99</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.76</v>
+        <v>3.13</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.14</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-12.12</v>
+        <v>-13.79</v>
       </c>
       <c r="D18" s="5">
-        <v>-13.79</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.67</v>
+        <v>-13.71</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.08</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-5.61</v>
+        <v>-5.34</v>
       </c>
       <c r="D19" s="5">
-        <v>-5.34</v>
+        <v>-4.42</v>
       </c>
       <c r="E19" s="6">
-        <v>0.27</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-18.93</v>
+        <v>-19.42</v>
       </c>
       <c r="D20" s="5">
-        <v>-19.42</v>
+        <v>-19.76</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.49</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-36.16</v>
+        <v>-37.11</v>
       </c>
       <c r="D21" s="5">
-        <v>-37.11</v>
+        <v>-37.18</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.95</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="D22" s="5">
-        <v>1385</v>
+        <v>1398.5</v>
       </c>
       <c r="E22" s="6">
-        <v>4</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="D23" s="5">
-        <v>1640</v>
+        <v>1633</v>
       </c>
       <c r="E23" s="7">
-        <v>-10</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>438</v>
+        <v>431.5</v>
       </c>
       <c r="D24" s="5">
-        <v>431.5</v>
+        <v>431</v>
       </c>
       <c r="E24" s="7">
-        <v>-6.5</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1713,16 +1713,16 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>66</v>
+        <v>55.74</v>
       </c>
       <c r="D25" s="5">
-        <v>99</v>
+        <v>58.67</v>
       </c>
       <c r="E25" s="6">
-        <v>33</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1730,118 +1730,84 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>99</v>
+        <v>54.82</v>
       </c>
       <c r="D26" s="5">
-        <v>66</v>
+        <v>53.64</v>
       </c>
       <c r="E26" s="7">
-        <v>-33</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>54.86</v>
+        <v>31.44</v>
       </c>
       <c r="D27" s="5">
-        <v>55.74</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.88</v>
+        <v>31.24</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>56.48</v>
+        <v>60.9</v>
       </c>
       <c r="D28" s="5">
-        <v>54.82</v>
+        <v>41.34</v>
       </c>
       <c r="E28" s="7">
-        <v>-1.66</v>
+        <v>-19.56</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>34.13</v>
+        <v>-53.38</v>
       </c>
       <c r="D29" s="5">
-        <v>31.44</v>
+        <v>-73.44</v>
       </c>
       <c r="E29" s="7">
-        <v>-2.69</v>
+        <v>-20.06</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>149.68</v>
+        <v>-32.08</v>
       </c>
       <c r="D30" s="5">
-        <v>60.9</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-88.78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-56.74</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-53.38</v>
-      </c>
-      <c r="E31" s="6">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-47.66</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-32.08</v>
-      </c>
-      <c r="E32" s="6">
-        <v>15.58</v>
+        <v>-29.67</v>
+      </c>
+      <c r="E30" s="6">
+        <v>2.41</v>
       </c>
     </row>
   </sheetData>
@@ -1906,16 +1872,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="E2" s="10">
         <v>33.3</v>
       </c>
       <c r="F2" s="10">
-        <v>1.2</v>
+        <v>-0.1</v>
       </c>
       <c r="G2" s="10">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="H2" s="10">
         <v>66</v>
@@ -2034,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1358</v>
+        <v>0.1368</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0247</v>
+        <v>0.0245</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0712</v>
+        <v>-0.0688</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>53.6 → 47.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.6</t>
+  </si>
+  <si>
+    <t>47.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -246,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,17 +389,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -884,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1398.5</v>
+        <v>1394.2</v>
       </c>
       <c r="D2">
-        <v>0.97</v>
+        <v>-0.31</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,46 +924,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-4.42</v>
+        <v>-4.71</v>
       </c>
       <c r="H2">
-        <v>15.97</v>
+        <v>15.61</v>
       </c>
       <c r="I2">
-        <v>4.47</v>
+        <v>0.35</v>
       </c>
       <c r="J2">
-        <v>3.98</v>
+        <v>4.08</v>
       </c>
       <c r="K2">
-        <v>-2.93</v>
+        <v>-2.82</v>
       </c>
       <c r="L2">
-        <v>-1.33</v>
+        <v>-2.95</v>
       </c>
       <c r="M2">
-        <v>13.68</v>
+        <v>11.31</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>1390.18</v>
+        <v>1391.14</v>
       </c>
       <c r="Q2">
-        <v>1347.69</v>
+        <v>1350.4</v>
       </c>
       <c r="R2">
-        <v>1381.31</v>
+        <v>1380.6</v>
       </c>
       <c r="S2">
-        <v>1353.66</v>
+        <v>1353.85</v>
       </c>
       <c r="T2">
-        <v>3.31</v>
+        <v>2.98</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +978,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>58.67</v>
+        <v>57.37</v>
       </c>
       <c r="Z2">
-        <v>4.55</v>
+        <v>6.14</v>
       </c>
       <c r="AA2">
-        <v>-4.66</v>
+        <v>-2.5</v>
       </c>
       <c r="AB2">
-        <v>9.210000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="AC2">
-        <v>90.67</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="AD2">
-        <v>92.7</v>
+        <v>91.05</v>
       </c>
       <c r="AE2">
-        <v>25.5</v>
+        <v>25.57</v>
       </c>
       <c r="AF2">
-        <v>41.34</v>
+        <v>-2.54</v>
       </c>
       <c r="AG2">
-        <v>1409.01</v>
+        <v>1414.99</v>
       </c>
       <c r="AH2">
-        <v>1286.37</v>
+        <v>1285.81</v>
       </c>
       <c r="AI2">
         <v>1319.72</v>
@@ -986,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>43.55</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1633</v>
+        <v>1592</v>
       </c>
       <c r="D3">
-        <v>-0.43</v>
+        <v>-2.51</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1037,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-19.76</v>
+        <v>-21.78</v>
       </c>
       <c r="H3">
-        <v>14.38</v>
+        <v>11.51</v>
       </c>
       <c r="I3">
-        <v>-4.67</v>
+        <v>-5.88</v>
       </c>
       <c r="J3">
-        <v>8.210000000000001</v>
+        <v>7.57</v>
       </c>
       <c r="K3">
-        <v>3.13</v>
+        <v>-1.67</v>
       </c>
       <c r="L3">
-        <v>-18.19</v>
+        <v>-19.88</v>
       </c>
       <c r="M3">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>1658.92</v>
+        <v>1639.02</v>
       </c>
       <c r="Q3">
-        <v>1615.76</v>
+        <v>1620.33</v>
       </c>
       <c r="R3">
-        <v>1576.46</v>
+        <v>1575.43</v>
       </c>
       <c r="S3">
-        <v>1744.47</v>
+        <v>1742.6</v>
       </c>
       <c r="T3">
-        <v>-6.39</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1063,34 +1091,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>53.64</v>
+        <v>47.19</v>
       </c>
       <c r="Z3">
-        <v>30.81</v>
+        <v>24.45</v>
       </c>
       <c r="AA3">
-        <v>29.27</v>
+        <v>28.3</v>
       </c>
       <c r="AB3">
-        <v>1.54</v>
+        <v>-3.86</v>
       </c>
       <c r="AC3">
-        <v>19.04</v>
+        <v>3.9</v>
       </c>
       <c r="AD3">
-        <v>42.23</v>
+        <v>21.66</v>
       </c>
       <c r="AE3">
-        <v>48.04</v>
+        <v>48.4</v>
       </c>
       <c r="AF3">
-        <v>-73.44</v>
+        <v>-75.17</v>
       </c>
       <c r="AG3">
-        <v>1741.7</v>
+        <v>1734.79</v>
       </c>
       <c r="AH3">
-        <v>1489.82</v>
+        <v>1505.87</v>
       </c>
       <c r="AI3">
         <v>1583.65</v>
@@ -1099,7 +1127,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>48.58</v>
+        <v>42.53</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1113,7 +1141,7 @@
         <v>431</v>
       </c>
       <c r="D4">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1128,40 +1156,40 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-3.15</v>
+        <v>-4.01</v>
       </c>
       <c r="J4">
-        <v>-12.58</v>
+        <v>-11.44</v>
       </c>
       <c r="K4">
-        <v>-13.71</v>
+        <v>-14.06</v>
       </c>
       <c r="L4">
-        <v>-26.32</v>
+        <v>-27.4</v>
       </c>
       <c r="M4">
-        <v>-6.88</v>
+        <v>-6.91</v>
       </c>
       <c r="N4">
         <v>33</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="P4">
-        <v>438.9</v>
+        <v>435.3</v>
       </c>
       <c r="Q4">
-        <v>452.32</v>
+        <v>449.65</v>
       </c>
       <c r="R4">
-        <v>477.66</v>
+        <v>476.25</v>
       </c>
       <c r="S4">
-        <v>538.4299999999999</v>
+        <v>537.21</v>
       </c>
       <c r="T4">
-        <v>-19.95</v>
+        <v>-19.77</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1179,40 +1207,40 @@
         <v>31.24</v>
       </c>
       <c r="Z4">
-        <v>-11.52</v>
+        <v>-11.84</v>
       </c>
       <c r="AA4">
-        <v>-10.22</v>
+        <v>-10.54</v>
       </c>
       <c r="AB4">
-        <v>-1.3</v>
+        <v>-1.29</v>
       </c>
       <c r="AC4">
-        <v>7.16</v>
+        <v>0.41</v>
       </c>
       <c r="AD4">
-        <v>22.81</v>
+        <v>9.66</v>
       </c>
       <c r="AE4">
-        <v>12.76</v>
+        <v>12.55</v>
       </c>
       <c r="AF4">
-        <v>-29.67</v>
+        <v>-30.16</v>
       </c>
       <c r="AG4">
-        <v>477.57</v>
+        <v>471.67</v>
       </c>
       <c r="AH4">
-        <v>427.08</v>
+        <v>427.63</v>
       </c>
       <c r="AI4">
-        <v>465.78</v>
+        <v>465.16</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>42.27</v>
+        <v>45.33</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1373,12 +1401,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1386,428 +1449,377 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>3.44</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>3.98</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.54</v>
+      <c r="D7" s="6">
+        <v>4.08</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>12.48</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>8.210000000000001</v>
       </c>
-      <c r="E8" s="7">
-        <v>-4.27</v>
+      <c r="D8" s="6">
+        <v>7.57</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-12.3</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-12.58</v>
       </c>
+      <c r="D9" s="6">
+        <v>-11.44</v>
+      </c>
       <c r="E9" s="7">
-        <v>-0.28</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>1.82</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>4.47</v>
       </c>
-      <c r="E10" s="6">
-        <v>2.65</v>
+      <c r="D10" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-4.12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-3.06</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-4.67</v>
       </c>
-      <c r="E11" s="7">
-        <v>-1.61</v>
+      <c r="D11" s="6">
+        <v>-5.88</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-3.47</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-3.15</v>
       </c>
-      <c r="E12" s="6">
-        <v>0.32</v>
+      <c r="D12" s="6">
+        <v>-4.01</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-0.96</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-1.33</v>
       </c>
-      <c r="E13" s="7">
-        <v>-0.37</v>
+      <c r="D13" s="6">
+        <v>-2.95</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-18.25</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-18.19</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.06</v>
+      <c r="D14" s="6">
+        <v>-19.88</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-26.36</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-26.32</v>
       </c>
-      <c r="E15" s="6">
-        <v>0.04</v>
+      <c r="D15" s="6">
+        <v>-27.4</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-5.34</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-2.93</v>
       </c>
-      <c r="E16" s="6">
-        <v>2.41</v>
+      <c r="D16" s="6">
+        <v>-2.82</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.11</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>0.99</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>3.13</v>
       </c>
-      <c r="E17" s="6">
-        <v>2.14</v>
+      <c r="D17" s="6">
+        <v>-1.67</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-4.8</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-13.79</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-13.71</v>
       </c>
-      <c r="E18" s="6">
-        <v>0.08</v>
+      <c r="D18" s="6">
+        <v>-14.06</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-5.34</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-4.42</v>
       </c>
-      <c r="E19" s="6">
-        <v>0.92</v>
+      <c r="D19" s="6">
+        <v>-4.71</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-19.42</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-19.76</v>
       </c>
-      <c r="E20" s="7">
-        <v>-0.34</v>
+      <c r="D20" s="6">
+        <v>-21.78</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1398.5</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1394.2</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-4.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1633</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1592</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="6">
+        <v>58.67</v>
+      </c>
+      <c r="D23" s="6">
+        <v>57.37</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="6">
+        <v>53.64</v>
+      </c>
+      <c r="D24" s="6">
+        <v>47.19</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-6.45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="6">
+        <v>41.34</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-2.54</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-43.88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-73.44</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-75.17</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-37.11</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-37.18</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1385</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1398.5</v>
-      </c>
-      <c r="E22" s="6">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1640</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1633</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>431.5</v>
-      </c>
-      <c r="D24" s="5">
-        <v>431</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5">
-        <v>55.74</v>
-      </c>
-      <c r="D25" s="5">
-        <v>58.67</v>
-      </c>
-      <c r="E25" s="6">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5">
-        <v>54.82</v>
-      </c>
-      <c r="D26" s="5">
-        <v>53.64</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>31.44</v>
-      </c>
-      <c r="D27" s="5">
-        <v>31.24</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>60.9</v>
-      </c>
-      <c r="D28" s="5">
-        <v>41.34</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-19.56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-53.38</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-73.44</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-20.06</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-32.08</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C27" s="6">
         <v>-29.67</v>
       </c>
-      <c r="E30" s="6">
-        <v>2.41</v>
+      <c r="D27" s="6">
+        <v>-30.16</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -1833,60 +1845,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>49.72</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>47.8</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>45.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>33.3</v>
       </c>
-      <c r="F2" s="10">
-        <v>-0.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-4.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-6.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>66</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1988,25 +2000,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1368</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0245</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0688</v>
+      <c r="A2" s="14">
+        <v>0.1131</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0198</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.06909999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>53.6 → 47.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.6</t>
-  </si>
-  <si>
-    <t>47.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,18 +362,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -778,8 +750,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -912,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1394.2</v>
+        <v>1403</v>
       </c>
       <c r="D2">
-        <v>-0.31</v>
+        <v>0.63</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,46 +895,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-4.71</v>
+        <v>-4.11</v>
       </c>
       <c r="H2">
-        <v>15.61</v>
+        <v>16.34</v>
       </c>
       <c r="I2">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="J2">
-        <v>4.08</v>
+        <v>4.7</v>
       </c>
       <c r="K2">
-        <v>-2.82</v>
+        <v>-2.09</v>
       </c>
       <c r="L2">
-        <v>-2.95</v>
+        <v>0.91</v>
       </c>
       <c r="M2">
-        <v>11.31</v>
+        <v>11.77</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>1391.14</v>
+        <v>1392.34</v>
       </c>
       <c r="Q2">
-        <v>1350.4</v>
+        <v>1353.82</v>
       </c>
       <c r="R2">
-        <v>1380.6</v>
+        <v>1380.03</v>
       </c>
       <c r="S2">
-        <v>1353.85</v>
+        <v>1354.01</v>
       </c>
       <c r="T2">
-        <v>2.98</v>
+        <v>3.62</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +949,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>57.37</v>
+        <v>59.36</v>
       </c>
       <c r="Z2">
-        <v>6.14</v>
+        <v>8.02</v>
       </c>
       <c r="AA2">
-        <v>-2.5</v>
+        <v>-0.4</v>
       </c>
       <c r="AB2">
-        <v>8.65</v>
+        <v>8.42</v>
       </c>
       <c r="AC2">
-        <v>91.06999999999999</v>
+        <v>95.66</v>
       </c>
       <c r="AD2">
-        <v>91.05</v>
+        <v>92.47</v>
       </c>
       <c r="AE2">
-        <v>25.57</v>
+        <v>25.55</v>
       </c>
       <c r="AF2">
-        <v>-2.54</v>
+        <v>-34.5</v>
       </c>
       <c r="AG2">
-        <v>1414.99</v>
+        <v>1422.03</v>
       </c>
       <c r="AH2">
-        <v>1285.81</v>
+        <v>1285.62</v>
       </c>
       <c r="AI2">
         <v>1319.72</v>
@@ -1014,7 +985,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>44.31</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +996,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1592</v>
+        <v>1580</v>
       </c>
       <c r="D3">
-        <v>-2.51</v>
+        <v>-0.75</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1037,46 +1008,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-21.78</v>
+        <v>-22.37</v>
       </c>
       <c r="H3">
-        <v>11.51</v>
+        <v>10.67</v>
       </c>
       <c r="I3">
-        <v>-5.88</v>
+        <v>-5.96</v>
       </c>
       <c r="J3">
-        <v>7.57</v>
+        <v>5.29</v>
       </c>
       <c r="K3">
-        <v>-1.67</v>
+        <v>-4.92</v>
       </c>
       <c r="L3">
-        <v>-19.88</v>
+        <v>-20.88</v>
       </c>
       <c r="M3">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P3">
-        <v>1639.02</v>
+        <v>1619</v>
       </c>
       <c r="Q3">
-        <v>1620.33</v>
+        <v>1620.48</v>
       </c>
       <c r="R3">
-        <v>1575.43</v>
+        <v>1574.33</v>
       </c>
       <c r="S3">
-        <v>1742.6</v>
+        <v>1740.63</v>
       </c>
       <c r="T3">
-        <v>-8.640000000000001</v>
+        <v>-9.23</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1091,43 +1062,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>47.19</v>
+        <v>45.47</v>
       </c>
       <c r="Z3">
-        <v>24.45</v>
+        <v>18.22</v>
       </c>
       <c r="AA3">
-        <v>28.3</v>
+        <v>26.29</v>
       </c>
       <c r="AB3">
-        <v>-3.86</v>
+        <v>-8.06</v>
       </c>
       <c r="AC3">
-        <v>3.9</v>
+        <v>0.57</v>
       </c>
       <c r="AD3">
-        <v>21.66</v>
+        <v>7.84</v>
       </c>
       <c r="AE3">
-        <v>48.4</v>
+        <v>47.36</v>
       </c>
       <c r="AF3">
-        <v>-75.17</v>
+        <v>-41.1</v>
       </c>
       <c r="AG3">
-        <v>1734.79</v>
+        <v>1734.71</v>
       </c>
       <c r="AH3">
-        <v>1505.87</v>
+        <v>1506.25</v>
       </c>
       <c r="AI3">
-        <v>1583.65</v>
+        <v>1728.97</v>
       </c>
       <c r="AJ3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AK3">
-        <v>42.53</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,7 +1109,7 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>431</v>
+        <v>422.2</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1147,49 +1118,49 @@
         <v>686.0700000000001</v>
       </c>
       <c r="F4">
-        <v>431</v>
+        <v>422.2</v>
       </c>
       <c r="G4">
-        <v>-37.18</v>
+        <v>-38.46</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-4.01</v>
+        <v>-5.12</v>
       </c>
       <c r="J4">
-        <v>-11.44</v>
+        <v>-12.86</v>
       </c>
       <c r="K4">
-        <v>-14.06</v>
+        <v>-15.65</v>
       </c>
       <c r="L4">
-        <v>-27.4</v>
+        <v>-29.01</v>
       </c>
       <c r="M4">
-        <v>-6.91</v>
+        <v>-7.33</v>
       </c>
       <c r="N4">
         <v>33</v>
       </c>
       <c r="O4">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>435.3</v>
+        <v>428.98</v>
       </c>
       <c r="Q4">
-        <v>449.65</v>
+        <v>447.09</v>
       </c>
       <c r="R4">
-        <v>476.25</v>
+        <v>474.39</v>
       </c>
       <c r="S4">
-        <v>537.21</v>
+        <v>535.87</v>
       </c>
       <c r="T4">
-        <v>-19.77</v>
+        <v>-21.21</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,43 +1175,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.24</v>
+        <v>27.83</v>
       </c>
       <c r="Z4">
-        <v>-11.84</v>
+        <v>-13.2</v>
       </c>
       <c r="AA4">
-        <v>-10.54</v>
+        <v>-11.19</v>
       </c>
       <c r="AB4">
-        <v>-1.29</v>
+        <v>-2.01</v>
       </c>
       <c r="AC4">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>9.66</v>
+        <v>2.52</v>
       </c>
       <c r="AE4">
-        <v>12.55</v>
+        <v>13.42</v>
       </c>
       <c r="AF4">
-        <v>-30.16</v>
+        <v>-13.64</v>
       </c>
       <c r="AG4">
-        <v>471.67</v>
+        <v>472.68</v>
       </c>
       <c r="AH4">
-        <v>427.63</v>
+        <v>421.5</v>
       </c>
       <c r="AI4">
-        <v>465.16</v>
+        <v>461.46</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>45.33</v>
+        <v>49.87</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1401,47 +1372,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1449,377 +1385,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>3.98</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>4.08</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.1</v>
+      <c r="D7" s="5">
+        <v>4.7</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.62</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>7.57</v>
       </c>
-      <c r="E8" s="8">
-        <v>-0.64</v>
+      <c r="D8" s="5">
+        <v>5.29</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.28</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-12.58</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-11.44</v>
       </c>
+      <c r="D9" s="5">
+        <v>-12.86</v>
+      </c>
       <c r="E9" s="7">
-        <v>1.14</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>4.47</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>0.35</v>
       </c>
-      <c r="E10" s="8">
-        <v>-4.12</v>
+      <c r="D10" s="5">
+        <v>0.43</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.08</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-4.67</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-5.88</v>
       </c>
-      <c r="E11" s="8">
-        <v>-1.21</v>
+      <c r="D11" s="5">
+        <v>-5.96</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-3.15</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-4.01</v>
       </c>
-      <c r="E12" s="8">
-        <v>-0.86</v>
+      <c r="D12" s="5">
+        <v>-5.12</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-1.33</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-2.95</v>
       </c>
-      <c r="E13" s="8">
-        <v>-1.62</v>
+      <c r="D13" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="E13" s="6">
+        <v>3.86</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-18.19</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-19.88</v>
       </c>
-      <c r="E14" s="8">
-        <v>-1.69</v>
+      <c r="D14" s="5">
+        <v>-20.88</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-26.32</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-27.4</v>
       </c>
-      <c r="E15" s="8">
-        <v>-1.08</v>
+      <c r="D15" s="5">
+        <v>-29.01</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>-2.93</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-2.82</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.11</v>
+      <c r="D16" s="5">
+        <v>-2.09</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.73</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>3.13</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-1.67</v>
       </c>
-      <c r="E17" s="8">
-        <v>-4.8</v>
+      <c r="D17" s="5">
+        <v>-4.92</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-13.71</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-14.06</v>
       </c>
-      <c r="E18" s="8">
-        <v>-0.35</v>
+      <c r="D18" s="5">
+        <v>-15.65</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-4.42</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-4.71</v>
       </c>
-      <c r="E19" s="8">
-        <v>-0.29</v>
+      <c r="D19" s="5">
+        <v>-4.11</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-19.76</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-21.78</v>
       </c>
-      <c r="E20" s="8">
-        <v>-2.02</v>
+      <c r="D20" s="5">
+        <v>-22.37</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-37.18</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-38.46</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="6">
-        <v>1398.5</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C22" s="5">
         <v>1394.2</v>
       </c>
-      <c r="E21" s="8">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="D22" s="5">
+        <v>1403</v>
+      </c>
+      <c r="E22" s="6">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>1633</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C23" s="5">
         <v>1592</v>
       </c>
-      <c r="E22" s="8">
-        <v>-41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="D23" s="5">
+        <v>1580</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>431</v>
+      </c>
+      <c r="D24" s="5">
+        <v>422.2</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-8.800000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="6">
-        <v>58.67</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C25" s="5">
         <v>57.37</v>
       </c>
-      <c r="E23" s="8">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="D25" s="5">
+        <v>59.36</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="6">
-        <v>53.64</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C26" s="5">
         <v>47.19</v>
       </c>
-      <c r="E24" s="8">
-        <v>-6.45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="D26" s="5">
+        <v>45.47</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>31.24</v>
+      </c>
+      <c r="D27" s="5">
+        <v>27.83</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="6">
-        <v>41.34</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C28" s="5">
         <v>-2.54</v>
       </c>
-      <c r="E25" s="8">
-        <v>-43.88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="D28" s="5">
+        <v>-34.5</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-31.96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="6">
-        <v>-73.44</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C29" s="5">
         <v>-75.17</v>
       </c>
-      <c r="E26" s="8">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="D29" s="5">
+        <v>-41.1</v>
+      </c>
+      <c r="E29" s="6">
+        <v>34.07</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="6">
-        <v>-29.67</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C30" s="5">
         <v>-30.16</v>
       </c>
-      <c r="E27" s="8">
-        <v>-0.49</v>
+      <c r="D30" s="5">
+        <v>-13.64</v>
+      </c>
+      <c r="E30" s="6">
+        <v>16.52</v>
       </c>
     </row>
   </sheetData>
@@ -1845,60 +1832,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="10">
+        <v>49.72</v>
+      </c>
+      <c r="C2" s="11">
+        <v>3</v>
+      </c>
+      <c r="D2" s="10">
+        <v>44.2</v>
+      </c>
+      <c r="E2" s="10">
+        <v>33.3</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.6</v>
+      </c>
+      <c r="H2" s="10">
         <v>66</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="11">
-        <v>49.72</v>
-      </c>
-      <c r="C2" s="12">
-        <v>3</v>
-      </c>
-      <c r="D2" s="11">
-        <v>45.3</v>
-      </c>
-      <c r="E2" s="11">
-        <v>33.3</v>
-      </c>
-      <c r="F2" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-6.2</v>
-      </c>
-      <c r="H2" s="11">
-        <v>66</v>
-      </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2000,25 +1987,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1131</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0198</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.06909999999999999</v>
+      <c r="A2" s="13">
+        <v>0.1177</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.017</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0733</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -750,7 +750,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -883,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1403</v>
+        <v>1386.9</v>
       </c>
       <c r="D2">
-        <v>0.63</v>
+        <v>-1.15</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -895,46 +896,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-4.11</v>
+        <v>-5.21</v>
       </c>
       <c r="H2">
-        <v>16.34</v>
+        <v>15.01</v>
       </c>
       <c r="I2">
         <v>0.43</v>
       </c>
       <c r="J2">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="K2">
-        <v>-2.09</v>
+        <v>-4.07</v>
       </c>
       <c r="L2">
-        <v>0.91</v>
+        <v>0.35</v>
       </c>
       <c r="M2">
-        <v>11.77</v>
+        <v>11.36</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P2">
-        <v>1392.34</v>
+        <v>1393.52</v>
       </c>
       <c r="Q2">
-        <v>1353.82</v>
+        <v>1356.83</v>
       </c>
       <c r="R2">
-        <v>1380.03</v>
+        <v>1379.63</v>
       </c>
       <c r="S2">
-        <v>1354.01</v>
+        <v>1353.89</v>
       </c>
       <c r="T2">
-        <v>3.62</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,34 +950,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>59.36</v>
+        <v>54.36</v>
       </c>
       <c r="Z2">
-        <v>8.02</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AA2">
-        <v>-0.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB2">
-        <v>8.42</v>
+        <v>6.81</v>
       </c>
       <c r="AC2">
-        <v>95.66</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="AD2">
-        <v>92.47</v>
+        <v>90.5</v>
       </c>
       <c r="AE2">
-        <v>25.55</v>
+        <v>25.54</v>
       </c>
       <c r="AF2">
-        <v>-34.5</v>
+        <v>29.43</v>
       </c>
       <c r="AG2">
-        <v>1422.03</v>
+        <v>1425.32</v>
       </c>
       <c r="AH2">
-        <v>1285.62</v>
+        <v>1288.34</v>
       </c>
       <c r="AI2">
         <v>1319.72</v>
@@ -985,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>44.97</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1580</v>
+        <v>1576.2</v>
       </c>
       <c r="D3">
-        <v>-0.75</v>
+        <v>-0.24</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1008,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-22.37</v>
+        <v>-22.55</v>
       </c>
       <c r="H3">
-        <v>10.67</v>
+        <v>10.4</v>
       </c>
       <c r="I3">
-        <v>-5.96</v>
+        <v>-4.47</v>
       </c>
       <c r="J3">
-        <v>5.29</v>
+        <v>-0.05</v>
       </c>
       <c r="K3">
-        <v>-4.92</v>
+        <v>-6.23</v>
       </c>
       <c r="L3">
-        <v>-20.88</v>
+        <v>-20.91</v>
       </c>
       <c r="M3">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="P3">
-        <v>1619</v>
+        <v>1604.24</v>
       </c>
       <c r="Q3">
-        <v>1620.48</v>
+        <v>1621.6</v>
       </c>
       <c r="R3">
-        <v>1574.33</v>
+        <v>1573.3</v>
       </c>
       <c r="S3">
-        <v>1740.63</v>
+        <v>1738.5</v>
       </c>
       <c r="T3">
-        <v>-9.23</v>
+        <v>-9.34</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1062,43 +1063,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>45.47</v>
+        <v>44.91</v>
       </c>
       <c r="Z3">
-        <v>18.22</v>
+        <v>12.84</v>
       </c>
       <c r="AA3">
-        <v>26.29</v>
+        <v>23.6</v>
       </c>
       <c r="AB3">
-        <v>-8.06</v>
+        <v>-10.76</v>
       </c>
       <c r="AC3">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>7.84</v>
+        <v>1.49</v>
       </c>
       <c r="AE3">
-        <v>47.36</v>
+        <v>45.96</v>
       </c>
       <c r="AF3">
-        <v>-41.1</v>
+        <v>-69.95999999999999</v>
       </c>
       <c r="AG3">
-        <v>1734.71</v>
+        <v>1733.48</v>
       </c>
       <c r="AH3">
-        <v>1506.25</v>
+        <v>1509.73</v>
       </c>
       <c r="AI3">
-        <v>1728.97</v>
+        <v>1707.88</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>38.1</v>
+        <v>35.36</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,7 +1110,7 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>422.2</v>
+        <v>413.35</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1118,49 +1119,49 @@
         <v>686.0700000000001</v>
       </c>
       <c r="F4">
-        <v>422.2</v>
+        <v>413.35</v>
       </c>
       <c r="G4">
-        <v>-38.46</v>
+        <v>-39.75</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-5.12</v>
+        <v>-5.63</v>
       </c>
       <c r="J4">
-        <v>-12.86</v>
+        <v>-11.01</v>
       </c>
       <c r="K4">
-        <v>-15.65</v>
+        <v>-18.92</v>
       </c>
       <c r="L4">
-        <v>-29.01</v>
+        <v>-30.32</v>
       </c>
       <c r="M4">
-        <v>-7.33</v>
+        <v>-8</v>
       </c>
       <c r="N4">
         <v>33</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="P4">
-        <v>428.98</v>
+        <v>422.28</v>
       </c>
       <c r="Q4">
-        <v>447.09</v>
+        <v>444.17</v>
       </c>
       <c r="R4">
-        <v>474.39</v>
+        <v>472.34</v>
       </c>
       <c r="S4">
-        <v>535.87</v>
+        <v>534.46</v>
       </c>
       <c r="T4">
-        <v>-21.21</v>
+        <v>-22.66</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1175,43 +1176,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>27.83</v>
+        <v>24.88</v>
       </c>
       <c r="Z4">
-        <v>-13.2</v>
+        <v>-14.81</v>
       </c>
       <c r="AA4">
-        <v>-11.19</v>
+        <v>-12.02</v>
       </c>
       <c r="AB4">
-        <v>-2.01</v>
+        <v>-2.79</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>2.52</v>
+        <v>0.14</v>
       </c>
       <c r="AE4">
-        <v>13.42</v>
+        <v>12.61</v>
       </c>
       <c r="AF4">
-        <v>-13.64</v>
+        <v>-41.3</v>
       </c>
       <c r="AG4">
-        <v>472.68</v>
+        <v>474.41</v>
       </c>
       <c r="AH4">
-        <v>421.5</v>
+        <v>413.93</v>
       </c>
       <c r="AI4">
-        <v>461.46</v>
+        <v>455.97</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>49.87</v>
+        <v>52.94</v>
       </c>
     </row>
   </sheetData>
@@ -1352,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1409,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>4.08</v>
+        <v>4.7</v>
       </c>
       <c r="D7" s="5">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="E7" s="6">
-        <v>0.62</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>7.57</v>
+        <v>5.29</v>
       </c>
       <c r="D8" s="5">
-        <v>5.29</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.28</v>
+        <v>-0.05</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-5.34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,370 +1444,353 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-11.44</v>
+        <v>-12.86</v>
       </c>
       <c r="D9" s="5">
-        <v>-12.86</v>
+        <v>-11.01</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.42</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>0.35</v>
+        <v>-5.96</v>
       </c>
       <c r="D10" s="5">
-        <v>0.43</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.08</v>
+        <v>-4.47</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.49</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-5.88</v>
+        <v>-5.12</v>
       </c>
       <c r="D11" s="5">
-        <v>-5.96</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.08</v>
+        <v>-5.63</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.01</v>
+        <v>0.91</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.12</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.11</v>
+        <v>0.35</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-2.95</v>
+        <v>-20.88</v>
       </c>
       <c r="D13" s="5">
-        <v>0.91</v>
+        <v>-20.91</v>
       </c>
       <c r="E13" s="6">
-        <v>3.86</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-19.88</v>
+        <v>-29.01</v>
       </c>
       <c r="D14" s="5">
-        <v>-20.88</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1</v>
+        <v>-30.32</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="5">
-        <v>-27.4</v>
+        <v>-2.09</v>
       </c>
       <c r="D15" s="5">
-        <v>-29.01</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.61</v>
+        <v>-4.07</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-2.82</v>
+        <v>-4.92</v>
       </c>
       <c r="D16" s="5">
-        <v>-2.09</v>
+        <v>-6.23</v>
       </c>
       <c r="E16" s="6">
-        <v>0.73</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-1.67</v>
+        <v>-15.65</v>
       </c>
       <c r="D17" s="5">
-        <v>-4.92</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.25</v>
+        <v>-18.92</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C18" s="5">
-        <v>-14.06</v>
+        <v>-4.11</v>
       </c>
       <c r="D18" s="5">
-        <v>-15.65</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.59</v>
+        <v>-5.21</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-4.71</v>
+        <v>-22.37</v>
       </c>
       <c r="D19" s="5">
-        <v>-4.11</v>
+        <v>-22.55</v>
       </c>
       <c r="E19" s="6">
-        <v>0.6</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-21.78</v>
+        <v>-38.46</v>
       </c>
       <c r="D20" s="5">
-        <v>-22.37</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.59</v>
+        <v>-39.75</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C21" s="5">
-        <v>-37.18</v>
+        <v>1403</v>
       </c>
       <c r="D21" s="5">
-        <v>-38.46</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.28</v>
+        <v>1386.9</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-16.1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1394.2</v>
+        <v>1580</v>
       </c>
       <c r="D22" s="5">
-        <v>1403</v>
+        <v>1576.2</v>
       </c>
       <c r="E22" s="6">
-        <v>8.800000000000001</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1592</v>
+        <v>422.2</v>
       </c>
       <c r="D23" s="5">
-        <v>1580</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-12</v>
+        <v>413.35</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-8.85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C24" s="5">
-        <v>431</v>
+        <v>59.36</v>
       </c>
       <c r="D24" s="5">
-        <v>422.2</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-8.800000000000001</v>
+        <v>54.36</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>57.37</v>
+        <v>45.47</v>
       </c>
       <c r="D25" s="5">
-        <v>59.36</v>
+        <v>44.91</v>
       </c>
       <c r="E25" s="6">
-        <v>1.99</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>47.19</v>
+        <v>27.83</v>
       </c>
       <c r="D26" s="5">
-        <v>45.47</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.72</v>
+        <v>24.88</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-2.95</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C27" s="5">
-        <v>31.24</v>
+        <v>-34.5</v>
       </c>
       <c r="D27" s="5">
-        <v>27.83</v>
+        <v>29.43</v>
       </c>
       <c r="E27" s="7">
-        <v>-3.41</v>
+        <v>63.93</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-2.54</v>
+        <v>-41.1</v>
       </c>
       <c r="D28" s="5">
-        <v>-34.5</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-31.96</v>
+        <v>-69.95999999999999</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-28.86</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-75.17</v>
+        <v>-13.64</v>
       </c>
       <c r="D29" s="5">
-        <v>-41.1</v>
+        <v>-41.3</v>
       </c>
       <c r="E29" s="6">
-        <v>34.07</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-30.16</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-13.64</v>
-      </c>
-      <c r="E30" s="6">
-        <v>16.52</v>
+        <v>-27.66</v>
       </c>
     </row>
   </sheetData>
@@ -1871,16 +1855,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>44.2</v>
+        <v>41.4</v>
       </c>
       <c r="E2" s="10">
         <v>33.3</v>
       </c>
       <c r="F2" s="10">
-        <v>-1</v>
+        <v>-2.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.6</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="H2" s="10">
         <v>66</v>
@@ -1999,13 +1983,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1177</v>
+        <v>0.1136</v>
       </c>
       <c r="B2" s="13">
-        <v>0.017</v>
+        <v>0.0173</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0733</v>
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1386.9</v>
+        <v>1377.6</v>
       </c>
       <c r="D2">
-        <v>-1.15</v>
+        <v>-0.67</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,25 +896,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-5.21</v>
+        <v>-5.84</v>
       </c>
       <c r="H2">
-        <v>15.01</v>
+        <v>14.24</v>
       </c>
       <c r="I2">
-        <v>0.43</v>
+        <v>-0.53</v>
       </c>
       <c r="J2">
-        <v>3.93</v>
+        <v>3.83</v>
       </c>
       <c r="K2">
-        <v>-4.07</v>
+        <v>-3.72</v>
       </c>
       <c r="L2">
-        <v>0.35</v>
+        <v>1.02</v>
       </c>
       <c r="M2">
-        <v>11.36</v>
+        <v>12.2</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -923,19 +923,19 @@
         <v>71</v>
       </c>
       <c r="P2">
-        <v>1393.52</v>
+        <v>1392.04</v>
       </c>
       <c r="Q2">
-        <v>1356.83</v>
+        <v>1360.61</v>
       </c>
       <c r="R2">
-        <v>1379.63</v>
+        <v>1378.84</v>
       </c>
       <c r="S2">
-        <v>1353.89</v>
+        <v>1353.64</v>
       </c>
       <c r="T2">
-        <v>2.44</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +950,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>54.36</v>
+        <v>51.65</v>
       </c>
       <c r="Z2">
-        <v>8.119999999999999</v>
+        <v>7.36</v>
       </c>
       <c r="AA2">
-        <v>1.31</v>
+        <v>2.52</v>
       </c>
       <c r="AB2">
-        <v>6.81</v>
+        <v>4.84</v>
       </c>
       <c r="AC2">
-        <v>84.76000000000001</v>
+        <v>70.39</v>
       </c>
       <c r="AD2">
-        <v>90.5</v>
+        <v>83.61</v>
       </c>
       <c r="AE2">
-        <v>25.54</v>
+        <v>25.53</v>
       </c>
       <c r="AF2">
-        <v>29.43</v>
+        <v>-24.51</v>
       </c>
       <c r="AG2">
-        <v>1425.32</v>
+        <v>1424.55</v>
       </c>
       <c r="AH2">
-        <v>1288.34</v>
+        <v>1296.67</v>
       </c>
       <c r="AI2">
         <v>1319.72</v>
@@ -986,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>45.07</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1576.2</v>
+        <v>1583.8</v>
       </c>
       <c r="D3">
-        <v>-0.24</v>
+        <v>0.48</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-22.55</v>
+        <v>-22.18</v>
       </c>
       <c r="H3">
-        <v>10.4</v>
+        <v>10.93</v>
       </c>
       <c r="I3">
-        <v>-4.47</v>
+        <v>-3.43</v>
       </c>
       <c r="J3">
-        <v>-0.05</v>
+        <v>1.94</v>
       </c>
       <c r="K3">
-        <v>-6.23</v>
+        <v>-5.94</v>
       </c>
       <c r="L3">
-        <v>-20.91</v>
+        <v>-19.67</v>
       </c>
       <c r="M3">
-        <v>1.73</v>
+        <v>2.22</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P3">
-        <v>1604.24</v>
+        <v>1593</v>
       </c>
       <c r="Q3">
-        <v>1621.6</v>
+        <v>1623.8</v>
       </c>
       <c r="R3">
-        <v>1573.3</v>
+        <v>1572.37</v>
       </c>
       <c r="S3">
-        <v>1738.5</v>
+        <v>1736.63</v>
       </c>
       <c r="T3">
-        <v>-9.34</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1063,34 +1063,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>44.91</v>
+        <v>46.33</v>
       </c>
       <c r="Z3">
-        <v>12.84</v>
+        <v>9.08</v>
       </c>
       <c r="AA3">
-        <v>23.6</v>
+        <v>20.69</v>
       </c>
       <c r="AB3">
-        <v>-10.76</v>
+        <v>-11.61</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD3">
-        <v>1.49</v>
+        <v>0.88</v>
       </c>
       <c r="AE3">
-        <v>45.96</v>
+        <v>44.68</v>
       </c>
       <c r="AF3">
-        <v>-69.95999999999999</v>
+        <v>-62.81</v>
       </c>
       <c r="AG3">
-        <v>1733.48</v>
+        <v>1730.54</v>
       </c>
       <c r="AH3">
-        <v>1509.73</v>
+        <v>1517.05</v>
       </c>
       <c r="AI3">
         <v>1707.88</v>
@@ -1099,7 +1099,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>35.36</v>
+        <v>32.51</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,7 +1110,7 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>413.35</v>
+        <v>409.55</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1119,49 +1119,49 @@
         <v>686.0700000000001</v>
       </c>
       <c r="F4">
-        <v>413.35</v>
+        <v>409.55</v>
       </c>
       <c r="G4">
-        <v>-39.75</v>
+        <v>-40.3</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-5.63</v>
+        <v>-5.09</v>
       </c>
       <c r="J4">
-        <v>-11.01</v>
+        <v>-11.54</v>
       </c>
       <c r="K4">
-        <v>-18.92</v>
+        <v>-19.71</v>
       </c>
       <c r="L4">
-        <v>-30.32</v>
+        <v>-32.31</v>
       </c>
       <c r="M4">
-        <v>-8</v>
+        <v>-7.74</v>
       </c>
       <c r="N4">
         <v>33</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>422.28</v>
+        <v>417.13</v>
       </c>
       <c r="Q4">
-        <v>444.17</v>
+        <v>441.52</v>
       </c>
       <c r="R4">
-        <v>472.34</v>
+        <v>470.27</v>
       </c>
       <c r="S4">
-        <v>534.46</v>
+        <v>533.08</v>
       </c>
       <c r="T4">
-        <v>-22.66</v>
+        <v>-23.17</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,43 +1176,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>24.88</v>
+        <v>23.72</v>
       </c>
       <c r="Z4">
-        <v>-14.81</v>
+        <v>-15.89</v>
       </c>
       <c r="AA4">
-        <v>-12.02</v>
+        <v>-12.85</v>
       </c>
       <c r="AB4">
-        <v>-2.79</v>
+        <v>-3.05</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>12.61</v>
+        <v>13.08</v>
       </c>
       <c r="AF4">
-        <v>-41.3</v>
+        <v>63.99</v>
       </c>
       <c r="AG4">
-        <v>474.41</v>
+        <v>475.36</v>
       </c>
       <c r="AH4">
-        <v>413.93</v>
+        <v>407.68</v>
       </c>
       <c r="AI4">
-        <v>455.97</v>
+        <v>447.84</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>52.94</v>
+        <v>57.43</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>4.7</v>
+        <v>3.93</v>
       </c>
       <c r="D7" s="5">
-        <v>3.93</v>
+        <v>3.83</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.77</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>5.29</v>
+        <v>-0.05</v>
       </c>
       <c r="D8" s="5">
-        <v>-0.05</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-5.34</v>
+        <v>1.94</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,353 +1444,370 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-12.86</v>
+        <v>-11.01</v>
       </c>
       <c r="D9" s="5">
-        <v>-11.01</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.85</v>
+        <v>-11.54</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-5.96</v>
+        <v>0.43</v>
       </c>
       <c r="D10" s="5">
-        <v>-4.47</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.49</v>
+        <v>-0.53</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-5.12</v>
+        <v>-4.47</v>
       </c>
       <c r="D11" s="5">
-        <v>-5.63</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.51</v>
+        <v>-3.43</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.04</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>0.91</v>
+        <v>-5.63</v>
       </c>
       <c r="D12" s="5">
-        <v>0.35</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.5600000000000001</v>
+        <v>-5.09</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.54</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-20.88</v>
+        <v>0.35</v>
       </c>
       <c r="D13" s="5">
-        <v>-20.91</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.03</v>
+        <v>1.02</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.67</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-29.01</v>
+        <v>-20.91</v>
       </c>
       <c r="D14" s="5">
-        <v>-30.32</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-1.31</v>
+        <v>-19.67</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.24</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-2.09</v>
+        <v>-30.32</v>
       </c>
       <c r="D15" s="5">
-        <v>-4.07</v>
+        <v>-32.31</v>
       </c>
       <c r="E15" s="6">
-        <v>-1.98</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-4.92</v>
+        <v>-4.07</v>
       </c>
       <c r="D16" s="5">
-        <v>-6.23</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-1.31</v>
+        <v>-3.72</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.35</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-15.65</v>
+        <v>-6.23</v>
       </c>
       <c r="D17" s="5">
-        <v>-18.92</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-3.27</v>
+        <v>-5.94</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-4.11</v>
+        <v>-18.92</v>
       </c>
       <c r="D18" s="5">
-        <v>-5.21</v>
+        <v>-19.71</v>
       </c>
       <c r="E18" s="6">
-        <v>-1.1</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-22.37</v>
+        <v>-5.21</v>
       </c>
       <c r="D19" s="5">
-        <v>-22.55</v>
+        <v>-5.84</v>
       </c>
       <c r="E19" s="6">
-        <v>-0.18</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-38.46</v>
+        <v>-22.55</v>
       </c>
       <c r="D20" s="5">
-        <v>-39.75</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.29</v>
+        <v>-22.18</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.37</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>1403</v>
+        <v>-39.75</v>
       </c>
       <c r="D21" s="5">
-        <v>1386.9</v>
+        <v>-40.3</v>
       </c>
       <c r="E21" s="6">
-        <v>-16.1</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1580</v>
+        <v>1386.9</v>
       </c>
       <c r="D22" s="5">
-        <v>1576.2</v>
+        <v>1377.6</v>
       </c>
       <c r="E22" s="6">
-        <v>-3.8</v>
+        <v>-9.300000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>422.2</v>
+        <v>1576.2</v>
       </c>
       <c r="D23" s="5">
-        <v>413.35</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-8.85</v>
+        <v>1583.8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>7.6</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>59.36</v>
+        <v>413.35</v>
       </c>
       <c r="D24" s="5">
-        <v>54.36</v>
+        <v>409.55</v>
       </c>
       <c r="E24" s="6">
-        <v>-5</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>45.47</v>
+        <v>54.36</v>
       </c>
       <c r="D25" s="5">
-        <v>44.91</v>
+        <v>51.65</v>
       </c>
       <c r="E25" s="6">
-        <v>-0.5600000000000001</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>27.83</v>
+        <v>44.91</v>
       </c>
       <c r="D26" s="5">
-        <v>24.88</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-2.95</v>
+        <v>46.33</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.42</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>-34.5</v>
+        <v>24.88</v>
       </c>
       <c r="D27" s="5">
-        <v>29.43</v>
-      </c>
-      <c r="E27" s="7">
-        <v>63.93</v>
+        <v>23.72</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-41.1</v>
+        <v>29.43</v>
       </c>
       <c r="D28" s="5">
-        <v>-69.95999999999999</v>
+        <v>-24.51</v>
       </c>
       <c r="E28" s="6">
-        <v>-28.86</v>
+        <v>-53.94</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-13.64</v>
+        <v>-69.95999999999999</v>
       </c>
       <c r="D29" s="5">
+        <v>-62.81</v>
+      </c>
+      <c r="E29" s="7">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="5">
         <v>-41.3</v>
       </c>
-      <c r="E29" s="6">
-        <v>-27.66</v>
+      <c r="D30" s="5">
+        <v>63.99</v>
+      </c>
+      <c r="E30" s="7">
+        <v>105.29</v>
       </c>
     </row>
   </sheetData>
@@ -1855,16 +1872,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>41.4</v>
+        <v>40.6</v>
       </c>
       <c r="E2" s="10">
         <v>33.3</v>
       </c>
       <c r="F2" s="10">
-        <v>-2.4</v>
+        <v>-1.9</v>
       </c>
       <c r="G2" s="10">
-        <v>-9.699999999999999</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="H2" s="10">
         <v>66</v>
@@ -1983,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1136</v>
+        <v>0.122</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0173</v>
+        <v>0.0222</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.08</v>
+        <v>-0.0774</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1377.6</v>
+        <v>1386.6</v>
       </c>
       <c r="D2">
-        <v>-0.67</v>
+        <v>0.65</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,25 +896,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-5.84</v>
+        <v>-5.23</v>
       </c>
       <c r="H2">
-        <v>14.24</v>
+        <v>14.98</v>
       </c>
       <c r="I2">
-        <v>-0.53</v>
+        <v>-0.85</v>
       </c>
       <c r="J2">
-        <v>3.83</v>
+        <v>6.5</v>
       </c>
       <c r="K2">
-        <v>-3.72</v>
+        <v>-3.57</v>
       </c>
       <c r="L2">
-        <v>1.02</v>
+        <v>0.65</v>
       </c>
       <c r="M2">
-        <v>12.2</v>
+        <v>12.25</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -923,19 +923,19 @@
         <v>71</v>
       </c>
       <c r="P2">
-        <v>1392.04</v>
+        <v>1389.66</v>
       </c>
       <c r="Q2">
-        <v>1360.61</v>
+        <v>1365.33</v>
       </c>
       <c r="R2">
-        <v>1378.84</v>
+        <v>1378.27</v>
       </c>
       <c r="S2">
-        <v>1353.64</v>
+        <v>1353.39</v>
       </c>
       <c r="T2">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +950,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>51.65</v>
+        <v>54.03</v>
       </c>
       <c r="Z2">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="AA2">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="AB2">
-        <v>4.84</v>
+        <v>3.91</v>
       </c>
       <c r="AC2">
-        <v>70.39</v>
+        <v>57.99</v>
       </c>
       <c r="AD2">
-        <v>83.61</v>
+        <v>71.05</v>
       </c>
       <c r="AE2">
-        <v>25.53</v>
+        <v>25.25</v>
       </c>
       <c r="AF2">
-        <v>-24.51</v>
+        <v>-7.95</v>
       </c>
       <c r="AG2">
-        <v>1424.55</v>
+        <v>1421.47</v>
       </c>
       <c r="AH2">
-        <v>1296.67</v>
+        <v>1309.19</v>
       </c>
       <c r="AI2">
         <v>1319.72</v>
@@ -986,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>39.54</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1583.8</v>
+        <v>1572.9</v>
       </c>
       <c r="D3">
-        <v>0.48</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-22.18</v>
+        <v>-22.71</v>
       </c>
       <c r="H3">
-        <v>10.93</v>
+        <v>10.17</v>
       </c>
       <c r="I3">
-        <v>-3.43</v>
+        <v>-3.68</v>
       </c>
       <c r="J3">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="K3">
-        <v>-5.94</v>
+        <v>-4.6</v>
       </c>
       <c r="L3">
-        <v>-19.67</v>
+        <v>-20.81</v>
       </c>
       <c r="M3">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P3">
-        <v>1593</v>
+        <v>1580.98</v>
       </c>
       <c r="Q3">
-        <v>1623.8</v>
+        <v>1626.69</v>
       </c>
       <c r="R3">
-        <v>1572.37</v>
+        <v>1571.31</v>
       </c>
       <c r="S3">
-        <v>1736.63</v>
+        <v>1734.99</v>
       </c>
       <c r="T3">
-        <v>-8.800000000000001</v>
+        <v>-9.34</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1063,43 +1063,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>46.33</v>
+        <v>44.56</v>
       </c>
       <c r="Z3">
-        <v>9.08</v>
+        <v>5.16</v>
       </c>
       <c r="AA3">
-        <v>20.69</v>
+        <v>17.59</v>
       </c>
       <c r="AB3">
-        <v>-11.61</v>
+        <v>-12.43</v>
       </c>
       <c r="AC3">
         <v>2.07</v>
       </c>
       <c r="AD3">
-        <v>0.88</v>
+        <v>1.38</v>
       </c>
       <c r="AE3">
-        <v>44.68</v>
+        <v>43.3</v>
       </c>
       <c r="AF3">
-        <v>-62.81</v>
+        <v>-57.08</v>
       </c>
       <c r="AG3">
-        <v>1730.54</v>
+        <v>1723.71</v>
       </c>
       <c r="AH3">
-        <v>1517.05</v>
+        <v>1529.67</v>
       </c>
       <c r="AI3">
-        <v>1707.88</v>
+        <v>1701.6</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>32.51</v>
+        <v>30.14</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,7 +1110,7 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>409.55</v>
+        <v>412</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1122,46 +1122,46 @@
         <v>409.55</v>
       </c>
       <c r="G4">
-        <v>-40.3</v>
+        <v>-39.95</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I4">
-        <v>-5.09</v>
+        <v>-4.41</v>
       </c>
       <c r="J4">
-        <v>-11.54</v>
+        <v>-10.18</v>
       </c>
       <c r="K4">
-        <v>-19.71</v>
+        <v>-19.48</v>
       </c>
       <c r="L4">
-        <v>-32.31</v>
+        <v>-31.32</v>
       </c>
       <c r="M4">
-        <v>-7.74</v>
+        <v>-7.66</v>
       </c>
       <c r="N4">
         <v>33</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>417.13</v>
+        <v>413.82</v>
       </c>
       <c r="Q4">
-        <v>441.52</v>
+        <v>440.01</v>
       </c>
       <c r="R4">
-        <v>470.27</v>
+        <v>468.38</v>
       </c>
       <c r="S4">
-        <v>533.08</v>
+        <v>531.75</v>
       </c>
       <c r="T4">
-        <v>-23.17</v>
+        <v>-22.52</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,43 +1176,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>23.72</v>
+        <v>26.12</v>
       </c>
       <c r="Z4">
-        <v>-15.89</v>
+        <v>-15.98</v>
       </c>
       <c r="AA4">
-        <v>-12.85</v>
+        <v>-13.44</v>
       </c>
       <c r="AB4">
-        <v>-3.05</v>
+        <v>-2.54</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>7.36</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AE4">
-        <v>13.08</v>
+        <v>12.54</v>
       </c>
       <c r="AF4">
-        <v>63.99</v>
+        <v>-54.23</v>
       </c>
       <c r="AG4">
-        <v>475.36</v>
+        <v>475.87</v>
       </c>
       <c r="AH4">
-        <v>407.68</v>
+        <v>404.16</v>
       </c>
       <c r="AI4">
-        <v>447.84</v>
+        <v>445.71</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>57.43</v>
+        <v>60.47</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>3.93</v>
+        <v>3.83</v>
       </c>
       <c r="D7" s="5">
-        <v>3.83</v>
+        <v>6.5</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.1</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-0.05</v>
+        <v>1.94</v>
       </c>
       <c r="D8" s="5">
-        <v>1.94</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.99</v>
+        <v>2.14</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-11.01</v>
+        <v>-11.54</v>
       </c>
       <c r="D9" s="5">
-        <v>-11.54</v>
+        <v>-10.18</v>
       </c>
       <c r="E9" s="6">
-        <v>-0.53</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>0.43</v>
+        <v>-0.53</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.53</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.96</v>
+        <v>-0.85</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-4.47</v>
+        <v>-3.43</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.43</v>
+        <v>-3.68</v>
       </c>
       <c r="E11" s="7">
-        <v>1.04</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.63</v>
+        <v>-5.09</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.09</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.54</v>
+        <v>-4.41</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.68</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>0.35</v>
+        <v>1.02</v>
       </c>
       <c r="D13" s="5">
-        <v>1.02</v>
+        <v>0.65</v>
       </c>
       <c r="E13" s="7">
-        <v>0.67</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-20.91</v>
+        <v>-19.67</v>
       </c>
       <c r="D14" s="5">
-        <v>-19.67</v>
+        <v>-20.81</v>
       </c>
       <c r="E14" s="7">
-        <v>1.24</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-30.32</v>
+        <v>-32.31</v>
       </c>
       <c r="D15" s="5">
-        <v>-32.31</v>
+        <v>-31.32</v>
       </c>
       <c r="E15" s="6">
-        <v>-1.99</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-4.07</v>
+        <v>-3.72</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.72</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.35</v>
+        <v>-3.57</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.15</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-6.23</v>
+        <v>-5.94</v>
       </c>
       <c r="D17" s="5">
-        <v>-5.94</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.29</v>
+        <v>-4.6</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.34</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-18.92</v>
+        <v>-19.71</v>
       </c>
       <c r="D18" s="5">
-        <v>-19.71</v>
+        <v>-19.48</v>
       </c>
       <c r="E18" s="6">
-        <v>-0.79</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-5.21</v>
+        <v>-5.84</v>
       </c>
       <c r="D19" s="5">
-        <v>-5.84</v>
+        <v>-5.23</v>
       </c>
       <c r="E19" s="6">
-        <v>-0.63</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-22.55</v>
+        <v>-22.18</v>
       </c>
       <c r="D20" s="5">
-        <v>-22.18</v>
+        <v>-22.71</v>
       </c>
       <c r="E20" s="7">
-        <v>0.37</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-39.75</v>
+        <v>-40.3</v>
       </c>
       <c r="D21" s="5">
-        <v>-40.3</v>
+        <v>-39.95</v>
       </c>
       <c r="E21" s="6">
-        <v>-0.55</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1386.9</v>
+        <v>1377.6</v>
       </c>
       <c r="D22" s="5">
-        <v>1377.6</v>
+        <v>1386.6</v>
       </c>
       <c r="E22" s="6">
-        <v>-9.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1576.2</v>
+        <v>1583.8</v>
       </c>
       <c r="D23" s="5">
-        <v>1583.8</v>
+        <v>1572.9</v>
       </c>
       <c r="E23" s="7">
-        <v>7.6</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>413.35</v>
+        <v>409.55</v>
       </c>
       <c r="D24" s="5">
-        <v>409.55</v>
+        <v>412</v>
       </c>
       <c r="E24" s="6">
-        <v>-3.8</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1716,13 +1716,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>54.36</v>
+        <v>51.65</v>
       </c>
       <c r="D25" s="5">
-        <v>51.65</v>
+        <v>54.03</v>
       </c>
       <c r="E25" s="6">
-        <v>-2.71</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1733,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>44.91</v>
+        <v>46.33</v>
       </c>
       <c r="D26" s="5">
-        <v>46.33</v>
+        <v>44.56</v>
       </c>
       <c r="E26" s="7">
-        <v>1.42</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1750,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>24.88</v>
+        <v>23.72</v>
       </c>
       <c r="D27" s="5">
-        <v>23.72</v>
+        <v>26.12</v>
       </c>
       <c r="E27" s="6">
-        <v>-1.16</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1767,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>29.43</v>
+        <v>-24.51</v>
       </c>
       <c r="D28" s="5">
-        <v>-24.51</v>
+        <v>-7.95</v>
       </c>
       <c r="E28" s="6">
-        <v>-53.94</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1784,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-69.95999999999999</v>
+        <v>-62.81</v>
       </c>
       <c r="D29" s="5">
-        <v>-62.81</v>
-      </c>
-      <c r="E29" s="7">
-        <v>7.15</v>
+        <v>-57.08</v>
+      </c>
+      <c r="E29" s="6">
+        <v>5.73</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1801,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-41.3</v>
+        <v>63.99</v>
       </c>
       <c r="D30" s="5">
-        <v>63.99</v>
+        <v>-54.23</v>
       </c>
       <c r="E30" s="7">
-        <v>105.29</v>
+        <v>-118.22</v>
       </c>
     </row>
   </sheetData>
@@ -1872,16 +1872,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>40.6</v>
+        <v>41.6</v>
       </c>
       <c r="E2" s="10">
         <v>33.3</v>
       </c>
       <c r="F2" s="10">
-        <v>-1.9</v>
+        <v>-0.5</v>
       </c>
       <c r="G2" s="10">
-        <v>-9.800000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H2" s="10">
         <v>66</v>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.122</v>
+        <v>0.1225</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0222</v>
+        <v>0.0189</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0774</v>
+        <v>-0.0766</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1386.6</v>
+        <v>1398</v>
       </c>
       <c r="D2">
-        <v>0.65</v>
+        <v>0.82</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,46 +896,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-5.23</v>
+        <v>-4.45</v>
       </c>
       <c r="H2">
-        <v>14.98</v>
+        <v>15.93</v>
       </c>
       <c r="I2">
-        <v>-0.85</v>
+        <v>0.27</v>
       </c>
       <c r="J2">
-        <v>6.5</v>
+        <v>8.19</v>
       </c>
       <c r="K2">
-        <v>-3.57</v>
+        <v>-2.5</v>
       </c>
       <c r="L2">
-        <v>0.65</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
-        <v>12.25</v>
+        <v>12.4</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>1389.66</v>
+        <v>1390.42</v>
       </c>
       <c r="Q2">
-        <v>1365.33</v>
+        <v>1369.14</v>
       </c>
       <c r="R2">
-        <v>1378.27</v>
+        <v>1377.99</v>
       </c>
       <c r="S2">
-        <v>1353.39</v>
+        <v>1353.36</v>
       </c>
       <c r="T2">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +950,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>54.03</v>
+        <v>56.94</v>
       </c>
       <c r="Z2">
-        <v>7.4</v>
+        <v>8.26</v>
       </c>
       <c r="AA2">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="AB2">
-        <v>3.91</v>
+        <v>3.81</v>
       </c>
       <c r="AC2">
-        <v>57.99</v>
+        <v>64</v>
       </c>
       <c r="AD2">
-        <v>71.05</v>
+        <v>64.13</v>
       </c>
       <c r="AE2">
-        <v>25.25</v>
+        <v>24.99</v>
       </c>
       <c r="AF2">
-        <v>-7.95</v>
+        <v>-17.77</v>
       </c>
       <c r="AG2">
-        <v>1421.47</v>
+        <v>1423.13</v>
       </c>
       <c r="AH2">
-        <v>1309.19</v>
+        <v>1315.16</v>
       </c>
       <c r="AI2">
         <v>1319.72</v>
@@ -986,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>36.39</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1572.9</v>
+        <v>1580.8</v>
       </c>
       <c r="D3">
-        <v>-0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1009,46 @@
         <v>1427.7</v>
       </c>
       <c r="G3">
-        <v>-22.71</v>
+        <v>-22.33</v>
       </c>
       <c r="H3">
-        <v>10.17</v>
+        <v>10.72</v>
       </c>
       <c r="I3">
-        <v>-3.68</v>
+        <v>-0.7</v>
       </c>
       <c r="J3">
-        <v>2.14</v>
+        <v>4.34</v>
       </c>
       <c r="K3">
-        <v>-4.6</v>
+        <v>-3.49</v>
       </c>
       <c r="L3">
-        <v>-20.81</v>
+        <v>-20.12</v>
       </c>
       <c r="M3">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="P3">
-        <v>1580.98</v>
+        <v>1578.74</v>
       </c>
       <c r="Q3">
-        <v>1626.69</v>
+        <v>1626.23</v>
       </c>
       <c r="R3">
-        <v>1571.31</v>
+        <v>1570.45</v>
       </c>
       <c r="S3">
-        <v>1734.99</v>
+        <v>1733.45</v>
       </c>
       <c r="T3">
-        <v>-9.34</v>
+        <v>-8.81</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1063,43 +1063,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>44.56</v>
+        <v>46.17</v>
       </c>
       <c r="Z3">
-        <v>5.16</v>
+        <v>2.66</v>
       </c>
       <c r="AA3">
-        <v>17.59</v>
+        <v>14.6</v>
       </c>
       <c r="AB3">
-        <v>-12.43</v>
+        <v>-11.94</v>
       </c>
       <c r="AC3">
-        <v>2.07</v>
+        <v>4.39</v>
       </c>
       <c r="AD3">
-        <v>1.38</v>
+        <v>2.84</v>
       </c>
       <c r="AE3">
-        <v>43.3</v>
+        <v>42.17</v>
       </c>
       <c r="AF3">
-        <v>-57.08</v>
+        <v>-69.63</v>
       </c>
       <c r="AG3">
-        <v>1723.71</v>
+        <v>1724.07</v>
       </c>
       <c r="AH3">
-        <v>1529.67</v>
+        <v>1528.39</v>
       </c>
       <c r="AI3">
-        <v>1701.6</v>
+        <v>1693.56</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>30.14</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,7 +1110,7 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>412</v>
+        <v>411.95</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1122,46 +1122,46 @@
         <v>409.55</v>
       </c>
       <c r="G4">
-        <v>-39.95</v>
+        <v>-39.96</v>
       </c>
       <c r="H4">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I4">
-        <v>-4.41</v>
+        <v>-2.43</v>
       </c>
       <c r="J4">
-        <v>-10.18</v>
+        <v>-7.33</v>
       </c>
       <c r="K4">
-        <v>-19.48</v>
+        <v>-19.32</v>
       </c>
       <c r="L4">
-        <v>-31.32</v>
+        <v>-31.19</v>
       </c>
       <c r="M4">
-        <v>-7.66</v>
+        <v>-7.9</v>
       </c>
       <c r="N4">
         <v>33</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>413.82</v>
+        <v>411.76</v>
       </c>
       <c r="Q4">
-        <v>440.01</v>
+        <v>438.42</v>
       </c>
       <c r="R4">
-        <v>468.38</v>
+        <v>466.65</v>
       </c>
       <c r="S4">
-        <v>531.75</v>
+        <v>530.4</v>
       </c>
       <c r="T4">
-        <v>-22.52</v>
+        <v>-22.33</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,43 +1176,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>26.12</v>
+        <v>26.1</v>
       </c>
       <c r="Z4">
-        <v>-15.98</v>
+        <v>-16.02</v>
       </c>
       <c r="AA4">
-        <v>-13.44</v>
+        <v>-13.96</v>
       </c>
       <c r="AB4">
-        <v>-2.54</v>
+        <v>-2.06</v>
       </c>
       <c r="AC4">
-        <v>7.36</v>
+        <v>10.99</v>
       </c>
       <c r="AD4">
-        <v>3.68</v>
+        <v>7.34</v>
       </c>
       <c r="AE4">
-        <v>12.54</v>
+        <v>12.04</v>
       </c>
       <c r="AF4">
-        <v>-54.23</v>
+        <v>-54.73</v>
       </c>
       <c r="AG4">
-        <v>475.87</v>
+        <v>476.34</v>
       </c>
       <c r="AH4">
-        <v>404.16</v>
+        <v>400.5</v>
       </c>
       <c r="AI4">
-        <v>445.71</v>
+        <v>446.31</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>60.47</v>
+        <v>61.76</v>
       </c>
     </row>
   </sheetData>
@@ -1316,27 +1316,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U4">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V4">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W4">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y4">
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>3.83</v>
+        <v>6.5</v>
       </c>
       <c r="D7" s="5">
-        <v>6.5</v>
+        <v>8.19</v>
       </c>
       <c r="E7" s="6">
-        <v>2.67</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="D8" s="5">
-        <v>2.14</v>
+        <v>4.34</v>
       </c>
       <c r="E8" s="6">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-11.54</v>
+        <v>-10.18</v>
       </c>
       <c r="D9" s="5">
-        <v>-10.18</v>
+        <v>-7.33</v>
       </c>
       <c r="E9" s="6">
-        <v>1.36</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-0.53</v>
+        <v>-0.85</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.85</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.32</v>
+        <v>0.27</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.43</v>
+        <v>-3.68</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.68</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.25</v>
+        <v>-0.7</v>
+      </c>
+      <c r="E11" s="6">
+        <v>2.98</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.09</v>
+        <v>-4.41</v>
       </c>
       <c r="D12" s="5">
-        <v>-4.41</v>
+        <v>-2.43</v>
       </c>
       <c r="E12" s="6">
-        <v>0.68</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>1.02</v>
+        <v>0.65</v>
       </c>
       <c r="D13" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.37</v>
+        <v>1.48</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.83</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-19.67</v>
+        <v>-20.81</v>
       </c>
       <c r="D14" s="5">
-        <v>-20.81</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.14</v>
+        <v>-20.12</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-32.31</v>
+        <v>-31.32</v>
       </c>
       <c r="D15" s="5">
-        <v>-31.32</v>
+        <v>-31.19</v>
       </c>
       <c r="E15" s="6">
-        <v>0.99</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-3.72</v>
+        <v>-3.57</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.57</v>
+        <v>-2.5</v>
       </c>
       <c r="E16" s="6">
-        <v>0.15</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-5.94</v>
+        <v>-4.6</v>
       </c>
       <c r="D17" s="5">
-        <v>-4.6</v>
+        <v>-3.49</v>
       </c>
       <c r="E17" s="6">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-19.71</v>
+        <v>-19.48</v>
       </c>
       <c r="D18" s="5">
-        <v>-19.48</v>
+        <v>-19.32</v>
       </c>
       <c r="E18" s="6">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-5.84</v>
+        <v>-5.23</v>
       </c>
       <c r="D19" s="5">
-        <v>-5.23</v>
+        <v>-4.45</v>
       </c>
       <c r="E19" s="6">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-22.18</v>
+        <v>-22.71</v>
       </c>
       <c r="D20" s="5">
-        <v>-22.71</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.53</v>
+        <v>-22.33</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.38</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-40.3</v>
+        <v>-39.95</v>
       </c>
       <c r="D21" s="5">
-        <v>-39.95</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.35</v>
+        <v>-39.96</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1377.6</v>
+        <v>1386.6</v>
       </c>
       <c r="D22" s="5">
-        <v>1386.6</v>
+        <v>1398</v>
       </c>
       <c r="E22" s="6">
-        <v>9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1583.8</v>
+        <v>1572.9</v>
       </c>
       <c r="D23" s="5">
-        <v>1572.9</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-10.9</v>
+        <v>1580.8</v>
+      </c>
+      <c r="E23" s="6">
+        <v>7.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>409.55</v>
+        <v>412</v>
       </c>
       <c r="D24" s="5">
-        <v>412</v>
-      </c>
-      <c r="E24" s="6">
-        <v>2.45</v>
+        <v>411.95</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1716,13 +1716,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>51.65</v>
+        <v>54.03</v>
       </c>
       <c r="D25" s="5">
-        <v>54.03</v>
+        <v>56.94</v>
       </c>
       <c r="E25" s="6">
-        <v>2.38</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1733,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>46.33</v>
+        <v>44.56</v>
       </c>
       <c r="D26" s="5">
-        <v>44.56</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.77</v>
+        <v>46.17</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1.61</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1750,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>23.72</v>
+        <v>26.12</v>
       </c>
       <c r="D27" s="5">
-        <v>26.12</v>
-      </c>
-      <c r="E27" s="6">
-        <v>2.4</v>
+        <v>26.1</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1767,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-24.51</v>
+        <v>-7.95</v>
       </c>
       <c r="D28" s="5">
-        <v>-7.95</v>
-      </c>
-      <c r="E28" s="6">
-        <v>16.56</v>
+        <v>-17.77</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-9.82</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1784,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-62.81</v>
+        <v>-57.08</v>
       </c>
       <c r="D29" s="5">
-        <v>-57.08</v>
-      </c>
-      <c r="E29" s="6">
-        <v>5.73</v>
+        <v>-69.63</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-12.55</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1801,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>63.99</v>
+        <v>-54.23</v>
       </c>
       <c r="D30" s="5">
-        <v>-54.23</v>
+        <v>-54.73</v>
       </c>
       <c r="E30" s="7">
-        <v>-118.22</v>
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1866,22 +1866,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="10">
-        <v>49.72</v>
+        <v>49.7</v>
       </c>
       <c r="C2" s="11">
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>41.6</v>
+        <v>43.1</v>
       </c>
       <c r="E2" s="10">
         <v>33.3</v>
       </c>
       <c r="F2" s="10">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
       <c r="G2" s="10">
-        <v>-9.199999999999999</v>
+        <v>-8.4</v>
       </c>
       <c r="H2" s="10">
         <v>66</v>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1225</v>
+        <v>0.124</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0189</v>
+        <v>0.015</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0766</v>
+        <v>-0.079</v>
       </c>
     </row>
   </sheetData>
